--- a/mod_project/data_tables/qol_item_text.xlsx
+++ b/mod_project/data_tables/qol_item_text.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bread stuffed with yakisoba noodles. Sells out very quickly.</t>
+          <t>Yakisoba noodle bread. Sells out very quickly. (HP/TP +20, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>no room for (HP/TP +20, cures 1 ailment): 89 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Premium steak sandwich with luxury sauce. Extra deluxe.</t>
+          <t>Premium steak sandwich, luxury sauce. Extra deluxe. (HP/TP +30, cures all ailments)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -825,7 +825,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>no room for (HP/TP +30, cures all ailments): 87 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Super spicy curry that would make even a Maharaja groan.</t>
+          <t>Spicy curry that would make even a Maharaja groan. (HP/TP +150, cures all ailments)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>no room for (HP/TP +150, cures all ailments): 89 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Legendary food that's said to make any who eats it fall in love.</t>
+          <t>Legendary food. Whoever eats it falls in love. (HP/TP +1000, cures all ailments)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>no room for (HP/TP +1000, cures all ailments): 98 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>High in nutritional value, it heals HP and TP but is extremely bitter.</t>
+          <t>Highly nutritious, it heals HP and TP but is extremely bitter. (HP +50, TP +20)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>no room for (HP +50, TP +20): 87 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Beard's special bento. A well-balanced meal, and big enough to share.</t>
+          <t>Beard's special bento. Balanced, big enough to share. (party HP +75, party TP +25)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>no room for (party HP +75, party TP +25): 98 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Peggy's eggy milk pudding. It's said to be legendary. (TP +30, sleep 20%)</t>
+          <t>Peggy's eggy milk pudding. It's said to be legendary. (TP +30, 20% sleep)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Kumaya Mangetsudo's anpan. It's low-calorie, but still delicious.</t>
+          <t>Kumaya Mangetsudo's anpan. Low-calorie, but still delicious. (HP/TP +20, 15% sleep)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>no room for (HP/TP +20, sleep 15%): 88 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mrs. Mary's snack smothered in maple butter. (HP/TP +20, sleep 15%)</t>
+          <t>Mrs. Mary's snack smothered in maple butter. (HP/TP +20, 15% sleep)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Honey-filled monaka sold at the Kumana Mangetsudo. (TP +30, sleep 20%)</t>
+          <t>Honey-filled monaka sold at the Kumana Mangetsudo. (TP +30, 20% sleep)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Consists of Mary Florina's super rich milk collagen. Sorts ailments right out.</t>
+          <t>Mary Florina's rich milk collagen gel. (cures all ailments, restores stats)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>no room for (cures all ailments, restores stats): 115 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>There's a cure for pretty much anything, and there's plenty of it.</t>
+          <t>A cure for anything, and plenty of it. (cures all ailments, restores stats)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>no room for (cures all ailments, restores stats): 103 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>It scrambles your brain, and then you die. No coming back from that.</t>
+          <t>It scrambles your brain, and then you die. No coming back from that. (10% instakill)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2067,11 +2067,7 @@
           <t>It scrambles your brain, and then you die. No coming back from that (25% Death).</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2091,7 +2087,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Inscribed with impressive wish-granting runes.</t>
+          <t>Inscribed with impressive wish-granting runes. (80% Divine Shield, 80% Insurance)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2105,11 +2101,7 @@
           <t>Inscribed with impressive wish-granting runes.</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2163,7 +2155,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Rock-hard cracker. Not just a snack, but also an emergency ration!</t>
+          <t>Rock-hard cracker. Snack and emergency ration! (HP/TP +75, cancels Shadow Sew)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2180,7 +2172,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>no room for (HP/TP +75, cancels Shadow Sew): 98 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2304,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A miraculous wind that once brought spring to the underworld.</t>
+          <t>Wind that brought spring to the underworld. (80% party ATK up, 80% party DEF up)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2328,7 +2320,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2380,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>For those elegant afternoons.</t>
+          <t>For those elegant afternoons. (60% evasion up)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2402,11 +2394,7 @@
           <t>For those elegant afternoons (+60% EVA).</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2426,7 +2414,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Everyone has been looking, and we've finally found it!</t>
+          <t>Everyone has been looking, and we've finally found it! (20% Berserk)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2440,11 +2428,7 @@
           <t>Everyone has been looking, and we've finally found it! (+20% ATK).</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2600,7 +2584,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>When I peeked in, something peeked back... There's someone in there!</t>
+          <t>When I peeked in, something peeked back... There's someone in there! (6% instakill)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2614,11 +2598,7 @@
           <t>When I peeked in, something peeked back... There's someone in there! (25% Death).</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2880,7 +2860,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Whatever's under all that breading, you can bet it's good and fried.</t>
+          <t>Whatever's under the breading, it's good and fried. (HP/TP +175, 75% Berserk)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2896,7 +2876,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2932,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Those memories are precious... and painful.</t>
+          <t>Those memories are precious... and painful. (20% silence)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2966,11 +2946,7 @@
           <t>Those memories are precious... and painful (40% Silence).</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3232,7 +3208,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>I must immediately depart on a long, long journey. Don't look for me.</t>
+          <t>I must immediately depart on a long, long journey. Don't look for me. (25% silence)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3246,11 +3222,7 @@
           <t>I must immediately depart on a long, long journey. Don't look for me (50% Silence).</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3308,7 +3280,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>A red feather you receive after donating to a fundraiser.</t>
+          <t>A red feather you receive after donating to a fundraiser. (TP +150, 75% Berserk)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3322,11 +3294,7 @@
           <t>A red feather you receive after donating to a fundraiser (+75% ATK).</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3346,7 +3314,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Creepy pitch-black rosary.</t>
+          <t>Creepy pitch-black rosary. (25% stun)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3360,11 +3328,7 @@
           <t>Creepy pitch-black rosary (50% Blind).</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3384,7 +3348,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cursed words from an ex-girlfriend. She's really vile...</t>
+          <t>Cursed words from an ex-girlfriend. She's really vile... (30% petrify)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3399,11 +3363,7 @@
 (Inflict Gray Curse (75% chance).)</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3491,7 +3451,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>One prick with this needle would be disastrous. Handle with care.</t>
+          <t>One prick with this needle would be disastrous. Handle with care. (20% poison)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3505,11 +3465,7 @@
           <t>One prick with this needle would be disastrous. Handle with care (40% Poison).</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3529,7 +3485,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>A mirror that reveals the truth... You might not want to look.</t>
+          <t>A mirror that reveals the truth... You might not want to look. (15% stun)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3543,11 +3499,7 @@
           <t>A mirror that reveals the truth... You might not want to look (30% Blind).</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3673,7 +3625,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>You can be a magical girl too.</t>
+          <t>You can be a magical girl too. (40% 2 clones)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3687,11 +3639,7 @@
           <t>You can be a magical girl too.</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3817,7 +3765,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>A disconcerting egg. The face is always screaming.</t>
+          <t>A disconcerting egg. The face is always screaming. (25% instakill)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3831,11 +3779,7 @@
           <t>A disconcerting egg. The face is always screaming (90% Death).</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3855,7 +3799,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Clay used for handicraft in the heavens. Heh. They soil themselves.</t>
+          <t>Clay used for handicraft in the heavens. Heh. They soil themselves. (10% 2 clones)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3869,11 +3813,7 @@
           <t>Clay used for handicraft in the heavens. Heh. They soil themselves.</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3893,7 +3833,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Vial of mysterious holy water. Tiny waves are ever-present at the top.</t>
+          <t>Vial of mysterious holy water. Tiny waves ripple at the top. (cures 1 ailment)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3910,7 +3850,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>no room for (cures 1 ailment): 88 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3872,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fried up in an iron pan. A steal at 3 million lira!</t>
+          <t>Fried up in an iron pan. A steal at 3 million lira! (HP +50, 20% ATK up)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3946,11 +3886,7 @@
           <t>Fried up in an iron pan. A steal at 3 million lira! (+20% ATK).</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3970,7 +3906,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>There's no wind blowing, yet you can hear its sound. It cries Mary.</t>
+          <t>There's no wind blowing, yet you can hear its sound. It cries Mary. (15% silence)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3984,11 +3920,7 @@
           <t>There's no wind blowing, yet you can hear its sound. It cries Mary (30% Silence).</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4080,7 +4012,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Just one drop will refresh constantly overworked eyes.</t>
+          <t>Just one drop will refresh constantly overworked eyes. (80% accuracy up)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4094,11 +4026,7 @@
           <t>Just one drop will refresh constantly overworked eyes (Accuracy +80%.).</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4225,7 +4153,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Make a man out of this and it comes to life. Weird.</t>
+          <t>Make a man out of this and it comes to life. Weird. (30% Insurance)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -4239,11 +4167,7 @@
           <t>Make a man out of this and it comes to life. Weird.</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4297,7 +4221,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>If this is waiting back at the base, you know someone's about to die.</t>
+          <t>If this waits back at base, someone's about to die. (TP +40, 30% instakill)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4313,7 +4237,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4361,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Moist with the power of life.</t>
+          <t>Moist with the power of life. (50% max HP up)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4451,11 +4375,7 @@
           <t>Moist with the power of life.</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4683,7 +4603,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Plan the perfect trip to the world beyond the veil.</t>
+          <t>Plan the perfect trip to the world beyond the veil. (10% instakill)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -4697,11 +4617,7 @@
           <t>Plan the perfect trip to the world beyond the veil (20% Death).</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4827,7 +4743,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Smooth, sticky lotion for professional use.</t>
+          <t>Smooth, sticky lotion for professional use. (30% evasion up)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4841,11 +4757,7 @@
           <t>Smooth, sticky lotion for professional use (+30% EVA).</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4899,7 +4811,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>A skull ascended through a secret rite. It's said to grant wishes.</t>
+          <t>A skull from a secret rite. Grants wishes. (60% party ATK up, 30% party magic DEF up)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4915,7 +4827,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -5005,7 +4917,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>A branch only certain people are allowed to pray to. It's twig-sclusive.</t>
+          <t>A branch only some may pray to. It's twig-sclusive. (cures all ailments)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5022,7 +4934,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>no room for (cures all ailments): 93 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -5044,7 +4956,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>A bud of a tree that grows where God resides.</t>
+          <t>A bud of a tree that grows where God resides. (50% party cure-all)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5058,11 +4970,7 @@
           <t>A bud of a tree that grows where God resides.</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5082,7 +4990,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sandals that are no longer of any use. Might as well toss 'em.</t>
+          <t>Sandals that are no longer of any use. Might as well toss 'em. (15% evasion up)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5096,11 +5004,7 @@
           <t>Sandals that are no longer of any use. Might as well toss 'em (+15% EVA).</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5230,7 +5134,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Stone core made when an evil heart has hardened completely.</t>
+          <t>Stone core made when an evil heart has hardened completely. (20% stun)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -5244,11 +5148,7 @@
           <t>Stone core made when an evil heart has hardened completely (35% Blind).</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5268,7 +5168,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Do YOU ever ruin your good cleaver on bone? Finally, there's help!</t>
+          <t>Do YOU ever ruin your good cleaver on bone? Finally, there's help! (50% ATK up)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5282,11 +5182,7 @@
           <t>Do YOU ever ruin your good cleaver on bone? Finally, there's help! (+50% ATK).</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5451,7 +5347,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>It might be able to take... one more hit. Hit it baby one more time.</t>
+          <t>It might take... one more hit. Hit it baby one more time. (30 fixed damage)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5467,7 +5363,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5385,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Do the goggles switch her personality, or just give her confidence...?</t>
+          <t>Do the goggles switch her personality, or just add confidence...? (50% max HP up)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5505,7 +5401,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5495,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Drop made out of collected mirage.</t>
+          <t>Drop made out of collected mirage. (20% Divine Shield)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -5613,11 +5509,7 @@
           <t>Drop made out of collected mirage.</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5637,7 +5529,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>A large, mysterious key made in Hyperborea.</t>
+          <t>A large, mysterious key made in Hyperborea. (40% 1 clone)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -5651,11 +5543,7 @@
           <t>A large, mysterious key made in Hyperborea.</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5675,7 +5563,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Eat this and you may die on the spot... or not at all.</t>
+          <t>Eat this and you may die on the spot... or not at all. (90% instakill, TP +999)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -5689,11 +5577,7 @@
           <t>Eat this and you may die on the spot... or not at all (+999 TP).</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5781,7 +5665,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Tonight, I will steal away your heart.</t>
+          <t>Tonight, I will steal away your heart. (80% accuracy up)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -5795,11 +5679,7 @@
           <t>Tonight, I will steal away your heart (Accuracy +80%.).</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5853,7 +5733,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>A support item used by people who can't swim.</t>
+          <t>A support item used by people who can't swim. (cures freeze)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -5867,11 +5747,7 @@
           <t>A support item used by people who can't swim (Cure Freeze).</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6061,7 +5937,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Rice-based liquor aged for more than three years.</t>
+          <t>Rice-based liquor aged for more than three years. (TP +50, 50% Berserk)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6075,11 +5951,7 @@
           <t>Rice-based liquor aged for more than three years (+50% ATK).</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6099,7 +5971,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>For nailing uncooperative ogres to the ground.</t>
+          <t>For nailing uncooperative ogres to the ground. (30% slow)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6113,11 +5985,7 @@
           <t>For nailing uncooperative ogres to the ground (Speed DOWN -60%.).</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6323,7 +6191,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Oil you can rub on a wound in place of salve. If you want.</t>
+          <t>Oil you can rub on a wound in place of salve. If you want. (HP +60, 20% evasion up)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6337,11 +6205,7 @@
           <t>Oil you can rub on a wound in place of salve. If you want (+20% EVA).</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6399,7 +6263,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Somebody shut it up!</t>
+          <t>Somebody shut it up! (cures sleep)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -6413,11 +6277,7 @@
           <t>Somebody shut it up! (Cure Sleep).</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6437,7 +6297,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Looks like that's a YES. (HP +200, sleep 75%)</t>
+          <t>Looks like that's a YES. (HP +200, 75% sleep)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6509,7 +6369,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Huge poisonous spike plucked from a tarasque's back.</t>
+          <t>Huge poisonous spike plucked from a tarasque's back. (35% poison)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6523,11 +6383,7 @@
           <t>Huge poisonous spike plucked from a tarasque's back (75% Poison).</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6657,7 +6513,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Fake version of Alexandrite Cat's Eye.</t>
+          <t>Fake version of Alexandrite Cat's Eye. (30% accuracy up)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -6671,11 +6527,7 @@
           <t>Fake version of Alexandrite Cat's Eye (Accuracy +30%.).</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6832,7 +6684,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>You were forced to buy it at 5x the market price. I could cry. (sleep 90%)</t>
+          <t>You were forced to buy it at 5x the market price. I could cry. (90% sleep)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -6866,7 +6718,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Unfortunately, it's a one-way ticket.</t>
+          <t>Unfortunately, it's a one-way ticket. (10% petrifying)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -6880,11 +6732,7 @@
           <t>Unfortunately, it's a one-way ticket (Inflict Curse (40% chance).).</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6904,7 +6752,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Apparently it'll send you to another world with just one sip (it's poison).</t>
+          <t>It'll send you to another world with just one sip (it's poison). (30% instakill)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -6921,7 +6769,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6791,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Still a step or two away from being a salad.</t>
+          <t>Still a step or two away from being a salad. (20% Divine Shield)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -6957,11 +6805,7 @@
           <t>Still a step or two away from being a salad.</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7015,7 +6859,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Said to bring its holder happiness.</t>
+          <t>Said to bring its holder happiness. (30% Insurance, 30% evasion up)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7029,11 +6873,7 @@
           <t>Said to bring its holder happiness (+30% EVA).</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7053,7 +6893,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Honestly, just cut me some slack.</t>
+          <t>Honestly, just cut me some slack. (15% petrifying)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7067,11 +6907,7 @@
           <t>Honestly, just cut me some slack (Inflict Curse (30% chance).).</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7091,7 +6927,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>It says it's lucky. You can't believe everything you read, now can you?</t>
+          <t>It says it's lucky. You can't believe everything you read, now can you? (15% silence)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7106,11 +6942,7 @@
 (30% Silence)</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7130,7 +6962,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>A letter that simply says: You are my fire. My one desire.</t>
+          <t>A letter that simply says: You are my fire. My one desire. (50% accuracy up)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7144,11 +6976,7 @@
           <t>A letter that simply says: You are my fire. My one desire (Accuracy +50%.).</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7168,7 +6996,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>The prompt asks, who's your personal hero? I wrote, 'Me.'</t>
+          <t>The prompt asks, who's your personal hero? I wrote, 'Me.' (80% Berserk)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7182,11 +7010,7 @@
           <t>The prompt asks, who's your personal hero? I wrote, 'Me.' (+80% ATK).</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7206,7 +7030,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Tiger scroll filled with innermost secrets of martial arts.</t>
+          <t>Tiger scroll filled with innermost secrets of martial arts. (30% ATK up)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7220,11 +7044,7 @@
           <t>Tiger scroll filled with innermost secrets of martial arts (+30% ATK).</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7244,7 +7064,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>The symbol of justice. Who needs bats, anyways?</t>
+          <t>The symbol of justice. Who needs bats, anyways? (50% ATK up)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7258,11 +7078,7 @@
           <t>The symbol of justice. Who needs bats, anyways? (+50% ATK).</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7388,7 +7204,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Holy river water that contains all sorts of extracts. Extracts...</t>
+          <t>Holy river water that contains all sorts of extracts. Extracts... (TP +100, 75% stun)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7403,11 +7219,7 @@
 (+100 TP, 75% Blind)</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7567,7 +7379,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>More of a snow acquaintance. A snowperson at any rate.</t>
+          <t>More of a snow acquaintance. A snowperson at any rate. (20% freeze)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -7581,11 +7393,7 @@
           <t>More of a snow acquaintance. A snowperson at any rate (40% Freeze).</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7923,7 +7731,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>An origami crane made with an exceedingly high number of folds.</t>
+          <t>An origami crane made with an exceedingly high number of folds. (60% party cure-all)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7937,11 +7745,7 @@
           <t>An origami crane made with an exceedingly high number of folds.</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8101,7 +7905,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Dangerous box that shoots out needles when opened improperly.</t>
+          <t>Dangerous box that shoots out needles when opened improperly. (110 fixed damage)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8115,11 +7919,7 @@
           <t>Dangerous box that shoots out needles when opened improperly.</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8207,7 +8007,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>A box full of contracts signed under threat of violence.</t>
+          <t>A box full of contracts signed under threat of violence. (party 150 fixed damage)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8221,11 +8021,7 @@
           <t>A box full of contracts signed under threat of violence.</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8313,7 +8109,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>A sword with a bamboo grip. For some reason, the grip... reeks.</t>
+          <t>A sword with a bamboo grip. For some reason, the grip... reeks. (35% stun)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -8327,11 +8123,7 @@
           <t>A sword with a bamboo grip. For some reason, the grip... reeks (50% Blind).</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8385,7 +8177,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>A giant bloodshot eyeball. At least it's not moving.</t>
+          <t>A giant bloodshot eyeball. At least it's not moving. (35% paralysis)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -8399,11 +8191,7 @@
           <t>A giant bloodshot eyeball. At least it's not moving (50% Paralysis).</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8423,7 +8211,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>A chain that's been worn down by too much grinding. Kinda like my ex.</t>
+          <t>A chain worn down by too much grinding. Kinda like my ex. (15 fixed damage)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -8439,7 +8227,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8351,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Despite its not having a head, you swear you've heard it giggle.</t>
+          <t>Despite its not having a head, you swear you've heard it giggle. (22% paralysis)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8577,11 +8365,7 @@
           <t>Despite its not having a head, you swear you've heard it giggle (35% Paralysis).</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8601,7 +8385,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Doll that changes to look just like you when you press its nose.</t>
+          <t>Doll that changes to look just like you when you press its nose. (30% 1 clone)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8615,11 +8399,7 @@
           <t>Doll that changes to look just like you when you press its nose.</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8775,7 +8555,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Every time you look at it, the people are in different poses.</t>
+          <t>Every time you look at it, the people are in different poses. (15% silence)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8789,11 +8569,7 @@
           <t>Every time you look at it, the people are in different poses (30% Silence).</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8813,7 +8589,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>A primal scream that resounds through the natural world.</t>
+          <t>A primal scream that resounds through the natural world. (20% stun)</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8827,11 +8603,7 @@
           <t>A primal scream that resounds through the natural world (40% Blind).</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8987,7 +8759,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Low-tech but reliable way to warm up.</t>
+          <t>Low-tech but reliable way to warm up. (cures freeze)</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9001,11 +8773,7 @@
           <t>Low-tech but reliable way to warm up (Cure Freeze).</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9025,7 +8793,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Not for use indoors. DEFINITELY not for use in a vehicle!</t>
+          <t>Not for use indoors. DEFINITELY not for use in a vehicle! (15% instakill)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9039,11 +8807,7 @@
           <t>Not for use indoors. DEFINITELY not for use in a vehicle! (30% Death).</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9097,7 +8861,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Used for voodoo curses. Picture your enemy, and give it your all!</t>
+          <t>Used for voodoo curses. Picture your enemy, and give it your all! (12% stun)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9111,11 +8875,7 @@
           <t>Used for voodoo curses. Picture your enemy, and give it your all! (15% Blind).</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9135,7 +8895,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Jelly infused with natural demon... stuff.</t>
+          <t>Jelly infused with natural demon... stuff. (10% poison, 10% silence)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9149,11 +8909,7 @@
           <t>Jelly infused with natural demon... stuff (20% Poison, 20% Silence).</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9321,7 +9077,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Mist that covers your skin in glossy beads.</t>
+          <t>Mist that covers your skin in glossy beads. (TP +150, 30% freeze)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9335,11 +9091,7 @@
           <t>Mist that covers your skin in glossy beads (+150 TP, 30% Freeze).</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9431,7 +9183,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>I'd like to think this is the cause for my weight gain...</t>
+          <t>I'd like to think this is the cause for my weight gain... (40% slow)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9445,11 +9197,7 @@
           <t>I'd like to think this is the cause for my weight gain.. (Speed DOWN -60%.).</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9542,7 +9290,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Collecting seven of these summons a dragon that grants your wishes.</t>
+          <t>Collect seven of these to summon a wish-granting dragon. (75% strips buffs)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9558,7 +9306,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -9618,7 +9366,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>It had to be removed due to cavity.</t>
+          <t>It had to be removed due to cavity. (35% poison)</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9632,11 +9380,7 @@
           <t>It had to be removed due to cavity (60% Poison).</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9656,7 +9400,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>A paralyzing claw that was cut to the quick.</t>
+          <t>A paralyzing claw that was cut to the quick. (35% paralysis)</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9670,11 +9414,7 @@
           <t>A paralyzing claw that was cut to the quick (60% Paralysis).</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9732,7 +9472,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>No-good apple that tempts women into strife.</t>
+          <t>No-good apple that tempts women into strife. (party TP +100, party 500 fixed damage)</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -9746,11 +9486,7 @@
           <t>No-good apple that tempts women into strife (Party: +100 TP).</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9804,7 +9540,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Huge bell that wards off evil when run. Awkward to carry around.</t>
+          <t>Huge bell that wards off evil when run. Awkward to carry around. (20% party DEF up)</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -9818,11 +9554,7 @@
           <t>Huge bell that wards off evil when run. Awkward to carry around.</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9842,7 +9574,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Water from a shrine that venerates a god of the land.</t>
+          <t>Water from a shrine that venerates a god of the land. (90% party cure-all)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -9856,11 +9588,7 @@
           <t>Water from a shrine that venerates a god of the land.</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9880,7 +9608,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Fruit goes in the dragon. This stuff comes out. Don't ask.</t>
+          <t>Fruit goes in the dragon. This stuff comes out. Don't ask. (TP +50, 40% Berserk)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -9894,11 +9622,7 @@
           <t>Fruit goes in the dragon. This stuff comes out. Don't ask (+40% ATK).</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9918,7 +9642,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Press it if you want peace at any cost. There may be consequences...</t>
+          <t>Press it for peace at any cost. There may be consequences... (90% strips buffs)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -9934,7 +9658,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9680,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Used by busy mommy dragons to keep their babies quiet. (sleep 20%)</t>
+          <t>Used by busy mommy dragons to keep their babies quiet. (20% sleep)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -9990,7 +9714,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Tough enough to survive in a mouth full of dragon baby teeth. (sleep 40%)</t>
+          <t>Tough enough to survive in a mouth full of dragon baby teeth. (40% sleep)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -10058,7 +9782,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>A strange substance that feels like nothingness when you touch it.</t>
+          <t>A strange substance that feels like nothingness when you touch it. (30% evasion up)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -10072,11 +9796,7 @@
           <t>A strange substance that feels like nothingness when you touch it (+30% EVA).</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10096,7 +9816,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Not for napping in. For hiding people taking naps. (HP +200, sleep 90%)</t>
+          <t>Not for napping in. For hiding people taking naps. (HP +200, 90% sleep)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -10130,7 +9850,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>A mask that is just gold in color. Not all that glitters is gold.</t>
+          <t>A mask that is just gold in color. Not all that glitters is gold. (12% paralysis)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -10144,11 +9864,7 @@
           <t>A mask that is just gold in color. Not all that glitters is gold (15% Paralysis).</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10240,7 +9956,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Goodnight forever.</t>
+          <t>Goodnight forever. (20% instakill)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -10254,11 +9970,7 @@
           <t>Goodnight forever (60% Death).</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10384,7 +10096,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Dangerous! Do not touch! Deadly poison! Requires careful handling!</t>
+          <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! (15% instakill)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -10398,11 +10110,7 @@
           <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! (40% Death).</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10422,7 +10130,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! #2</t>
+          <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! #2 (20% instakill)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -10436,11 +10144,7 @@
           <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! #2 (80% Death).</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10460,7 +10164,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>A nice little rowboat. Cruise the river separating life and death.</t>
+          <t>A nice little rowboat. Cruise the river separating life and death. (30% instakill)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -10474,11 +10178,7 @@
           <t>A nice little rowboat. Cruise the river separating life and death (95% Death).</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10498,7 +10198,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Sweet mint immortali-tea. More relaxing than relaxation itself. (TP +35, sleep 25%)</t>
+          <t>Sweet mint immortali-tea. More relaxing than relaxation itself. (TP +35, 25% sleep)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -10532,7 +10232,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>So much jealousy, it's visible to the naked eye.</t>
+          <t>So much jealousy, it's visible to the naked eye. (30% paralysis, 30% sleep)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -10546,11 +10246,7 @@
           <t>So much jealousy, it's visible to the naked eye (30% Paralysis, 30% Sleep).</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10604,7 +10300,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Bun that gives off the taste of the afterlife.</t>
+          <t>Bun that gives off the taste of the afterlife. (HP +60, 25% stun)</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -10618,11 +10314,7 @@
           <t>Bun that gives off the taste of the afterlife (+60 HP, 25% Blind).</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10676,7 +10368,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>I really hope my photo's not on there.</t>
+          <t>I really hope my photo's not on there. (15% petrifying)</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -10690,11 +10382,7 @@
           <t>I really hope my photo's not on there (Inflict Curse (20% chance).).</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10748,7 +10436,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>You'll want to stay away from the water this came from.</t>
+          <t>You'll want to stay away from the water this came from. (25% paralysis)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -10762,11 +10450,7 @@
           <t>You'll want to stay away from the water this came from (50% Paralysis).</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10854,7 +10538,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Living shadow that leaves and acts on its own.</t>
+          <t>Living shadow that leaves and acts on its own. (25% 2 clones)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -10868,11 +10552,7 @@
           <t>Living shadow that leaves and acts on its own.</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10892,7 +10572,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Toss it in to any potluck stew to instantly increase the chaos.</t>
+          <t>Toss it in to any potluck stew to instantly increase the chaos. (50 fixed damage)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -10906,11 +10586,7 @@
           <t>Toss it in to any potluck stew to instantly increase the chaos.</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10964,7 +10640,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Just ignore them.</t>
+          <t>Just ignore them. (20% silence)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -10978,11 +10654,7 @@
           <t>Just ignore them (40% Silence).</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -11002,7 +10674,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Disembodied wrist. Scurries all over the floor like a cleaning robot.</t>
+          <t>Disembodied wrist. Scurries all over the floor like a cleaning robot. (30% stun)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -11016,11 +10688,7 @@
           <t>Disembodied wrist. Scurries all over the floor like a cleaning robot (60% Blind).</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -11188,7 +10856,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Ice cream in a peach-shaped container.</t>
+          <t>Ice cream in a peach-shaped container. (TP +12, 20% freeze)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -11202,11 +10870,7 @@
           <t>Ice cream in a peach-shaped container (+12 TP, 20% Freeze).</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11226,7 +10890,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Sweet mixed drink popular with the ladies. (TP +24, sleep 20%)</t>
+          <t>Sweet mixed drink popular with the ladies. (TP +24, 20% sleep)</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -11328,7 +10992,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Sweet persimmons fumigated with sulfur for preservation. Tasty.</t>
+          <t>Sweet persimmons preserved with sulfur. Tasty. (TP +15, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -11345,7 +11009,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>no room for (TP +15, cures 1 ailment): 89 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11065,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Sushi wrapped in persimmon leaves. Don't eat the leaves, kiddo.</t>
+          <t>Sushi in persimmon leaves. Don't eat the leaves. (party HP +130, cancels Shadow Sew)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -11418,7 +11082,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>no room for (party HP +130, cancels Shadow Sew): 99 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11104,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Stew of bear-meat citatap with pukusakina and plenty of veggies.</t>
+          <t>Bear-meat citatap stew with pukusakina and veggies. (party HP +600, cures freeze)</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -11457,7 +11121,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11143,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Bear soup that warms up your body.</t>
+          <t>Bear soup that warms up your body. (HP +200, cures freeze)</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -11493,11 +11157,7 @@
           <t>Bear soup that warms up your body (+200 HP, Cure Freeze).</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11619,7 +11279,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Piping hot fried chicken. Ask before you add lemon juice, just to be safe.</t>
+          <t>Hot fried chicken. Ask before you add lemon juice. (HP +240, restores stats)</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
@@ -11636,7 +11296,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>no room for (HP +240, restores stats): 100 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11488,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Fried lamb meatballs with strong coriander scent.</t>
+          <t>Fried lamb meatballs with strong coriander scent. (TP +50, 100% evasion up)</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -11842,11 +11502,7 @@
           <t>Fried lamb meatballs with strong coriander scent (+100% EVA).</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11900,7 +11556,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Brave penguins gave their lives to bring you fuel and soap.</t>
+          <t>Brave penguins gave their lives to bring you fuel and soap. (80% evasion up)</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -11914,11 +11570,7 @@
           <t>Brave penguins gave their lives to bring you fuel and soap (+80% EVA).</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11972,7 +11624,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Feel refreshed by the mint's cold and transcendent stimulation.</t>
+          <t>Feel refreshed by the mint's cold, transcendent stimulation. (HP +200, cures sleep)</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
@@ -11988,7 +11640,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12036,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Supplement with a pungently strange odor.</t>
+          <t>Supplement with a pungently strange odor. (5% poison)</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
@@ -12398,11 +12050,7 @@
           <t>Supplement with a pungently strange odor (5% Poison).</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12422,7 +12070,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Sketchy in over seven ways. Get it? Like seven colors of the rainbow!</t>
+          <t>Sketchy in over seven ways. Get it? Like seven colors of the rainbow! (10% stun)</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
@@ -12436,11 +12084,7 @@
           <t>Sketchy in over seven ways. Get it? Like seven colors of the rainbow! (10% Blind).</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12460,7 +12104,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>All your exhaustion magically melts away.</t>
+          <t>All your exhaustion magically melts away. (20% Insurance)</t>
         </is>
       </c>
       <c r="E334" t="inlineStr"/>
@@ -12474,11 +12118,7 @@
           <t>All your exhaustion magically melts away.</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12566,7 +12206,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Three delicious aspects of the dumpling, together on one skewer.</t>
+          <t>Three aspects of the dumpling on one skewer. (party HP +180, 60% party ATK up)</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
@@ -12582,7 +12222,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -12676,7 +12316,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Raw meat cut fine and called a steak. Consume with caution.</t>
+          <t>Raw meat cut fine and called a steak. Eat with caution. (HP/TP +2000, 95% 1 clone)</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
@@ -12692,7 +12332,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -12850,7 +12490,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Glutinous steamed rice dish with big pieces of chestnut.</t>
+          <t>Glutinous steamed rice dish with big pieces of chestnut. (HP +515, 30% 1 clone)</t>
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
@@ -12864,11 +12504,7 @@
           <t>Glutinous steamed rice dish with big pieces of chestnut (+515 HP).</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12922,7 +12558,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Seashell-shaped snack. Sally sells them by the seashore.</t>
+          <t>Seashell-shaped snack. Sally sells them by the seashore. (HP +135, 30% accuracy up)</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
@@ -12936,11 +12572,7 @@
           <t>Seashell-shaped snack. Sally sells them by the seashore (+135 HP).</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12960,7 +12592,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Solidified syrup and dry fruit. A hard candy for hard men.</t>
+          <t>Syrup and dry fruit. A hard candy for hard men. (party HP +165, restores stats)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
@@ -12977,7 +12609,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>no room for (party HP +165, restores stats): 90 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12631,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>A cake with a figurine in it. Whoever finds the little feller gets to be king.</t>
+          <t>Cake with a figurine. Whoever finds it gets to be king. (party HP +250, party TP +25)</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -13016,7 +12648,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>no room for (party HP +250, party TP +25): 108 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -13072,7 +12704,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Off the shelf or the classy kind? They're really not that different.</t>
+          <t>Off the shelf or classy? Really not that different. (HP +50, 50% accuracy up)</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
@@ -13088,7 +12720,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -13110,7 +12742,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Party pastry constructed of fruits, custard, and jelly.</t>
+          <t>Party pastry of fruits, custard, and jelly. (party TP +115, 70% party magic DEF up)</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
@@ -13126,7 +12758,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -13216,7 +12848,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>A cookie cut into a highly complex shape. Ooh, looks like Japan!</t>
+          <t>A cookie in a complex shape. Looks like Japan! (party HP +200, 60% party cure-all)</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
@@ -13232,7 +12864,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -13288,7 +12920,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Rice cracker covered in plenty of cayenne powder.</t>
+          <t>Rice cracker covered in plenty of cayenne powder. (HP +120, 25% Defender)</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -13302,11 +12934,7 @@
           <t>Rice cracker covered in plenty of cayenne powder (+120 HP).</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -13326,7 +12954,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Just a cracker with tasty sauce, but dang, that's tasty.</t>
+          <t>Just a cracker with tasty sauce, but dang, that's tasty. (HP +240, 50% Defender)</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -13340,11 +12968,7 @@
           <t>Just a cracker with tasty sauce, but dang, that's tasty (+240 HP).</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13364,7 +12988,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Pre-chewed for convenience. Yum!</t>
+          <t>Pre-chewed for convenience. Yum! (HP +300, 70% Defender)</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -13378,11 +13002,7 @@
           <t>Pre-chewed for convenience. Yum! (+300 HP).</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13436,7 +13056,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Extremely smelly and rotten tofu.</t>
+          <t>Extremely smelly and rotten tofu. (HP +120, 90% silence)</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
@@ -13450,11 +13070,7 @@
           <t>Extremely smelly and rotten tofu (+120 HP, 90% Silence).</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -13686,7 +13302,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Eat a long candy, live a long life. It's just math.</t>
+          <t>Eat a long candy, live a long life. It's just math. (TP +150, 75% accuracy up)</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -13700,11 +13316,7 @@
           <t>Eat a long candy, live a long life. It's just math (+150 TP).</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13724,7 +13336,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>An extremely rare, top-notch candy from the demon world.</t>
+          <t>Rare, top-notch candy from the demon world. (party HP/TP +666, 95% party cure-all)</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -13740,7 +13352,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13374,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Meatball patty with conspicuous chunks of onion.</t>
+          <t>Meatball patty with conspicuous chunks of onion. (HP +80, 35% ATK up)</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -13776,11 +13388,7 @@
           <t>Meatball patty with conspicuous chunks of onion (+35% ATK).</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13800,7 +13408,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Sunny-side up egg on a patty. When to break the yolk...?</t>
+          <t>Sunny-side up egg on a patty. When to break the yolk...? (HP +300, 75% ATK up)</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -13814,11 +13422,7 @@
           <t>Sunny-side up egg on a patty. When to break the yolk...? (+75% ATK).</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13986,7 +13590,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>An ominous monaka in the shape of a coffin.</t>
+          <t>An ominous monaka in the shape of a coffin. (35% instakill)</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
@@ -14000,11 +13604,7 @@
           <t>An ominous monaka in the shape of a coffin (95% Death).</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -14024,7 +13624,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Sesame, white bean paste, and... red bean paste!</t>
+          <t>Sesame, white bean paste, and... red bean paste! (HP +400, 75% accuracy up)</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
@@ -14038,11 +13638,7 @@
           <t>Sesame, white bean paste, and... red bean paste! (+400 HP).</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -14096,7 +13692,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Bright macarons with an assortment of colors.</t>
+          <t>Bright macarons with an assortment of colors. (HP +150, 75% accuracy up)</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -14110,11 +13706,7 @@
           <t>Bright macarons with an assortment of colors (+150 HP).</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -14134,7 +13726,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Cookies for your iron abs.</t>
+          <t>Cookies for your iron abs. (HP +50, 75% DEF up)</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
@@ -14148,11 +13740,7 @@
           <t>Cookies for your iron abs (+75% DEF).</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -14172,7 +13760,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Cake for your swole six-pack.</t>
+          <t>Cake for your swole six-pack. (HP +100, 50% ATK up)</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
@@ -14186,11 +13774,7 @@
           <t>Cake for your swole six-pack (+50% ATK).</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -14210,7 +13794,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Staple food on Planet Muscle. Go from ripped to jacked.</t>
+          <t>Staple food on Planet Muscle. Go from ripped to jacked. (HP +300, 75% max HP up)</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -14224,11 +13808,7 @@
           <t>Staple food on Planet Muscle. Go from ripped to jacked (+300 HP).</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -14248,7 +13828,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Apple drink. Sweet, spiked, or sparkling. (TP +55, sleep 10%)</t>
+          <t>Apple drink. Sweet, spiked, or sparkling. (TP +55, 10% sleep)</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -14282,7 +13862,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Mellow, rich, and just the right amount of bitter. (TP +74, sleep 25%)</t>
+          <t>Mellow, rich, and just the right amount of bitter. (TP +74, 25% sleep)</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -14316,7 +13896,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Sultry spirit. The perfect apertif. (TP +140, sleep 35%)</t>
+          <t>Sultry spirit. The perfect apertif. (TP +140, 35% sleep)</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -14350,7 +13930,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>The oil of conversation. The philosophic wine. (TP +999, sleep 45%)</t>
+          <t>The oil of conversation. The philosophic wine. (TP +999, 45% sleep)</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -14384,7 +13964,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>You know you should stop but you just can't kelp yourself.</t>
+          <t>You know you should stop but you just can't kelp yourself. (TP +20, 40% silence)</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -14398,11 +13978,7 @@
           <t>You know you should stop but you just can't kelp yourself (+20 TP, 40% Silence).</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -14422,7 +13998,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Sandfish simmered in sugar and soy sauce.</t>
+          <t>Sandfish simmered in sugar and soy sauce. (TP +30, 60% silence)</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -14436,11 +14012,7 @@
           <t>Sandfish simmered in sugar and soy sauce (+30 TP, 60% Silence).</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -14460,7 +14032,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>If you get served this without a warning, you're the butt of a joke.</t>
+          <t>Served without a warning, you're the butt of a joke. (TP +40, 60% silence)</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -14477,7 +14049,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -14499,7 +14071,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Bad looks and worse texture but weirdly addictive.</t>
+          <t>Bad looks and worse texture but weirdly addictive. (TP +50, 60% silence)</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -14513,11 +14085,7 @@
           <t>Bad looks and worse texture but weirdly addictive (+50 TP, 60% Silence).</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -14537,7 +14105,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Flatten an octopus and this is what you get. There's plenty to go around.</t>
+          <t>A flattened octopus. Plenty to go around. (party HP +160, 20% party magic DEF up)</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -14554,7 +14122,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -14576,7 +14144,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Rice with big ol' chunks of tentacle.</t>
+          <t>Rice with big ol' chunks of tentacle. (HP +400, 50% ATK up)</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
@@ -14590,11 +14158,7 @@
           <t>Rice with big ol' chunks of tentacle (+50% ATK).</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -14784,7 +14348,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Spiral sweet soaked in sugary syrup.</t>
+          <t>Spiral sweet soaked in sugary syrup. (TP +98, 50% accuracy up)</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -14798,11 +14362,7 @@
           <t>Spiral sweet soaked in sugary syrup (+98 TP).</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -15060,7 +14620,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Red bean bun baked with fine gold wheat. Diabetics should avoid it.</t>
+          <t>Red bean bun of fine gold wheat. Diabetics should avoid it. (HP +400, 80% Defender)</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
@@ -15076,7 +14636,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -15170,7 +14730,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Potato chips that'll blow your top.</t>
+          <t>Potato chips that'll blow your top. (40% ATK up, 70% stun)</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
@@ -15184,11 +14744,7 @@
           <t>Potato chips that'll blow your top (+40% ATK).</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -15310,7 +14866,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>A candy so sweet it will cause your brain to melt.</t>
+          <t>A candy so sweet it will cause your brain to melt. (HP +300, 30% silence)</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
@@ -15324,11 +14880,7 @@
           <t>A candy so sweet it will cause your brain to melt (+300 HP, 30% Silence).</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -15348,7 +14900,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>So spicy it makes your eyes hurt.</t>
+          <t>So spicy it makes your eyes hurt. (25% paralysis)</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
@@ -15362,11 +14914,7 @@
           <t>So spicy it makes your eyes hurt (25% Paralysis).</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -15386,7 +14934,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Eat it and you'll sweat from every orifice you've got.</t>
+          <t>Eat it and you'll sweat from every orifice you've got. (HP +50, cures freeze)</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
@@ -15400,11 +14948,7 @@
           <t>Eat it and you'll sweat from every orifice you've got (+50 HP, Cure Freeze).</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -15424,7 +14968,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>First-timers will lose consciousness due to the spice.</t>
+          <t>First-timers will lose consciousness due to the spice. (HP/TP +75, 15% paralysis)</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
@@ -15438,11 +14982,7 @@
           <t>First-timers will lose consciousness due to the spice (+75 HP/TP, 15% Paralysis).</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -15462,7 +15002,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>So spicy, it's out of this world. Just one phone call and they'll deliver.</t>
+          <t>So spicy it's out of this world. One call and they deliver. (HP +400, 80% silence)</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
@@ -15479,7 +15019,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15317,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>The mushroom formerly known as matsutake. They're... fine.</t>
+          <t>The mushroom formerly known as matsutake. They're... fine. (25% Divine Shield)</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -15791,11 +15331,7 @@
           <t>The mushroom formerly known as matsutake. They're... fine.</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -15815,7 +15351,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Yellow with red spots. Eat it, and you might get bigger.</t>
+          <t>Yellow with red spots. Eat it, and you might get bigger. (50% max HP up)</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -15829,11 +15365,7 @@
           <t>Yellow with red spots. Eat it, and you might get bigger.</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -15921,7 +15453,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Refrigerated agar with added beans and fruits.</t>
+          <t>Refrigerated agar with added beans and fruits. (TP +160, cures freeze)</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
@@ -15935,11 +15467,7 @@
           <t>Refrigerated agar with added beans and fruits (+160 TP, Cure Freeze).</t>
         </is>
       </c>
-      <c r="H430" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -16095,7 +15623,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>This sticky pudding is speckled with raisins. It's just pudding. Honestly.</t>
+          <t>Sticky pudding with raisins. Just pudding. Honestly. (HP +100, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -16112,7 +15640,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>no room for (HP +100, cures 1 ailment): 101 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -16168,7 +15696,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Ol' reliable. You can't go wrong with bean paste.</t>
+          <t>Ol' reliable. You can't go wrong with bean paste. (TP +125, 65% Insurance)</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
@@ -16182,11 +15710,7 @@
           <t>Ol' reliable. You can't go wrong with bean paste (+125 TP).</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -16206,7 +15730,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Soup made wholly out of leftovers. Liver and let die!</t>
+          <t>Soup made of leftovers. Liver and let die! (party TP +10, 20% party cure-all)</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -16222,7 +15746,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -16244,7 +15768,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>The unagi's not necessarily good, but the sauce is.</t>
+          <t>The unagi's not always good, but the sauce is. (party TP +25, 40% party cure-all)</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -16260,7 +15784,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -16282,7 +15806,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Dead eels on rice. It's terrible, you wouldn't want any.</t>
+          <t>Dead eels on rice. You wouldn't want any. (party TP +50, 60% party cure-all)</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -16298,7 +15822,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -16320,7 +15844,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Sushi roll containing sticky, smelly, fermented soybeans. Yum...?</t>
+          <t>Sushi roll of sticky, smelly, fermented soybeans. Yum...? (HP/TP +30, 50% silence)</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -16337,7 +15861,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -16359,7 +15883,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>You must be mindful of your surroundings when eating this.</t>
+          <t>You must be mindful of your surroundings when eating this. (HP/TP +60, 60% silence)</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -16373,11 +15897,7 @@
           <t>You must be mindful of your surroundings when eating this (+60 HP/TP, 60% Silence).</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -16397,7 +15917,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Extremely smelly... but somehow delicious.</t>
+          <t>Extremely smelly... but somehow delicious. (HP/TP +100, 70% silence)</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
@@ -16411,11 +15931,7 @@
           <t>Extremely smelly... but somehow delicious (+100 HP/TP, 70% Silence).</t>
         </is>
       </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -16435,7 +15951,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Silky-smooth little fish, rich in calcium.</t>
+          <t>Silky-smooth little fish, rich in calcium. (HP +40, 30% DEF up)</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
@@ -16449,11 +15965,7 @@
           <t>Silky-smooth little fish, rich in calcium (+30% DEF).</t>
         </is>
       </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -16473,7 +15985,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Somewhat grotesque when the fish has the face of a man.</t>
+          <t>Somewhat grotesque when the fish has the face of a man. (HP +100, 40% stun)</t>
         </is>
       </c>
       <c r="E445" t="inlineStr"/>
@@ -16487,11 +15999,7 @@
           <t>Somewhat grotesque when the fish has the face of a man (+100 HP, 40% Blind).</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -16511,7 +16019,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Well dried bonito flakes.</t>
+          <t>Well dried bonito flakes. (HP +120, 60% DEF up)</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
@@ -16525,11 +16033,7 @@
           <t>Well dried bonito flakes (+60% DEF).</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -16549,7 +16053,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Bonito so dry it's a blunt weapon. The world's hardest food.</t>
+          <t>Bonito so dry it's a blunt weapon. The world's hardest food. (HP +200, 80% DEF up)</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -16563,11 +16067,7 @@
           <t>Bonito so dry it's a blunt weapon. The world's hardest food (+80% DEF).</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -16655,7 +16155,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Bitter jelly allegedly good for the skin. Not so great for the tortoise.</t>
+          <t>Bitter jelly good for the skin. Not so great for the tortoise. (cures all ailments)</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -16672,7 +16172,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>no room for (cures all ailments): 93 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16194,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Genuine, honest, real turtle soup! Would I lie to you?</t>
+          <t>Genuine, real turtle soup! Would I lie to you? (cures all ailments, 40% max HP up)</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -16710,7 +16210,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -16732,7 +16232,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Made in an earthenware pot at high temperature. Delicious but steep.</t>
+          <t>Made in an earthenware pot. Delicious but steep. (cures all ailments, TP +125)</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
@@ -16749,7 +16249,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>no room for (cures all ailments, TP +125): 98 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16305,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Bento with only meat and rice. Get those veggies out of here!</t>
+          <t>Bento with only meat and rice. Get those veggies out of here! (HP +150, 50% ATK up)</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -16819,11 +16319,7 @@
           <t>Bento with only meat and rice. Get those veggies out of here! (+50% ATK).</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -16843,7 +16339,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Sukiyaki bento with super luxurious wagyu included.</t>
+          <t>Sukiyaki bento with super luxurious wagyu included. (HP +200, 70% ATK up)</t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
@@ -16857,11 +16353,7 @@
           <t>Sukiyaki bento with super luxurious wagyu included (+70% ATK).</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -16881,7 +16373,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Steak bento so delicious it'll make you dizzy.</t>
+          <t>Steak bento so delicious it'll make you dizzy. (HP +400, 90% ATK up)</t>
         </is>
       </c>
       <c r="E456" t="inlineStr"/>
@@ -16895,11 +16387,7 @@
           <t>Steak bento so delicious it'll make you dizzy (+90% ATK).</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -16919,7 +16407,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>A liquid formed from the drool of the elusive nuko.</t>
+          <t>A liquid formed from the drool of the elusive nuko. (20% poison)</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
@@ -16933,11 +16421,7 @@
           <t>A liquid formed from the drool of the elusive nuko (60% Poison).</t>
         </is>
       </c>
-      <c r="H457" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -17025,7 +16509,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Don't drink too much if you like your brain cells.</t>
+          <t>Don't drink too much if you like your brain cells. (TP +75, 20% instakill)</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -17039,11 +16523,7 @@
           <t>Don't drink too much if you like your brain cells (+75 TP).</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -17097,7 +16577,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Cheap and delicious. Sometimes filled with strawberry or pudding.</t>
+          <t>Cheap and delicious. Sometimes filled with pudding. (HP +135, cancels Shadow Sew)</t>
         </is>
       </c>
       <c r="E462" t="inlineStr"/>
@@ -17114,7 +16594,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>no room for (HP +135, cancels Shadow Sew): 95 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -17272,7 +16752,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>If you don't handle it with care, the cream will spurt all over you.</t>
+          <t>Handle it with care, or the cream will spurt all over you. (HP +200, 25% DEF up)</t>
         </is>
       </c>
       <c r="E467" t="inlineStr"/>
@@ -17288,7 +16768,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -17344,7 +16824,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Triple-stack of pancakes smothered in sticky maple syrup.</t>
+          <t>Triple-stack of pancakes in sticky maple syrup. (party HP +180, 25% party ATK up)</t>
         </is>
       </c>
       <c r="E469" t="inlineStr"/>
@@ -17360,7 +16840,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -17382,7 +16862,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>It means white mountain. And yet, yellow cake. Y u do dis?</t>
+          <t>It means white mountain. And yet, yellow cake. Y u do dis? (HP +300, 25% accuracy up)</t>
         </is>
       </c>
       <c r="E470" t="inlineStr"/>
@@ -17396,11 +16876,7 @@
           <t>It means white mountain. And yet, yellow cake. Y u do dis? (+300 HP).</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -17420,7 +16896,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Sweetness and justice are synonymous.</t>
+          <t>Sweetness and justice are synonymous. (HP +400, 25% evasion up)</t>
         </is>
       </c>
       <c r="E471" t="inlineStr"/>
@@ -17434,11 +16910,7 @@
           <t>Sweetness and justice are synonymous (+25% EVA).</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -17458,7 +16930,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>A multi-layered, doughy pie cake.</t>
+          <t>A multi-layered, doughy pie cake. (party HP +300, 25% party magic DEF up)</t>
         </is>
       </c>
       <c r="E472" t="inlineStr"/>
@@ -17472,11 +16944,7 @@
           <t>A multi-layered, doughy pie cake (Party: +300 HP).</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -17496,7 +16964,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>A luxury item perfect for souvenirs or gift exchanges.</t>
+          <t>A luxury item perfect for souvenirs or gifts. (party TP +200, 40% party DEF up)</t>
         </is>
       </c>
       <c r="E473" t="inlineStr"/>
@@ -17512,7 +16980,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17036,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Liquor brewed from millet. Its mature flavor can become a habit. (HP +125, sleep 40%)</t>
+          <t>Liquor brewed from millet. Its mature flavor can become a habit. (HP +125, 40% sleep)</t>
         </is>
       </c>
       <c r="E475" t="inlineStr"/>
@@ -17602,7 +17070,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>The mascot creature of this chocolate has yet to be identified by science.</t>
+          <t>Its mascot creature has yet to be identified by science. (HP +165, 20% stun)</t>
         </is>
       </c>
       <c r="E476" t="inlineStr"/>
@@ -17619,7 +17087,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17109,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Canned whale. Slowly vanishing from shelves.</t>
+          <t>Canned whale. Slowly vanishing from shelves. (HP +200, 25% Divine Shield)</t>
         </is>
       </c>
       <c r="E477" t="inlineStr"/>
@@ -17655,11 +17123,7 @@
           <t>Canned whale. Slowly vanishing from shelves (+200 HP).</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -17717,7 +17181,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Simple hotpot of whale and mizuna.</t>
+          <t>Simple hotpot of whale and mizuna. (party HP +400, 60% party DEF up)</t>
         </is>
       </c>
       <c r="E479" t="inlineStr"/>
@@ -17731,11 +17195,7 @@
           <t>Simple hotpot of whale and mizuna (Party: +400 HP).</t>
         </is>
       </c>
-      <c r="H479" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -17789,7 +17249,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Filled with meat and veggies! Very delicious.</t>
+          <t>Filled with meat and veggies! Very delicious. (HP +120, cures freeze)</t>
         </is>
       </c>
       <c r="E481" t="inlineStr"/>
@@ -17803,11 +17263,7 @@
           <t>Filled with meat and veggies! Very delicious (+120 HP, Cure Freeze).</t>
         </is>
       </c>
-      <c r="H481" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -17827,7 +17283,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Warms your body to the core on a cold day.</t>
+          <t>Warms your body to the core on a cold day. (HP +180, cures freeze)</t>
         </is>
       </c>
       <c r="E482" t="inlineStr"/>
@@ -17841,11 +17297,7 @@
           <t>Warms your body to the core on a cold day (+180 HP, Cure Freeze).</t>
         </is>
       </c>
-      <c r="H482" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -17865,7 +17317,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Jelly made with copious amounts of slime.</t>
+          <t>Jelly made with copious amounts of slime. (10 fixed damage, 10% slow)</t>
         </is>
       </c>
       <c r="E483" t="inlineStr"/>
@@ -17879,11 +17331,7 @@
           <t>Jelly made with copious amounts of slime (Speed DOWN -20%.).</t>
         </is>
       </c>
-      <c r="H483" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -17903,7 +17351,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Made from only the gloopiest cuts of the slime.</t>
+          <t>Made from only the gloopiest cuts of the slime. (30 fixed damage, 5% slow)</t>
         </is>
       </c>
       <c r="E484" t="inlineStr"/>
@@ -17917,11 +17365,7 @@
           <t>Made from only the gloopiest cuts of the slime (Speed DOWN -10%.).</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -17941,7 +17385,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>So chewy it'll tire out your jaw.</t>
+          <t>So chewy it'll tire out your jaw. (50 fixed damage, 20% slow)</t>
         </is>
       </c>
       <c r="E485" t="inlineStr"/>
@@ -17955,11 +17399,7 @@
           <t>So chewy it'll tire out your jaw (Speed DOWN -40%.).</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -17979,7 +17419,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Bavarian cream filled with tons of slime. Appetizing, isn't it?</t>
+          <t>Bavarian cream full of slime. Appetizing? (party 50 fixed damage, 75% strips buffs)</t>
         </is>
       </c>
       <c r="E486" t="inlineStr"/>
@@ -17995,7 +17435,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -18017,7 +17457,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Spray that turns you into a super sadist for a few minutes.</t>
+          <t>Spray that turns you into a super sadist for a few minutes. (50% Berserk)</t>
         </is>
       </c>
       <c r="E487" t="inlineStr"/>
@@ -18031,11 +17471,7 @@
           <t>Spray that turns you into a super sadist for a few minutes (+50% ATK).</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -18055,7 +17491,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>The feeling of being foreign. You're a stranger in a strange land.</t>
+          <t>Feeling foreign. You're a stranger in a strange land. (75% Berserk, 75% stun)</t>
         </is>
       </c>
       <c r="E488" t="inlineStr"/>
@@ -18071,7 +17507,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -18093,7 +17529,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Can stuffed with dragon meat. Rare and expensive but a little smelly.</t>
+          <t>Canned dragon meat. Rare, expensive, a little smelly. (TP +150, cures all ailments)</t>
         </is>
       </c>
       <c r="E489" t="inlineStr"/>
@@ -18110,7 +17546,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>no room for (TP +150, cures all ailments): 99 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -18132,7 +17568,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>No alcohol until you're 21! (HP +75, sleep 30%)</t>
+          <t>No alcohol until you're 21! (HP +75, 30% sleep)</t>
         </is>
       </c>
       <c r="E490" t="inlineStr"/>
@@ -18166,7 +17602,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Some have never tried this sake, but none have tried it only once.</t>
+          <t>Some never tried this sake, but none tried it only once. (HP +150, 15% sleep)</t>
         </is>
       </c>
       <c r="E491" t="inlineStr"/>
@@ -18183,7 +17619,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>no room for (HP +150, sleep 15%): 87 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -18205,7 +17641,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Powerful sake that intoxicates even heavy drinkers. Super harsh flavor.</t>
+          <t>Sake that intoxicates even heavy drinkers. Super harsh. (HP +300, 20% stun)</t>
         </is>
       </c>
       <c r="E492" t="inlineStr"/>
@@ -18222,7 +17658,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -18244,7 +17680,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Port wine carefully aged for over a hundred years. (HP +400, sleep 20%)</t>
+          <t>Port wine carefully aged for over a hundred years. (HP +400, 20% sleep)</t>
         </is>
       </c>
       <c r="E493" t="inlineStr"/>
@@ -18346,7 +17782,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Dish made by shoving waterfowls into a dragon corpse.</t>
+          <t>Dish made by shoving waterfowls into a dragon corpse. (HP/TP +200, 50% paralysis)</t>
         </is>
       </c>
       <c r="E496" t="inlineStr"/>
@@ -18360,11 +17796,7 @@
           <t>Dish made by shoving waterfowls into a dragon corpse (+200 HP/TP, 50% Paralysis).</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -18384,7 +17816,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>A huge, hard egg. It's unbreakable.</t>
+          <t>A huge, hard egg. It's unbreakable. (HP/TP +260, 25% evasion up)</t>
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
@@ -18398,11 +17830,7 @@
           <t>A huge, hard egg. It's unbreakable (+25% EVA).</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -18456,7 +17884,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Cloying, syrupy drink.</t>
+          <t>Cloying, syrupy drink. (party HP/TP +200, restores stats)</t>
         </is>
       </c>
       <c r="E499" t="inlineStr"/>
@@ -18470,11 +17898,7 @@
           <t>Cloying, syrupy drink (Party: +250 HP/TP, Clear Debuffs).</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -18494,7 +17918,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Meat so tender that it melts at the touch.</t>
+          <t>Meat so tender that it melts at the touch. (25% poison)</t>
         </is>
       </c>
       <c r="E500" t="inlineStr"/>
@@ -18508,11 +17932,7 @@
           <t>Meat so tender that it melts at the touch (50% Poison).</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -18532,7 +17952,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Meat is most delicious when it's almost rotten... or so they say.</t>
+          <t>Meat is most delicious when it's almost rotten... or so they say. (35% poison)</t>
         </is>
       </c>
       <c r="E501" t="inlineStr"/>
@@ -18546,11 +17966,7 @@
           <t>Meat is most delicious when it's almost rotten... or so they say (70% Poison).</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -18570,7 +17986,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Primitive meat that shines suspiciously. Basically steroids in meat form.</t>
+          <t>Meat that shines suspiciously. Steroids in meat form. (50% poison, 40% paralysis)</t>
         </is>
       </c>
       <c r="E502" t="inlineStr"/>
@@ -18587,7 +18003,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -18779,7 +18195,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Konpeito as big as your fist.</t>
+          <t>Konpeito as big as your fist. (party TP +400, 50% 2 clones)</t>
         </is>
       </c>
       <c r="E508" t="inlineStr"/>
@@ -18793,11 +18209,7 @@
           <t>Konpeito as big as your fist (Party: +400 TP).</t>
         </is>
       </c>
-      <c r="H508" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -18817,7 +18229,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Beverage squeezed out of an apple creature's insides.</t>
+          <t>Beverage squeezed out of an apple creature's insides. (HP/TP +100, 40% poison)</t>
         </is>
       </c>
       <c r="E509" t="inlineStr"/>
@@ -18831,11 +18243,7 @@
           <t>Beverage squeezed out of an apple creature's insides (+100 HP/TP, 40% Poison).</t>
         </is>
       </c>
-      <c r="H509" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -18855,7 +18263,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>A candy with a whole appler trapped inside.</t>
+          <t>A candy with a whole appler trapped inside. (HP/TP +200, 80% poison)</t>
         </is>
       </c>
       <c r="E510" t="inlineStr"/>
@@ -18869,11 +18277,7 @@
           <t>A candy with a whole appler trapped inside (+200 HP/TP, 80% Poison).</t>
         </is>
       </c>
-      <c r="H510" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -18893,7 +18297,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Beverage squeezed out of a melon creature's insides.</t>
+          <t>Beverage squeezed out of a melon creature's insides. (HP/TP +100, 90% paralysis)</t>
         </is>
       </c>
       <c r="E511" t="inlineStr"/>
@@ -18907,11 +18311,7 @@
           <t>Beverage squeezed out of a melon creature's insides (+100 HP/TP, 90% Paralysis).</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -18931,7 +18331,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Unrelated to that anime character who lets people eat her face.</t>
+          <t>Unrelated to the anime girl whose face gets eaten. (HP/TP +200, 80% paralysis)</t>
         </is>
       </c>
       <c r="E512" t="inlineStr"/>
@@ -18948,7 +18348,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -18970,7 +18370,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Beverage squeezed out of a banana creature's insides.</t>
+          <t>Beverage squeezed out of a banana creature's insides. (HP/TP +100, 40% silence)</t>
         </is>
       </c>
       <c r="E513" t="inlineStr"/>
@@ -18984,11 +18384,7 @@
           <t>Beverage squeezed out of a banana creature's insides (+100 HP/TP, 40% Silence).</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -19008,7 +18404,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>It's a big banana. Looks pretty sexy.</t>
+          <t>It's a big banana. Looks pretty sexy. (HP/TP +200, 80% silence)</t>
         </is>
       </c>
       <c r="E514" t="inlineStr"/>
@@ -19022,11 +18418,7 @@
           <t>It's a big banana. Looks pretty sexy (+200 HP/TP, 80% Silence).</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -19046,7 +18438,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>A Fairy Mandra that's badly wounded.</t>
+          <t>A Fairy Mandra that's badly wounded. (10% stun)</t>
         </is>
       </c>
       <c r="E515" t="inlineStr"/>
@@ -19060,11 +18452,7 @@
           <t>A Fairy Mandra that's badly wounded (10% Blind).</t>
         </is>
       </c>
-      <c r="H515" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -19152,7 +18540,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>The trefoil of a mandra, used as a graduation charm.</t>
+          <t>A mandra trefoil, used as a graduation charm. (party TP +150, 60% party magic DEF up)</t>
         </is>
       </c>
       <c r="E518" t="inlineStr"/>
@@ -19168,7 +18556,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -19190,7 +18578,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Made by grinding up mandras.</t>
+          <t>Made by grinding up mandras. (99% silence, 99% freeze)</t>
         </is>
       </c>
       <c r="E519" t="inlineStr"/>
@@ -19204,11 +18592,7 @@
           <t>Made by grinding up mandras (95% Silence, 95% Freeze).</t>
         </is>
       </c>
-      <c r="H519" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -19228,7 +18612,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>An Otherworld Mandra that's badly wounded.</t>
+          <t>An Otherworld Mandra that's badly wounded. (15% poison)</t>
         </is>
       </c>
       <c r="E520" t="inlineStr"/>
@@ -19242,11 +18626,7 @@
           <t>An Otherworld Mandra that's badly wounded (15% Poison).</t>
         </is>
       </c>
-      <c r="H520" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -19334,7 +18714,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Too much of it will cause severe hallucinations. Not the good kind.</t>
+          <t>Too much of it will cause severe hallucinations. Not the good kind. (80% Defender)</t>
         </is>
       </c>
       <c r="E523" t="inlineStr"/>
@@ -19348,11 +18728,7 @@
           <t>Too much of it will cause severe hallucinations. Not the good kind.</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -19372,7 +18748,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Freshly squeezed mandra juice. Nice and pulpy.</t>
+          <t>Fresh-squeezed mandra juice. Nice and pulpy. (party HP/TP +2000, 90% party cure-all)</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
@@ -19388,7 +18764,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -19410,7 +18786,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Said to bring good fortune. Does anyone actually believe that?</t>
+          <t>Said to bring good fortune. Does anyone actually believe that? (party HP/TP +1000)</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
@@ -19424,11 +18800,7 @@
           <t>Said to bring good fortune. Does anyone actually believe that? (Party: +1000 HP/TP).</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -19618,7 +18990,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Made in an attempt to achieve sake supremacy. To sake-cceed.</t>
+          <t>Made to achieve sake supremacy. To sake-cceed. (HP/TP +50, cures all ailments)</t>
         </is>
       </c>
       <c r="E531" t="inlineStr"/>
@@ -19635,7 +19007,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>no room for (HP/TP +50, cures all ailments): 92 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -19657,7 +19029,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>The denizens of the world above say these pair well with tea.</t>
+          <t>Denizens of the world above say these pair well with tea. (TP +1000, 90% Insurance)</t>
         </is>
       </c>
       <c r="E532" t="inlineStr"/>
@@ -19673,7 +19045,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19101,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Rice cake that crumbles from the outside as you eat it.</t>
+          <t>Rice cake that crumbles from the outside as you eat it. (TP +130, 75% Divine Shield)</t>
         </is>
       </c>
       <c r="E534" t="inlineStr"/>
@@ -19743,11 +19115,7 @@
           <t>Rice cake that crumbles from the outside as you eat it (+130 TP).</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -19767,7 +19135,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Precious, sweet-smelling beverage made of liquified mana crystals.</t>
+          <t>Sweet-smelling beverage of liquified mana crystals. (TP +999, cures all ailments)</t>
         </is>
       </c>
       <c r="E535" t="inlineStr"/>
@@ -19784,7 +19152,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>no room for (TP +999, cures all ailments): 96 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -19806,7 +19174,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Dangerous drink that lights a fire in your loins. Yowch! That's hot!</t>
+          <t>Drink that lights a fire in your loins. Yowch! Hot! (HP +5000, 99% max HP up)</t>
         </is>
       </c>
       <c r="E536" t="inlineStr"/>
@@ -19822,7 +19190,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -19878,7 +19246,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>The most treasured treasure of the Dragon Palace... cures Freeze.</t>
+          <t>The most treasured treasure of the Dragon Palace... cures Freeze. (cures freeze)</t>
         </is>
       </c>
       <c r="E538" t="inlineStr"/>
@@ -19892,11 +19260,7 @@
           <t>The most treasured treasure of the Dragon Palace... cures Freeze (Cure Freeze).</t>
         </is>
       </c>
-      <c r="H538" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -19916,7 +19280,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Tender green bud held by the former ruler of the world.</t>
+          <t>Tender green bud held by the former ruler of the world. (95% strips buffs)</t>
         </is>
       </c>
       <c r="E539" t="inlineStr"/>
@@ -19930,11 +19294,7 @@
           <t>Tender green bud held by the former ruler of the world.</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -20158,7 +19518,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>A precious book depicting powerful bonds between men.</t>
+          <t>A precious book depicting powerful bonds between men. (50% silence)</t>
         </is>
       </c>
       <c r="E546" t="inlineStr"/>
@@ -20172,11 +19532,7 @@
           <t>A precious book depicting powerful bonds between men (95% Silence).</t>
         </is>
       </c>
-      <c r="H546" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">

--- a/mod_project/data_tables/qol_item_text.xlsx
+++ b/mod_project/data_tables/qol_item_text.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Yakisoba noodle bread. Sells out very quickly. (HP/TP +20, cures 1 ailment)</t>
+          <t>Yakisoba noodle bread. Sells out fast. (HP/TP +20, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Premium steak sandwich, luxury sauce. Extra deluxe. (HP/TP +30, cures all ailments)</t>
+          <t>Steak sandwich, luxury sauce. Deluxe. (HP/TP +30, cures all ailments)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Spicy curry that would make even a Maharaja groan. (HP/TP +150, cures all ailments)</t>
+          <t>Curry to make a Maharaja groan. (HP/TP +150, cures all ailments)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Legendary food. Whoever eats it falls in love. (HP/TP +1000, cures all ailments)</t>
+          <t>Legendary. Eat it and fall in love. (HP/TP +1000, cures all ailments)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Revive a fallen ally. Considerably bitter aftertaste. (revives at 10% HP)</t>
+          <t>Revive a fallen ally. Very bitter aftertaste. (revives at 10% HP)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1109,7 +1109,11 @@
           <t>Revive a fallen ally. Considerably bitter aftertaste (Revive 30% HP).</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1368,7 +1372,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Highly nutritious, it heals HP and TP but is extremely bitter. (HP +50, TP +20)</t>
+          <t>Nutritious, heals HP and TP, but extremely bitter. (HP +50, TP +20)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1407,7 +1411,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tea with condensed bitterness. I hear it's an acquired taste... (HP +30, TP +40)</t>
+          <t>Condensed bitterness. An acquired taste, I hear... (HP +30, TP +40)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1421,7 +1425,11 @@
           <t>Tea with condensed bitterness. I hear it's an acquired taste.. (+30 HP, +40 TP).</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1441,7 +1449,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Beard's special bento. Balanced, big enough to share. (party HP +75, party TP +25)</t>
+          <t>Beard's special bento, made to share. (party HP +75, party TP +25)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1480,7 +1488,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Peggy's eggy milk pudding. It's said to be legendary. (TP +30, 20% sleep)</t>
+          <t>Peggy's eggy milk pudding. Said to be legendary. (TP +30, 20% sleep)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1494,7 +1502,11 @@
           <t>Peggy's eggy milk pudding. It's said to be legendary (+30 TP, 20% Sleep).</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1514,7 +1526,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Kumaya Mangetsudo's anpan. Low-calorie, but still delicious. (HP/TP +20, 15% sleep)</t>
+          <t>Kumaya Mangetsudo's low-calorie, tasty anpan. (HP/TP +20, 15% sleep)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1621,7 +1633,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mary Florina's rich milk collagen gel. (cures all ailments, restores stats)</t>
+          <t>Mary Florina's milk collagen gel. (cures all ailments, restores stats)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1733,7 +1745,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>An exciting new way to cheat death. Courtesy of the Peggy Company. (revives at 1% HP)</t>
+          <t>A new way to cheat death, by the Peggy Company. (revives at 1% HP)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1747,7 +1759,11 @@
           <t>An exciting new way to cheat death. Courtesy of the Peggy Company (Revive 100% HP).</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1767,7 +1783,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A cure for anything, and plenty of it. (cures all ailments, restores stats)</t>
+          <t>A cure for anything, and plenty. (cures all ailments, restores stats)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1951,7 +1967,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>An aged icon that's heard prayers year after year. (cures all ailments)</t>
+          <t>An aged icon that's heard years of prayers. (cures all ailments)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1965,7 +1981,11 @@
           <t>An aged icon that's heard prayers year after year (Cure All Ailments).</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1985,7 +2005,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A gun shell left by one who gave up their life for revolution. (restores stats)</t>
+          <t>A shell left by one who died for the revolution. (restores stats)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1999,7 +2019,11 @@
           <t>A gun shell left by one who gave up their life for revolution (Clear Debuffs).</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2019,7 +2043,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A splendidly well-made futuristic metal. It's a bit lumpy. Weird. (150 steps)</t>
+          <t>A well-made futuristic metal. A bit lumpy. Weird. (150 steps)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2033,7 +2057,11 @@
           <t>A splendidly well-made futuristic metal. It's a bit lumpy. Weird (Light 30 steps).</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2053,7 +2081,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>It scrambles your brain, and then you die. No coming back from that. (10% instakill)</t>
+          <t>It scrambles your brain, then you die. No coming back. (10% instakill)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2067,7 +2095,11 @@
           <t>It scrambles your brain, and then you die. No coming back from that (25% Death).</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2087,7 +2119,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Inscribed with impressive wish-granting runes. (80% Divine Shield, 80% Insurance)</t>
+          <t>Wish-granting runes. Impressive. (80% Divine Shield, 80% Insurance)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2101,7 +2133,11 @@
           <t>Inscribed with impressive wish-granting runes.</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2155,7 +2191,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Rock-hard cracker. Snack and emergency ration! (HP/TP +75, cancels Shadow Sew)</t>
+          <t>Rock-hard snack and emergency food! (HP/TP +75, cancels Shadow Sew)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2304,7 +2340,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Wind that brought spring to the underworld. (80% party ATK up, 80% party DEF up)</t>
+          <t>Spring wind of the underworld. (80% party ATK up, 80% party DEF up)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2584,7 +2620,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>When I peeked in, something peeked back... There's someone in there! (6% instakill)</t>
+          <t>I peeked in, it peeked back... Someone's in there! (6% instakill)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2598,7 +2634,11 @@
           <t>When I peeked in, something peeked back... There's someone in there! (25% Death).</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2656,7 +2696,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Might be usable in traditional medicine... if anything. (cancels Shadow Sew)</t>
+          <t>Maybe usable in traditional medicine... maybe. (cancels Shadow Sew)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2670,7 +2710,11 @@
           <t>Might be usable in traditional medicine... if anything (Cure Shadow Sew &amp; Bind).</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2860,7 +2904,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Whatever's under the breading, it's good and fried. (HP/TP +175, 75% Berserk)</t>
+          <t>Whatever's in the breading, it's good fried. (HP/TP +175, 75% Berserk)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3174,7 +3218,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Might's not all that makes right. Money does the trick too. (cures all ailments)</t>
+          <t>Might's not all that makes right. Money does too. (cures all ailments)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3188,7 +3232,11 @@
           <t>Might's not all that makes right. Money does the trick too (Cure All Ailments).</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3208,7 +3256,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>I must immediately depart on a long, long journey. Don't look for me. (25% silence)</t>
+          <t>I must leave on a long, long journey. Don't look for me. (25% silence)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3222,7 +3270,11 @@
           <t>I must immediately depart on a long, long journey. Don't look for me (50% Silence).</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3280,7 +3332,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>A red feather you receive after donating to a fundraiser. (TP +150, 75% Berserk)</t>
+          <t>A red feather you get for donating to a cause. (TP +150, 75% Berserk)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3294,7 +3346,11 @@
           <t>A red feather you receive after donating to a fundraiser (+75% ATK).</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3417,7 +3473,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Down came the rain, but this web did not get washed out. (leaves the dungeon)</t>
+          <t>The rain came down, but this web stayed put. (leaves the dungeon)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3431,7 +3487,11 @@
           <t>Down came the rain, but this web did not get washed out (Escape Dungeon).</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3451,7 +3511,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>One prick with this needle would be disastrous. Handle with care. (20% poison)</t>
+          <t>One prick would be disastrous. Handle with care. (20% poison)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3465,7 +3525,11 @@
           <t>One prick with this needle would be disastrous. Handle with care (40% Poison).</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3485,7 +3549,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>A mirror that reveals the truth... You might not want to look. (15% stun)</t>
+          <t>A mirror that shows the truth... You may not want to look. (15% stun)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3499,7 +3563,11 @@
           <t>A mirror that reveals the truth... You might not want to look (30% Blind).</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3799,7 +3867,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Clay used for handicraft in the heavens. Heh. They soil themselves. (10% 2 clones)</t>
+          <t>Clay of the heavens. Heh. They soil themselves. (10% 2 clones)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3813,7 +3881,11 @@
           <t>Clay used for handicraft in the heavens. Heh. They soil themselves.</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3833,7 +3905,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Vial of mysterious holy water. Tiny waves ripple at the top. (cures 1 ailment)</t>
+          <t>Mysterious holy water. Tiny waves ripple on top. (cures 1 ailment)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3872,7 +3944,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fried up in an iron pan. A steal at 3 million lira! (HP +50, 20% ATK up)</t>
+          <t>Pan-fried. A steal at 3 million lira! (HP +50, 20% ATK up)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3886,7 +3958,11 @@
           <t>Fried up in an iron pan. A steal at 3 million lira! (+20% ATK).</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3906,7 +3982,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>There's no wind blowing, yet you can hear its sound. It cries Mary. (15% silence)</t>
+          <t>No wind blows, yet you hear its sound. It cries Mary. (15% silence)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3920,7 +3996,11 @@
           <t>There's no wind blowing, yet you can hear its sound. It cries Mary (30% Silence).</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4012,7 +4092,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Just one drop will refresh constantly overworked eyes. (80% accuracy up)</t>
+          <t>One drop refreshes constantly overworked eyes. (80% accuracy up)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4026,7 +4106,11 @@
           <t>Just one drop will refresh constantly overworked eyes (Accuracy +80%.).</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4080,7 +4164,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Blowing or splashing water won't put out this fire. We didn't start it. (75 steps)</t>
+          <t>Blowing or water won't put it out. We didn't start it. (75 steps)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4095,7 +4179,11 @@
 (Light 15 steps)</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4187,7 +4275,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>The fruit, sadly, not the special event. Sweet and packed with energy. (TP +24)</t>
+          <t>The fruit, sadly, not the event. Sweet, packed with energy. (TP +24)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -4201,7 +4289,11 @@
           <t>The fruit, sadly, not the special event. Sweet and packed with energy (+24 TP).</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4221,7 +4313,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>If this waits back at base, someone's about to die. (TP +40, 30% instakill)</t>
+          <t>If it waits at base, someone's about to die. (TP +40, 30% instakill)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4259,7 +4351,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>A pastry for the prosperous. Crumbles on your tongue. (party HP +100, party TP +40)</t>
+          <t>A pastry for the prosperous. Crumbly. (party HP +100, party TP +40)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -4273,7 +4365,11 @@
           <t>A pastry for the prosperous. Crumbles on your tongue (Party: +100 HP, +40 TP).</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4811,7 +4907,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>A skull from a secret rite. Grants wishes. (60% party ATK up, 30% party magic DEF up)</t>
+          <t>Rite skull. Grants wishes. (60% party ATK up, 30% party magic DEF up)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4883,7 +4979,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>It makes a nice crunching sound when you bite into it. (revives at 35% HP)</t>
+          <t>Makes a nice crunch when you bite into it. (revives at 35% HP)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -4897,7 +4993,11 @@
           <t>It makes a nice crunching sound when you bite into it (Revive 35% HP).</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4917,7 +5017,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>A branch only some may pray to. It's twig-sclusive. (cures all ailments)</t>
+          <t>A branch only some may pray to. Twig-sclusive. (cures all ailments)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4990,7 +5090,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sandals that are no longer of any use. Might as well toss 'em. (15% evasion up)</t>
+          <t>Useless sandals. Might as well toss 'em. (15% evasion up)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5004,7 +5104,11 @@
           <t>Sandals that are no longer of any use. Might as well toss 'em (+15% EVA).</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5168,7 +5272,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Do YOU ever ruin your good cleaver on bone? Finally, there's help! (50% ATK up)</t>
+          <t>Ruined your good cleaver on bone? Finally, there's help! (50% ATK up)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5182,7 +5286,11 @@
           <t>Do YOU ever ruin your good cleaver on bone? Finally, there's help! (+50% ATK).</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5347,7 +5455,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>It might take... one more hit. Hit it baby one more time. (30 fixed damage)</t>
+          <t>One more hit... Hit it baby one more time. (30 fixed damage)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5385,7 +5493,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Do the goggles switch her personality, or just add confidence...? (50% max HP up)</t>
+          <t>Do they switch her personality, or add confidence...? (50% max HP up)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5563,7 +5671,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Eat this and you may die on the spot... or not at all. (90% instakill, TP +999)</t>
+          <t>Eat it and die on the spot... or never. (90% instakill, TP +999)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -5577,7 +5685,11 @@
           <t>Eat this and you may die on the spot... or not at all (+999 TP).</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5937,7 +6049,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Rice-based liquor aged for more than three years. (TP +50, 50% Berserk)</t>
+          <t>Rice liquor aged for more than three years. (TP +50, 50% Berserk)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5951,7 +6063,11 @@
           <t>Rice-based liquor aged for more than three years (+50% ATK).</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6191,7 +6307,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Oil you can rub on a wound in place of salve. If you want. (HP +60, 20% evasion up)</t>
+          <t>Oil for wounds instead of salve. If you want. (HP +60, 20% evasion up)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6205,7 +6321,11 @@
           <t>Oil you can rub on a wound in place of salve. If you want (+20% EVA).</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6684,7 +6804,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>You were forced to buy it at 5x the market price. I could cry. (90% sleep)</t>
+          <t>You were forced to buy it at 5x the price. I could cry. (90% sleep)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -6698,7 +6818,11 @@
           <t>You were forced to buy it at 5x the market price. I could cry (90% Sleep).</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6752,7 +6876,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>It'll send you to another world with just one sip (it's poison). (30% instakill)</t>
+          <t>One sip sends you to another world (it's poison). (30% instakill)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -6927,7 +7051,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>It says it's lucky. You can't believe everything you read, now can you? (15% silence)</t>
+          <t>It says it's lucky. Can't believe all you read, can you? (15% silence)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -6942,7 +7066,11 @@
 (30% Silence)</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6962,7 +7090,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>A letter that simply says: You are my fire. My one desire. (50% accuracy up)</t>
+          <t>It simply says: You are my fire. My one desire. (50% accuracy up)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -6976,7 +7104,11 @@
           <t>A letter that simply says: You are my fire. My one desire (Accuracy +50%.).</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6996,7 +7128,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>The prompt asks, who's your personal hero? I wrote, 'Me.' (80% Berserk)</t>
+          <t>Prompt: who's your personal hero? I wrote, 'Me.' (80% Berserk)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7010,7 +7142,11 @@
           <t>The prompt asks, who's your personal hero? I wrote, 'Me.' (+80% ATK).</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7030,7 +7166,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Tiger scroll filled with innermost secrets of martial arts. (30% ATK up)</t>
+          <t>Tiger scroll of the innermost secrets of martial arts. (30% ATK up)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7044,7 +7180,11 @@
           <t>Tiger scroll filled with innermost secrets of martial arts (+30% ATK).</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7204,7 +7344,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Holy river water that contains all sorts of extracts. Extracts... (TP +100, 75% stun)</t>
+          <t>Holy river water full of extracts. Extracts... (TP +100, 75% stun)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7219,7 +7359,11 @@
 (+100 TP, 75% Blind)</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7595,7 +7739,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Good for massages and hair care and so on. (cancels Shadow Sew, restores stats)</t>
+          <t>For massages, hair care, etc. (cancels Shadow Sew, restores stats)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -7609,7 +7753,11 @@
           <t>Good for massages and hair care and so on (Cure Shadow Sew).</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7731,7 +7879,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>An origami crane made with an exceedingly high number of folds. (60% party cure-all)</t>
+          <t>An origami crane with a great many folds. (60% party cure-all)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7745,7 +7893,11 @@
           <t>An origami crane made with an exceedingly high number of folds.</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7905,7 +8057,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Dangerous box that shoots out needles when opened improperly. (110 fixed damage)</t>
+          <t>Shoots out needles when opened improperly. (110 fixed damage)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -7919,7 +8071,11 @@
           <t>Dangerous box that shoots out needles when opened improperly.</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8007,7 +8163,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>A box full of contracts signed under threat of violence. (party 150 fixed damage)</t>
+          <t>Contracts signed under threat of violence. (party 150 fixed damage)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8021,7 +8177,11 @@
           <t>A box full of contracts signed under threat of violence.</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8109,7 +8269,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>A sword with a bamboo grip. For some reason, the grip... reeks. (35% stun)</t>
+          <t>A sword with a bamboo grip. Somehow the grip... reeks. (35% stun)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -8123,7 +8283,11 @@
           <t>A sword with a bamboo grip. For some reason, the grip... reeks (50% Blind).</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8211,7 +8375,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>A chain worn down by too much grinding. Kinda like my ex. (15 fixed damage)</t>
+          <t>Worn down by too much grinding. Kinda like my ex. (15 fixed damage)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -8351,7 +8515,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Despite its not having a head, you swear you've heard it giggle. (22% paralysis)</t>
+          <t>It has no head, yet you swear you've heard it giggle. (22% paralysis)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8365,7 +8529,11 @@
           <t>Despite its not having a head, you swear you've heard it giggle (35% Paralysis).</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8385,7 +8553,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Doll that changes to look just like you when you press its nose. (30% 1 clone)</t>
+          <t>Press its nose and it changes to look just like you. (30% 1 clone)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8399,7 +8567,11 @@
           <t>Doll that changes to look just like you when you press its nose.</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8555,7 +8727,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Every time you look at it, the people are in different poses. (15% silence)</t>
+          <t>Each time you look, the people are in different poses. (15% silence)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8569,7 +8741,11 @@
           <t>Every time you look at it, the people are in different poses (30% Silence).</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8793,7 +8969,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Not for use indoors. DEFINITELY not for use in a vehicle! (15% instakill)</t>
+          <t>Not for indoors. DEFINITELY not for use in a vehicle! (15% instakill)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -8807,7 +8983,11 @@
           <t>Not for use indoors. DEFINITELY not for use in a vehicle! (30% Death).</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8861,7 +9041,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Used for voodoo curses. Picture your enemy, and give it your all! (12% stun)</t>
+          <t>For voodoo curses. Picture your enemy, give it your all! (12% stun)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -8875,7 +9055,11 @@
           <t>Used for voodoo curses. Picture your enemy, and give it your all! (15% Blind).</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9149,7 +9333,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>A boxful of crackin' chocolate. The ladies love it! (party TP +75, restores stats)</t>
+          <t>Crackin' chocolate. Ladies love it! (party TP +75, restores stats)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9163,7 +9347,11 @@
           <t>A boxful of crackin' chocolate. The ladies love it! (Party: +75 TP, Clear Debuffs).</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9290,7 +9478,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Collect seven of these to summon a wish-granting dragon. (75% strips buffs)</t>
+          <t>Collect seven to summon a wish-granting dragon. (75% strips buffs)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9472,7 +9660,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>No-good apple that tempts women into strife. (party TP +100, party 500 fixed damage)</t>
+          <t>Tempts women into strife. (party TP +100, party 500 fixed damage)</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -9486,7 +9674,11 @@
           <t>No-good apple that tempts women into strife (Party: +100 TP).</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9540,7 +9732,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Huge bell that wards off evil when run. Awkward to carry around. (20% party DEF up)</t>
+          <t>Huge bell that wards off evil. Awkward to carry. (20% party DEF up)</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -9554,7 +9746,11 @@
           <t>Huge bell that wards off evil when run. Awkward to carry around.</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9574,7 +9770,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Water from a shrine that venerates a god of the land. (90% party cure-all)</t>
+          <t>Water from a shrine to a god of the land. (90% party cure-all)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -9588,7 +9784,11 @@
           <t>Water from a shrine that venerates a god of the land.</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9608,7 +9808,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Fruit goes in the dragon. This stuff comes out. Don't ask. (TP +50, 40% Berserk)</t>
+          <t>Fruit in the dragon, this out. Don't ask. (TP +50, 40% Berserk)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -9622,7 +9822,11 @@
           <t>Fruit goes in the dragon. This stuff comes out. Don't ask (+40% ATK).</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9642,7 +9846,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Press it for peace at any cost. There may be consequences... (90% strips buffs)</t>
+          <t>Peace at any cost. There may be consequences... (90% strips buffs)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -9714,7 +9918,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Tough enough to survive in a mouth full of dragon baby teeth. (40% sleep)</t>
+          <t>Tough enough for a mouth full of dragon baby teeth. (40% sleep)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -9728,7 +9932,11 @@
           <t>Tough enough to survive in a mouth full of dragon baby teeth (40% Sleep).</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9782,7 +9990,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>A strange substance that feels like nothingness when you touch it. (30% evasion up)</t>
+          <t>Strange substance. Touching it feels like nothing. (30% evasion up)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -9796,7 +10004,11 @@
           <t>A strange substance that feels like nothingness when you touch it (+30% EVA).</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9816,7 +10028,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Not for napping in. For hiding people taking naps. (HP +200, 90% sleep)</t>
+          <t>Not for napping in. For hiding nappers. (HP +200, 90% sleep)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -9830,7 +10042,11 @@
           <t>Not for napping in. For hiding people taking naps (+200 HP, 90% Sleep).</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9850,7 +10066,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>A mask that is just gold in color. Not all that glitters is gold. (12% paralysis)</t>
+          <t>Just gold in color. Not all that glitters is gold. (12% paralysis)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -9864,7 +10080,11 @@
           <t>A mask that is just gold in color. Not all that glitters is gold (15% Paralysis).</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10096,7 +10316,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! (15% instakill)</t>
+          <t>Dangerous! Do not touch! Deadly poison! (15% instakill)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -10110,7 +10330,11 @@
           <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! (40% Death).</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10130,7 +10354,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! #2 (20% instakill)</t>
+          <t>Dangerous! Do not touch! Deadly poison! #2 (20% instakill)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -10144,7 +10368,11 @@
           <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! #2 (80% Death).</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10164,7 +10392,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>A nice little rowboat. Cruise the river separating life and death. (30% instakill)</t>
+          <t>Nice rowboat. Cruise the river between life and death. (30% instakill)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -10178,7 +10406,11 @@
           <t>A nice little rowboat. Cruise the river separating life and death (95% Death).</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10198,7 +10430,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Sweet mint immortali-tea. More relaxing than relaxation itself. (TP +35, 25% sleep)</t>
+          <t>Sweet mint immortali-tea. Beyond relaxing. (TP +35, 25% sleep)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -10212,7 +10444,11 @@
           <t>Sweet mint immortali-tea. More relaxing than relaxation itself (+35 TP, 25% Sleep).</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10232,7 +10468,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>So much jealousy, it's visible to the naked eye. (30% paralysis, 30% sleep)</t>
+          <t>Jealousy so thick you can see it. (30% paralysis, 30% sleep)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -10246,7 +10482,11 @@
           <t>So much jealousy, it's visible to the naked eye (30% Paralysis, 30% Sleep).</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10436,7 +10676,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>You'll want to stay away from the water this came from. (25% paralysis)</t>
+          <t>Stay away from the water this came from. (25% paralysis)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -10450,7 +10690,11 @@
           <t>You'll want to stay away from the water this came from (50% Paralysis).</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10572,7 +10816,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Toss it in to any potluck stew to instantly increase the chaos. (50 fixed damage)</t>
+          <t>Toss it in any potluck stew for instant chaos. (50 fixed damage)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -10586,7 +10830,11 @@
           <t>Toss it in to any potluck stew to instantly increase the chaos.</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10674,7 +10922,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Disembodied wrist. Scurries all over the floor like a cleaning robot. (30% stun)</t>
+          <t>Disembodied wrist. Scurries about like a cleaning robot. (30% stun)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -10688,7 +10936,11 @@
           <t>Disembodied wrist. Scurries all over the floor like a cleaning robot (60% Blind).</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10924,7 +11176,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Peach-shaped bun eaten in times of celebration. (TP +36, cures 1 ailment)</t>
+          <t>Peach-shaped bun for celebrations. (TP +36, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -10938,7 +11190,11 @@
           <t>Peach-shaped bun eaten in times of celebration (+36 TP, Cure 1 Ailment).</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr"/>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10992,7 +11248,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Sweet persimmons preserved with sulfur. Tasty. (TP +15, cures 1 ailment)</t>
+          <t>Sweet sulfur-preserved persimmons. Tasty. (TP +15, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -11065,7 +11321,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Sushi in persimmon leaves. Don't eat the leaves. (party HP +130, cancels Shadow Sew)</t>
+          <t>Don't eat the persimmon leaves. (party HP +130, cancels Shadow Sew)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -11104,7 +11360,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Bear-meat citatap stew with pukusakina and veggies. (party HP +600, cures freeze)</t>
+          <t>Bear citatap stew with pukusakina. (party HP +600, cures freeze)</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -11279,7 +11535,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Hot fried chicken. Ask before you add lemon juice. (HP +240, restores stats)</t>
+          <t>Hot fried chicken. Ask before the lemon. (HP +240, restores stats)</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
@@ -11420,7 +11676,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>A slightly disgusting dish made with simmered bear paw. (TP +300, cures all ailments)</t>
+          <t>Slightly disgusting simmered bear paw. (TP +300, cures all ailments)</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
@@ -11434,7 +11690,11 @@
           <t>A slightly disgusting dish made with simmered bear paw (+300 TP, Cure All Ailments).</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11488,7 +11748,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Fried lamb meatballs with strong coriander scent. (TP +50, 100% evasion up)</t>
+          <t>Fried lamb meatballs. Smells of coriander. (TP +50, 100% evasion up)</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -11502,7 +11762,11 @@
           <t>Fried lamb meatballs with strong coriander scent (+100% EVA).</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11522,7 +11786,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Lunch set with bird meat and bear meat mixed together. (HP +300, cures 1 ailment)</t>
+          <t>Bird meat and bear meat, mixed together. (HP +300, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
@@ -11536,7 +11800,11 @@
           <t>Lunch set with bird meat and bear meat mixed together (+300 HP, Cure 1 Ailment).</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11556,7 +11824,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Brave penguins gave their lives to bring you fuel and soap. (80% evasion up)</t>
+          <t>Brave penguins died to bring you fuel and soap. (80% evasion up)</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -11570,7 +11838,11 @@
           <t>Brave penguins gave their lives to bring you fuel and soap (+80% EVA).</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11624,7 +11896,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Feel refreshed by the mint's cold, transcendent stimulation. (HP +200, cures sleep)</t>
+          <t>Cold, transcendent minty stimulation. (HP +200, cures sleep)</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
@@ -12070,7 +12342,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Sketchy in over seven ways. Get it? Like seven colors of the rainbow! (10% stun)</t>
+          <t>Sketchy in seven ways. Get it? Seven rainbow colors! (10% stun)</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
@@ -12084,7 +12356,11 @@
           <t>Sketchy in over seven ways. Get it? Like seven colors of the rainbow! (10% Blind).</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr"/>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12206,7 +12482,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Three aspects of the dumpling on one skewer. (party HP +180, 60% party ATK up)</t>
+          <t>Dumpling trinity on one skewer. (party HP +180, 60% party ATK up)</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
@@ -12316,7 +12592,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Raw meat cut fine and called a steak. Eat with caution. (HP/TP +2000, 95% 1 clone)</t>
+          <t>Raw meat called a steak. Eat with caution. (HP/TP +2000, 95% 1 clone)</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
@@ -12490,7 +12766,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Glutinous steamed rice dish with big pieces of chestnut. (HP +515, 30% 1 clone)</t>
+          <t>Steamed rice with big pieces of chestnut. (HP +515, 30% 1 clone)</t>
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
@@ -12504,7 +12780,11 @@
           <t>Glutinous steamed rice dish with big pieces of chestnut (+515 HP).</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr"/>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12558,7 +12838,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Seashell-shaped snack. Sally sells them by the seashore. (HP +135, 30% accuracy up)</t>
+          <t>Sally sells these seashells by the shore. (HP +135, 30% accuracy up)</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
@@ -12572,7 +12852,11 @@
           <t>Seashell-shaped snack. Sally sells them by the seashore (+135 HP).</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12592,7 +12876,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Syrup and dry fruit. A hard candy for hard men. (party HP +165, restores stats)</t>
+          <t>A hard candy for hard men. (party HP +165, restores stats)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
@@ -12631,7 +12915,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Cake with a figurine. Whoever finds it gets to be king. (party HP +250, party TP +25)</t>
+          <t>Find the figurine, be the king. (party HP +250, party TP +25)</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -12670,7 +12954,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Not everyone who eats muffins is in the mafia. The muffia? Hyuk hyuk. (HP/TP +30)</t>
+          <t>Not all who eat muffins are mafia. The muffia? Hyuk hyuk. (HP/TP +30)</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
@@ -12684,7 +12968,11 @@
           <t>Not everyone who eats muffins is in the mafia. The muffia? Hyuk hyuk (+30 HP/TP).</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12704,7 +12992,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Off the shelf or classy? Really not that different. (HP +50, 50% accuracy up)</t>
+          <t>Shelf or classy? Not that different. (HP +50, 50% accuracy up)</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
@@ -12742,7 +13030,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Party pastry of fruits, custard, and jelly. (party TP +115, 70% party magic DEF up)</t>
+          <t>Fruit, custard, jelly. Party! (party TP +115, 70% party magic DEF up)</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
@@ -12780,7 +13068,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>A cookie cut into a simple shape. Ooh, looks like a star! (party HP +55)</t>
+          <t>A simple-shaped cookie. Ooh, looks like a star! (party HP +55)</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
@@ -12794,7 +13082,11 @@
           <t>A cookie cut into a simple shape. Ooh, looks like a star! (Party: +55 HP).</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12814,7 +13106,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>A cookie cut into a somewhat complex shape. Ooh, looks like a cow! (party HP +160)</t>
+          <t>A somewhat complex cookie. Ooh, looks like a cow! (party HP +160)</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
@@ -12828,7 +13120,11 @@
           <t>A cookie cut into a somewhat complex shape. Ooh, looks like a cow! (Party: +160 HP).</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr"/>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12848,7 +13144,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>A cookie in a complex shape. Looks like Japan! (party HP +200, 60% party cure-all)</t>
+          <t>Cookie that looks like Japan! (party HP +200, 60% party cure-all)</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
@@ -12920,7 +13216,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Rice cracker covered in plenty of cayenne powder. (HP +120, 25% Defender)</t>
+          <t>Rice cracker covered in cayenne powder. (HP +120, 25% Defender)</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -12934,7 +13230,11 @@
           <t>Rice cracker covered in plenty of cayenne powder (+120 HP).</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr"/>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12954,7 +13254,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Just a cracker with tasty sauce, but dang, that's tasty. (HP +240, 50% Defender)</t>
+          <t>Just a cracker with sauce, but dang, tasty. (HP +240, 50% Defender)</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -12968,7 +13268,11 @@
           <t>Just a cracker with tasty sauce, but dang, that's tasty (+240 HP).</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13200,7 +13504,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Colorful candy that is kneaded with two sticks. (TP +31, cures 1 ailment)</t>
+          <t>Colorful candy kneaded with two sticks. (TP +31, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -13214,7 +13518,11 @@
           <t>Colorful candy that is kneaded with two sticks (+31 TP, Cure 1 Ailment).</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -13302,7 +13610,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Eat a long candy, live a long life. It's just math. (TP +150, 75% accuracy up)</t>
+          <t>Long candy, long life. It's just math. (TP +150, 75% accuracy up)</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -13316,7 +13624,11 @@
           <t>Eat a long candy, live a long life. It's just math (+150 TP).</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13336,7 +13648,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Rare, top-notch candy from the demon world. (party HP/TP +666, 95% party cure-all)</t>
+          <t>Top candy of the demon world. (party HP/TP +666, 95% party cure-all)</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -13408,7 +13720,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Sunny-side up egg on a patty. When to break the yolk...? (HP +300, 75% ATK up)</t>
+          <t>Egg on a patty. When to break the yolk...? (HP +300, 75% ATK up)</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -13422,7 +13734,11 @@
           <t>Sunny-side up egg on a patty. When to break the yolk...? (+75% ATK).</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr"/>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13624,7 +13940,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Sesame, white bean paste, and... red bean paste! (HP +400, 75% accuracy up)</t>
+          <t>Sesame, white bean and... red bean paste! (HP +400, 75% accuracy up)</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
@@ -13638,7 +13954,11 @@
           <t>Sesame, white bean paste, and... red bean paste! (+400 HP).</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr"/>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13692,7 +14012,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Bright macarons with an assortment of colors. (HP +150, 75% accuracy up)</t>
+          <t>Bright macarons in assorted colors. (HP +150, 75% accuracy up)</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -13706,7 +14026,11 @@
           <t>Bright macarons with an assortment of colors (+150 HP).</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13794,7 +14118,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Staple food on Planet Muscle. Go from ripped to jacked. (HP +300, 75% max HP up)</t>
+          <t>Planet Muscle staple. From ripped to jacked. (HP +300, 75% max HP up)</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -13808,7 +14132,11 @@
           <t>Staple food on Planet Muscle. Go from ripped to jacked (+300 HP).</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr"/>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13964,7 +14292,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>You know you should stop but you just can't kelp yourself. (TP +20, 40% silence)</t>
+          <t>You should stop but can't kelp yourself. (TP +20, 40% silence)</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -13978,7 +14306,11 @@
           <t>You know you should stop but you just can't kelp yourself (+20 TP, 40% Silence).</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -14032,7 +14364,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Served without a warning, you're the butt of a joke. (TP +40, 60% silence)</t>
+          <t>Served unwarned, you're the butt of a joke. (TP +40, 60% silence)</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -14071,7 +14403,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Bad looks and worse texture but weirdly addictive. (TP +50, 60% silence)</t>
+          <t>Bad looks, worse texture, weirdly addictive. (TP +50, 60% silence)</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -14085,7 +14417,11 @@
           <t>Bad looks and worse texture but weirdly addictive (+50 TP, 60% Silence).</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr"/>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -14105,7 +14441,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>A flattened octopus. Plenty to go around. (party HP +160, 20% party magic DEF up)</t>
+          <t>Flat octopus. Plenty for all. (party HP +160, 20% party magic DEF up)</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -14212,7 +14548,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Apparently the primary source of sustenance for one particular race. (HP/TP +200)</t>
+          <t>The main sustenance of one particular race. (HP/TP +200)</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
@@ -14226,7 +14562,11 @@
           <t>Apparently the primary source of sustenance for one particular race (+200 HP/TP).</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr"/>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -14280,7 +14620,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Tastes... sweet. Nothing but sweet. Not to be confused with balaclava. (TP +44)</t>
+          <t>Nothing but sweet. Not to be confused with balaclava. (TP +44)</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
@@ -14294,7 +14634,11 @@
           <t>Tastes... sweet. Nothing but sweet. Not to be confused with balaclava (+44 TP).</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr"/>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -14314,7 +14658,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>A runny, sugary snack. The calorie content must be through the roof. (TP +72)</t>
+          <t>A runny, sugary snack. Calories through the roof. (TP +72)</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
@@ -14328,7 +14672,11 @@
           <t>A runny, sugary snack. The calorie content must be through the roof (+72 TP).</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr"/>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -14450,7 +14798,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Waffle made with rice flour. Comes out mochi-ish. (TP +50, restores stats)</t>
+          <t>Rice flour waffle. Comes out mochi-ish. (TP +50, restores stats)</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -14464,7 +14812,11 @@
           <t>Waffle made with rice flour. Comes out mochi-ish (+50 TP, Clear Debuffs).</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr"/>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -14484,7 +14836,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>A sweet waffle with syrup mixed into the batter. (TP +85, cures all ailments)</t>
+          <t>Sweet waffle with syrup in the batter. (TP +85, cures all ailments)</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -14498,7 +14850,11 @@
           <t>A sweet waffle with syrup mixed into the batter (+85 TP, Cure All Ailments).</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr"/>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -14518,7 +14874,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Luxury pancakes like you only get at overpriced hotels. (TP +160, cures all ailments)</t>
+          <t>Overpriced-hotel luxury pancakes. (TP +160, cures all ailments)</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
@@ -14532,7 +14888,11 @@
           <t>Luxury pancakes like you only get at overpriced hotels (+160 TP, Cure All Ailments).</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -14552,7 +14912,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Which end do you eat it from? It's a matter of scholarly debate. (TP +30)</t>
+          <t>Which end to eat first? A matter of scholarly debate. (TP +30)</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
@@ -14566,7 +14926,11 @@
           <t>Which end do you eat it from? It's a matter of scholarly debate (+30 TP).</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -14586,7 +14950,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Tough rye bread that poses a challenge for seniors with weak teeth. (HP +58)</t>
+          <t>Tough rye bread. A challenge for weak teeth. (HP +58)</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
@@ -14600,7 +14964,11 @@
           <t>Tough rye bread that poses a challenge for seniors with weak teeth (+58 HP).</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr"/>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -14620,7 +14988,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Red bean bun of fine gold wheat. Diabetics should avoid it. (HP +400, 80% Defender)</t>
+          <t>Fine gold wheat bun. Diabetics, avoid it. (HP +400, 80% Defender)</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
@@ -14798,7 +15166,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Invokes the undeniable urge to rap. You'll be a real Kandy-e West. (HP +70)</t>
+          <t>Brings the urge to rap. You'll be a real Kandy-e West. (HP +70)</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -14812,7 +15180,11 @@
           <t>Invokes the undeniable urge to rap. You'll be a real Kandy-e West (+70 HP).</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -14832,7 +15204,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>A high-class rusk coated in white chocolate. Mindblowingly delicious. (HP +150)</t>
+          <t>High-class white chocolate rusk. Mindblowingly delicious. (HP +150)</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
@@ -14846,7 +15218,11 @@
           <t>A high-class rusk coated in white chocolate. Mindblowingly delicious (+150 HP).</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14866,7 +15242,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>A candy so sweet it will cause your brain to melt. (HP +300, 30% silence)</t>
+          <t>Candy so sweet your brain will melt. (HP +300, 30% silence)</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
@@ -14880,7 +15256,11 @@
           <t>A candy so sweet it will cause your brain to melt (+300 HP, 30% Silence).</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14934,7 +15314,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Eat it and you'll sweat from every orifice you've got. (HP +50, cures freeze)</t>
+          <t>You'll sweat from every orifice you've got. (HP +50, cures freeze)</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
@@ -14948,7 +15328,11 @@
           <t>Eat it and you'll sweat from every orifice you've got (+50 HP, Cure Freeze).</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -14968,7 +15352,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>First-timers will lose consciousness due to the spice. (HP/TP +75, 15% paralysis)</t>
+          <t>First-timers pass out from the spice. (HP/TP +75, 15% paralysis)</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
@@ -14982,7 +15366,11 @@
           <t>First-timers will lose consciousness due to the spice (+75 HP/TP, 15% Paralysis).</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -15002,7 +15390,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>So spicy it's out of this world. One call and they deliver. (HP +400, 80% silence)</t>
+          <t>Out-of-this-world spicy. They deliver. (HP +400, 80% silence)</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
@@ -15075,7 +15463,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Donut with red bean paste on the inside, sugar coating on the outside. (HP +200)</t>
+          <t>Donut with red bean paste inside, sugar coating outside. (HP +200)</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
@@ -15089,7 +15477,11 @@
           <t>Donut with red bean paste on the inside, sugar coating on the outside (+200 HP).</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -15215,7 +15607,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Taiyaki with matcha mixed into the batter. Looks a little gross. (HP +200, TP +40)</t>
+          <t>Matcha in the batter. Looks a little gross. (HP +200, TP +40)</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
@@ -15229,7 +15621,11 @@
           <t>Taiyaki with matcha mixed into the batter. Looks a little gross (+200 HP, +40 TP).</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -15249,7 +15645,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>The shrooms of the hills despise the coddled city bamboo shoots. (TP +40)</t>
+          <t>Hill shrooms despise the coddled city bamboo shoots. (TP +40)</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
@@ -15263,7 +15659,11 @@
           <t>The shrooms of the hills despise the coddled city bamboo shoots (+40 TP).</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -15317,7 +15717,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>The mushroom formerly known as matsutake. They're... fine. (25% Divine Shield)</t>
+          <t>Formerly known as matsutake. They're... fine. (25% Divine Shield)</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -15331,7 +15731,11 @@
           <t>The mushroom formerly known as matsutake. They're... fine.</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr"/>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -15351,7 +15755,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Yellow with red spots. Eat it, and you might get bigger. (50% max HP up)</t>
+          <t>Yellow with red spots. Eat it and you may grow. (50% max HP up)</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -15365,7 +15769,11 @@
           <t>Yellow with red spots. Eat it, and you might get bigger.</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -15589,7 +15997,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Opulent Chinese vegetable dish. Contains no meat. For some reason. (TP +150)</t>
+          <t>Opulent vegetable dish. No meat. For some reason. (TP +150)</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
@@ -15603,7 +16011,11 @@
           <t>Opulent Chinese vegetable dish. Contains no meat. For some reason (+150 TP).</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr"/>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -15623,7 +16035,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Sticky pudding with raisins. Just pudding. Honestly. (HP +100, cures 1 ailment)</t>
+          <t>Just raisin pudding. Honestly. (HP +100, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -15662,7 +16074,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>A cakey treat filled with delicious red bean paste. (HP +280, cures 1 ailment)</t>
+          <t>Cakey treat filled with red bean paste. (HP +280, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -15676,7 +16088,11 @@
           <t>A cakey treat filled with delicious red bean paste (+280 HP, Cure 1 Ailment).</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -15696,7 +16112,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Ol' reliable. You can't go wrong with bean paste. (TP +125, 65% Insurance)</t>
+          <t>Ol' reliable. Bean paste can't go wrong. (TP +125, 65% Insurance)</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
@@ -15710,7 +16126,11 @@
           <t>Ol' reliable. You can't go wrong with bean paste (+125 TP).</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -15730,7 +16150,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Soup made of leftovers. Liver and let die! (party TP +10, 20% party cure-all)</t>
+          <t>Leftovers. Liver and let die! (party TP +10, 20% party cure-all)</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -15768,7 +16188,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>The unagi's not always good, but the sauce is. (party TP +25, 40% party cure-all)</t>
+          <t>Come for the sauce, not the eel. (party TP +25, 40% party cure-all)</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -15806,7 +16226,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Dead eels on rice. You wouldn't want any. (party TP +50, 60% party cure-all)</t>
+          <t>Dead eels on rice. You'd pass. (party TP +50, 60% party cure-all)</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -15844,7 +16264,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Sushi roll of sticky, smelly, fermented soybeans. Yum...? (HP/TP +30, 50% silence)</t>
+          <t>Sticky, smelly soybean sushi. Yum...? (HP/TP +30, 50% silence)</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -15883,7 +16303,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>You must be mindful of your surroundings when eating this. (HP/TP +60, 60% silence)</t>
+          <t>Mind your surroundings when eating this. (HP/TP +60, 60% silence)</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -15897,7 +16317,11 @@
           <t>You must be mindful of your surroundings when eating this (+60 HP/TP, 60% Silence).</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr"/>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -15985,7 +16409,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Somewhat grotesque when the fish has the face of a man. (HP +100, 40% stun)</t>
+          <t>Grotesque when the fish has a man's face. (HP +100, 40% stun)</t>
         </is>
       </c>
       <c r="E445" t="inlineStr"/>
@@ -15999,7 +16423,11 @@
           <t>Somewhat grotesque when the fish has the face of a man (+100 HP, 40% Blind).</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -16053,7 +16481,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Bonito so dry it's a blunt weapon. The world's hardest food. (HP +200, 80% DEF up)</t>
+          <t>Bonito so dry it's a blunt weapon. (HP +200, 80% DEF up)</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -16067,7 +16495,11 @@
           <t>Bonito so dry it's a blunt weapon. The world's hardest food (+80% DEF).</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -16121,7 +16553,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>A simple but deep sushi. Make this your last order to look cultured. (HP +50, TP +10)</t>
+          <t>Simple but deep. Order it last to look cultured. (HP +50, TP +10)</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
@@ -16135,7 +16567,11 @@
           <t>A simple but deep sushi. Make this your last order to look cultured (+50 HP, +10 TP).</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -16155,7 +16591,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Bitter jelly good for the skin. Not so great for the tortoise. (cures all ailments)</t>
+          <t>Good for the skin. Not so for the tortoise. (cures all ailments)</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -16194,7 +16630,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Genuine, real turtle soup! Would I lie to you? (cures all ailments, 40% max HP up)</t>
+          <t>Real turtle! Would I lie to you? (cures all ailments, 40% max HP up)</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -16232,7 +16668,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Made in an earthenware pot. Delicious but steep. (cures all ailments, TP +125)</t>
+          <t>Earthenware pot. Delicious but steep. (cures all ailments, TP +125)</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
@@ -16305,7 +16741,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Bento with only meat and rice. Get those veggies out of here! (HP +150, 50% ATK up)</t>
+          <t>Only meat and rice. Veggies, get out of here! (HP +150, 50% ATK up)</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -16319,7 +16755,11 @@
           <t>Bento with only meat and rice. Get those veggies out of here! (+50% ATK).</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -16339,7 +16779,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Sukiyaki bento with super luxurious wagyu included. (HP +200, 70% ATK up)</t>
+          <t>Sukiyaki bento with super luxurious wagyu. (HP +200, 70% ATK up)</t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
@@ -16353,7 +16793,11 @@
           <t>Sukiyaki bento with super luxurious wagyu included (+70% ATK).</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -16475,7 +16919,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Try to point out that it's yellow, and a rep will appear to call it gold. (TP +60)</t>
+          <t>Call it yellow and a rep will appear to call it gold. (TP +60)</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
@@ -16489,7 +16933,11 @@
           <t>Try to point out that it's yellow, and a rep will appear to call it gold (+60 TP).</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr"/>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -16509,7 +16957,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Don't drink too much if you like your brain cells. (TP +75, 20% instakill)</t>
+          <t>Go easy if you like your brain cells. (TP +75, 20% instakill)</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -16523,7 +16971,11 @@
           <t>Don't drink too much if you like your brain cells (+75 TP).</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr"/>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -16577,7 +17029,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Cheap and delicious. Sometimes filled with pudding. (HP +135, cancels Shadow Sew)</t>
+          <t>Cheap, tasty. Sometimes has pudding. (HP +135, cancels Shadow Sew)</t>
         </is>
       </c>
       <c r="E462" t="inlineStr"/>
@@ -16616,7 +17068,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Mochi with mugwort. You can never have too much mugwort! (HP +225, cures 1 ailment)</t>
+          <t>You can never have too much mugwort! (HP +225, cures 1 ailment)</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -16630,7 +17082,11 @@
           <t>Mochi with mugwort. You can never have too much mugwort! (+225 HP, Cure 1 Ailment).</t>
         </is>
       </c>
-      <c r="H463" t="inlineStr"/>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -16752,7 +17208,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Handle it with care, or the cream will spurt all over you. (HP +200, 25% DEF up)</t>
+          <t>Careful, or the cream will spurt all over you. (HP +200, 25% DEF up)</t>
         </is>
       </c>
       <c r="E467" t="inlineStr"/>
@@ -16824,7 +17280,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Triple-stack of pancakes in sticky maple syrup. (party HP +180, 25% party ATK up)</t>
+          <t>Triple-stack in maple syrup. (party HP +180, 25% party ATK up)</t>
         </is>
       </c>
       <c r="E469" t="inlineStr"/>
@@ -16862,7 +17318,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>It means white mountain. And yet, yellow cake. Y u do dis? (HP +300, 25% accuracy up)</t>
+          <t>White mountain, yellow cake. Y u do dis? (HP +300, 25% accuracy up)</t>
         </is>
       </c>
       <c r="E470" t="inlineStr"/>
@@ -16876,7 +17332,11 @@
           <t>It means white mountain. And yet, yellow cake. Y u do dis? (+300 HP).</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr"/>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -16930,7 +17390,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>A multi-layered, doughy pie cake. (party HP +300, 25% party magic DEF up)</t>
+          <t>Multi-layered doughy pie cake. (party HP +300, 25% party magic DEF up)</t>
         </is>
       </c>
       <c r="E472" t="inlineStr"/>
@@ -16944,7 +17404,11 @@
           <t>A multi-layered, doughy pie cake (Party: +300 HP).</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr"/>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -16964,7 +17428,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>A luxury item perfect for souvenirs or gifts. (party TP +200, 40% party DEF up)</t>
+          <t>A luxury souvenir or gift. (party TP +200, 40% party DEF up)</t>
         </is>
       </c>
       <c r="E473" t="inlineStr"/>
@@ -17002,7 +17466,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Maple leaf-shaped souvenir confection. Even better as ice cream. (HP +60, TP +15)</t>
+          <t>Maple leaf souvenir. Even better as ice cream. (HP +60, TP +15)</t>
         </is>
       </c>
       <c r="E474" t="inlineStr"/>
@@ -17016,7 +17480,11 @@
           <t>Maple leaf-shaped souvenir confection. Even better as ice cream (+60 HP, +15 TP).</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr"/>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -17036,7 +17504,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Liquor brewed from millet. Its mature flavor can become a habit. (HP +125, 40% sleep)</t>
+          <t>Millet liquor. Its mature flavor can be a habit. (HP +125, 40% sleep)</t>
         </is>
       </c>
       <c r="E475" t="inlineStr"/>
@@ -17050,7 +17518,11 @@
           <t>Liquor brewed from millet. Its mature flavor can become a habit (+125 HP, 40% Sleep).</t>
         </is>
       </c>
-      <c r="H475" t="inlineStr"/>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -17070,7 +17542,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Its mascot creature has yet to be identified by science. (HP +165, 20% stun)</t>
+          <t>Its mascot is still unidentified by science. (HP +165, 20% stun)</t>
         </is>
       </c>
       <c r="E476" t="inlineStr"/>
@@ -17109,7 +17581,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Canned whale. Slowly vanishing from shelves. (HP +200, 25% Divine Shield)</t>
+          <t>Canned whale. Vanishing from shelves. (HP +200, 25% Divine Shield)</t>
         </is>
       </c>
       <c r="E477" t="inlineStr"/>
@@ -17123,7 +17595,11 @@
           <t>Canned whale. Slowly vanishing from shelves (+200 HP).</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr"/>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -17351,7 +17827,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Made from only the gloopiest cuts of the slime. (30 fixed damage, 5% slow)</t>
+          <t>Only the gloopiest cuts of slime. (30 fixed damage, 5% slow)</t>
         </is>
       </c>
       <c r="E484" t="inlineStr"/>
@@ -17365,7 +17841,11 @@
           <t>Made from only the gloopiest cuts of the slime (Speed DOWN -10%.).</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr"/>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -17419,7 +17899,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Bavarian cream full of slime. Appetizing? (party 50 fixed damage, 75% strips buffs)</t>
+          <t>Full of slime. Appetizing? (party 50 fixed damage, 75% strips buffs)</t>
         </is>
       </c>
       <c r="E486" t="inlineStr"/>
@@ -17457,7 +17937,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Spray that turns you into a super sadist for a few minutes. (50% Berserk)</t>
+          <t>Spray that makes you a super sadist for a few minutes. (50% Berserk)</t>
         </is>
       </c>
       <c r="E487" t="inlineStr"/>
@@ -17471,7 +17951,11 @@
           <t>Spray that turns you into a super sadist for a few minutes (+50% ATK).</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr"/>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -17491,7 +17975,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Feeling foreign. You're a stranger in a strange land. (75% Berserk, 75% stun)</t>
+          <t>You're a stranger in a strange land. (75% Berserk, 75% stun)</t>
         </is>
       </c>
       <c r="E488" t="inlineStr"/>
@@ -17529,7 +18013,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Canned dragon meat. Rare, expensive, a little smelly. (TP +150, cures all ailments)</t>
+          <t>Rare, pricey, slightly smelly meat. (TP +150, cures all ailments)</t>
         </is>
       </c>
       <c r="E489" t="inlineStr"/>
@@ -17602,7 +18086,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Some never tried this sake, but none tried it only once. (HP +150, 15% sleep)</t>
+          <t>Some never tried it, none tried it only once. (HP +150, 15% sleep)</t>
         </is>
       </c>
       <c r="E491" t="inlineStr"/>
@@ -17641,7 +18125,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Sake that intoxicates even heavy drinkers. Super harsh. (HP +300, 20% stun)</t>
+          <t>Intoxicates even heavy drinkers. Super harsh. (HP +300, 20% stun)</t>
         </is>
       </c>
       <c r="E492" t="inlineStr"/>
@@ -17680,7 +18164,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Port wine carefully aged for over a hundred years. (HP +400, 20% sleep)</t>
+          <t>Port wine aged for over a hundred years. (HP +400, 20% sleep)</t>
         </is>
       </c>
       <c r="E493" t="inlineStr"/>
@@ -17694,7 +18178,11 @@
           <t>Port wine carefully aged for over a hundred years (+400 HP, 20% Sleep).</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr"/>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -17782,7 +18270,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Dish made by shoving waterfowls into a dragon corpse. (HP/TP +200, 50% paralysis)</t>
+          <t>Waterfowl shoved into a dragon corpse. (HP/TP +200, 50% paralysis)</t>
         </is>
       </c>
       <c r="E496" t="inlineStr"/>
@@ -17796,7 +18284,11 @@
           <t>Dish made by shoving waterfowls into a dragon corpse (+200 HP/TP, 50% Paralysis).</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr"/>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -17850,7 +18342,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>A snack so hard, you might chip a tooth when you bite into it. (HP +200, TP +50)</t>
+          <t>So hard, a bite might chip your tooth. (HP +200, TP +50)</t>
         </is>
       </c>
       <c r="E498" t="inlineStr"/>
@@ -17864,7 +18356,11 @@
           <t>A snack so hard, you might chip a tooth when you bite into it (+200 HP, +50 TP).</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr"/>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -17952,7 +18448,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Meat is most delicious when it's almost rotten... or so they say. (35% poison)</t>
+          <t>Meat is best when almost rotten... or so they say. (35% poison)</t>
         </is>
       </c>
       <c r="E501" t="inlineStr"/>
@@ -17966,7 +18462,11 @@
           <t>Meat is most delicious when it's almost rotten... or so they say (70% Poison).</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr"/>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -17986,7 +18486,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Meat that shines suspiciously. Steroids in meat form. (50% poison, 40% paralysis)</t>
+          <t>Shines suspiciously. Steroids as meat. (50% poison, 40% paralysis)</t>
         </is>
       </c>
       <c r="E502" t="inlineStr"/>
@@ -18229,7 +18729,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Beverage squeezed out of an apple creature's insides. (HP/TP +100, 40% poison)</t>
+          <t>Squeezed from an apple creature's guts. (HP/TP +100, 40% poison)</t>
         </is>
       </c>
       <c r="E509" t="inlineStr"/>
@@ -18243,7 +18743,11 @@
           <t>Beverage squeezed out of an apple creature's insides (+100 HP/TP, 40% Poison).</t>
         </is>
       </c>
-      <c r="H509" t="inlineStr"/>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -18297,7 +18801,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Beverage squeezed out of a melon creature's insides. (HP/TP +100, 90% paralysis)</t>
+          <t>Squeezed from a melon creature's guts. (HP/TP +100, 90% paralysis)</t>
         </is>
       </c>
       <c r="E511" t="inlineStr"/>
@@ -18311,7 +18815,11 @@
           <t>Beverage squeezed out of a melon creature's insides (+100 HP/TP, 90% Paralysis).</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr"/>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -18331,7 +18839,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Unrelated to the anime girl whose face gets eaten. (HP/TP +200, 80% paralysis)</t>
+          <t>Not the anime girl whose face gets eaten. (HP/TP +200, 80% paralysis)</t>
         </is>
       </c>
       <c r="E512" t="inlineStr"/>
@@ -18370,7 +18878,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Beverage squeezed out of a banana creature's insides. (HP/TP +100, 40% silence)</t>
+          <t>Squeezed from a banana creature's guts. (HP/TP +100, 40% silence)</t>
         </is>
       </c>
       <c r="E513" t="inlineStr"/>
@@ -18384,7 +18892,11 @@
           <t>Beverage squeezed out of a banana creature's insides (+100 HP/TP, 40% Silence).</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr"/>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -18506,7 +19018,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Can be used as herbal medicine. It has a strong scent. (cures all ailments)</t>
+          <t>Herbal medicine with a strong scent. (cures all ailments)</t>
         </is>
       </c>
       <c r="E517" t="inlineStr"/>
@@ -18520,7 +19032,11 @@
           <t>Can be used as herbal medicine. It has a strong scent (Cure All Ailments).</t>
         </is>
       </c>
-      <c r="H517" t="inlineStr"/>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -18540,7 +19056,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>A mandra trefoil, used as a graduation charm. (party TP +150, 60% party magic DEF up)</t>
+          <t>A mandra graduation charm. (party TP +150, 60% party magic DEF up)</t>
         </is>
       </c>
       <c r="E518" t="inlineStr"/>
@@ -18714,7 +19230,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Too much of it will cause severe hallucinations. Not the good kind. (80% Defender)</t>
+          <t>Too much causes hallucinations. Not the good kind. (80% Defender)</t>
         </is>
       </c>
       <c r="E523" t="inlineStr"/>
@@ -18728,7 +19244,11 @@
           <t>Too much of it will cause severe hallucinations. Not the good kind.</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr"/>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -18748,7 +19268,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Fresh-squeezed mandra juice. Nice and pulpy. (party HP/TP +2000, 90% party cure-all)</t>
+          <t>Fresh-squeezed and pulpy. (party HP/TP +2000, 90% party cure-all)</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
@@ -18786,7 +19306,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Said to bring good fortune. Does anyone actually believe that? (party HP/TP +1000)</t>
+          <t>Said to bring luck. Does anyone believe that? (party HP/TP +1000)</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
@@ -18800,7 +19320,11 @@
           <t>Said to bring good fortune. Does anyone actually believe that? (Party: +1000 HP/TP).</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr"/>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -18990,7 +19514,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Made to achieve sake supremacy. To sake-cceed. (HP/TP +50, cures all ailments)</t>
+          <t>For sake supremacy. To sake-cceed. (HP/TP +50, cures all ailments)</t>
         </is>
       </c>
       <c r="E531" t="inlineStr"/>
@@ -19029,7 +19553,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Denizens of the world above say these pair well with tea. (TP +1000, 90% Insurance)</t>
+          <t>Heaven's denizens pair these with tea. (TP +1000, 90% Insurance)</t>
         </is>
       </c>
       <c r="E532" t="inlineStr"/>
@@ -19101,7 +19625,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Rice cake that crumbles from the outside as you eat it. (TP +130, 75% Divine Shield)</t>
+          <t>Rice cake that crumbles as you eat it. (TP +130, 75% Divine Shield)</t>
         </is>
       </c>
       <c r="E534" t="inlineStr"/>
@@ -19115,7 +19639,11 @@
           <t>Rice cake that crumbles from the outside as you eat it (+130 TP).</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr"/>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -19135,7 +19663,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Sweet-smelling beverage of liquified mana crystals. (TP +999, cures all ailments)</t>
+          <t>Sweet drink of liquified mana crystals. (TP +999, cures all ailments)</t>
         </is>
       </c>
       <c r="E535" t="inlineStr"/>
@@ -19174,7 +19702,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Drink that lights a fire in your loins. Yowch! Hot! (HP +5000, 99% max HP up)</t>
+          <t>Lights a fire in your loins. Yowch! Hot! (HP +5000, 99% max HP up)</t>
         </is>
       </c>
       <c r="E536" t="inlineStr"/>
@@ -19246,7 +19774,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>The most treasured treasure of the Dragon Palace... cures Freeze. (cures freeze)</t>
+          <t>The Dragon Palace's most treasured treasure... (cures freeze)</t>
         </is>
       </c>
       <c r="E538" t="inlineStr"/>
@@ -19260,7 +19788,11 @@
           <t>The most treasured treasure of the Dragon Palace... cures Freeze (Cure Freeze).</t>
         </is>
       </c>
-      <c r="H538" t="inlineStr"/>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -19280,7 +19812,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Tender green bud held by the former ruler of the world. (95% strips buffs)</t>
+          <t>Green bud held by the former ruler of the world. (95% strips buffs)</t>
         </is>
       </c>
       <c r="E539" t="inlineStr"/>
@@ -19294,7 +19826,11 @@
           <t>Tender green bud held by the former ruler of the world.</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr"/>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -19314,7 +19850,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>A magical egg. There's a whole new world inside it. (HP +1000, restores stats)</t>
+          <t>There's a whole new world inside it. (HP +1000, restores stats)</t>
         </is>
       </c>
       <c r="E540" t="inlineStr"/>
@@ -19328,7 +19864,11 @@
           <t>A magical egg. There's a whole new world inside it (+1000 HP, Clear Debuffs).</t>
         </is>
       </c>
-      <c r="H540" t="inlineStr"/>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -19348,7 +19888,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Proof that you've attended all of Miss Euthys's lectures. (leaves the dungeon)</t>
+          <t>Proof you attended all of Miss Euthys's lectures. (leaves the dungeon)</t>
         </is>
       </c>
       <c r="E541" t="inlineStr"/>
@@ -19362,7 +19902,11 @@
           <t>Proof that you've attended all of Miss Euthys's lectures (Escape Dungeon).</t>
         </is>
       </c>
-      <c r="H541" t="inlineStr"/>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>original sentence shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -20608,7 +21152,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>QoL_Desc is the text the build writes into ItemData.pck. One line, 85 characters at most.</t>
+          <t>QoL_Desc is the text the build writes into ItemData.pck. One line, 70 characters at most (the battle bar).</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_item_text.xlsx
+++ b/mod_project/data_tables/qol_item_text.xlsx
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A Souffle special. Makes a mysterious ticking noise.</t>
+          <t>A Souffle special. Makes a mysterious ticking noise. (Fire Blast Lv10)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1875,11 +1875,7 @@
           <t>A Souffle special. Makes a mysterious ticking noise (10 Fixed Dmg).</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2264,7 +2260,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>The cage of a flame beast that's too hot to handle.</t>
+          <t>The cage of a flame beast that's too hot to handle. (Fire Blast Lv1)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2278,11 +2274,7 @@
           <t>The cage of a flame beast that's too hot to handle.</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2302,7 +2294,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A book chock-full of information about demons.</t>
+          <t>A book chock-full of information about demons. (Soul Absorb Lv2)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2316,11 +2308,7 @@
           <t>A book chock-full of information about demons.</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3294,7 +3282,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Compendium of every style made by a master fistfighter.</t>
+          <t>Every style of a master fistfighter. (85% Berserk, 85% speed up)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3310,7 +3298,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3643,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>A stick for kids. To play with. Get your mind out of the gutter.</t>
+          <t>A kids' toy stick. Get your mind out of the gutter. (Soul Absorb Lv6)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3671,7 +3659,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3715,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>The handle of a toilet plunger.</t>
+          <t>The handle of a toilet plunger. (Ice Edge Lv2)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3741,11 +3729,7 @@
           <t>The handle of a toilet plunger.</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4020,7 +4004,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>A glass bottle containing pure electricity. Shocking!</t>
+          <t>A glass bottle of pure electricity. Shocking! (Thunder Chain Lv2)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4036,7 +4020,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4187,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Creepy black fire. It was always burning since the world's been turning.</t>
+          <t>Creepy black fire, burning since the world's turning. (Fire Blast Lv2)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4219,7 +4203,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4645,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Apparently a product of lunar metallurgy. Who can say?</t>
+          <t>Apparently a product of lunar metallurgy. Who can say? (Meteor Lv1)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -4675,11 +4659,7 @@
           <t>Apparently a product of lunar metallurgy. Who can say?</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4767,7 +4747,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>It's better not to make contracts with your soul. Even with other humans.</t>
+          <t>No contracts with your soul. Even with other humans. (Soul Absorb Lv3)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4783,7 +4763,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5108,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Special fan that was distributed at a big event.</t>
+          <t>Special fan that was distributed at a big event. (Air Turbulence Lv1)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5142,11 +5122,7 @@
           <t>Special fan that was distributed at a big event.</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5310,7 +5286,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>A gem with a power source within. Apparently created by fairies.</t>
+          <t>A self-powered gem. Apparently created by fairies. (Rainbow Flash Lv1)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -5326,7 +5302,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5507,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Spice that flows smoothly, which is good, because it must.</t>
+          <t>Spice that flows smoothly. Good, because it must. (Soul Absorb Lv3)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -5547,7 +5523,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6173,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Block of ice all too available in the distant northern seas.</t>
+          <t>Ice all too available in the distant northern seas. (Ice Edge Lv1)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6213,7 +6189,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6211,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Unmeltable in fire of any temperature.</t>
+          <t>Unmeltable in fire of any temperature. (Ice Storm Lv1)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6249,11 +6225,7 @@
           <t>Unmeltable in fire of any temperature.</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6345,7 +6317,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lets you stay one step ahead of the bad weather.</t>
+          <t>Lets you stay one step ahead of the bad weather. (Ice Storm Lv1)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6359,11 +6331,7 @@
           <t>Lets you stay one step ahead of the bad weather.</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6451,7 +6419,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Red and white so you know it's auspicious. Only shaped like a turtle!</t>
+          <t>Auspicious red and white. Only turtle-shaped! (HP +100, 30% speed up)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -6467,7 +6435,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6491,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Spin it on its little stand and feel as if you rule the world.</t>
+          <t>Spin it and feel as if you rule the world. (Gaia Crush Lv2)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6539,7 +6507,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6529,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Made of a clear, shining crystal. It's missing one eye.</t>
+          <t>A clear, shining crystal. It's missing one eye. (Muon Plasma Lv1)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6577,7 +6545,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7206,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>The seven-colored liquid that rainbows are made of.</t>
+          <t>The seven-colored liquid rainbows are made of. (Rainbow Flash Lv2)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -7254,7 +7222,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7453,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Drill, baby, drill! Pierce those heavens!</t>
+          <t>Drill, baby, drill! Pierce those heavens! (Stone Hammer Lv1)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -7499,11 +7467,7 @@
           <t>Drill, baby, drill! Pierce those heavens!</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7557,7 +7521,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Works on door-to-door salesmen and debt collectors.</t>
+          <t>Works on door-to-door salesmen and debt collectors. (enemies flee)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -7571,11 +7535,7 @@
           <t>Works on door-to-door salesmen and debt collectors.</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7595,7 +7555,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Fossil of some kind of interstellar cetacean.</t>
+          <t>Fossil of some kind of interstellar cetacean. (Soul Absorb Lv1)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -7609,11 +7569,7 @@
           <t>Fossil of some kind of interstellar cetacean.</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7633,7 +7589,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>The soil of a lost continent. Rich in potassium and mystery.</t>
+          <t>Lost continent soil. Rich in potassium and mystery. (Gaia Crush Lv2)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -7649,7 +7605,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -7917,7 +7873,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Ancient doll so weird looking, it's gotta be extraterrestrial.</t>
+          <t>Ancient doll so weird, it's gotta be extraterrestrial. (Meteor Lv1)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7933,7 +7889,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9472,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Burned when praying for rain. Works great... as prayers go.</t>
+          <t>Burned to pray for rain. Works great... as prayers go. (Ice Storm Lv2)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9532,7 +9488,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9578,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Throw it and a violent tornado comes out.</t>
+          <t>Throw it and a violent tornado comes out. (Tempest Lv2)</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -9636,11 +9592,7 @@
           <t>Throw it and a violent tornado comes out.</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -10138,7 +10090,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Makes you feel somewhat quicker.</t>
+          <t>Makes you feel somewhat quicker. (25% speed up)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -10152,11 +10104,7 @@
           <t>Makes you feel somewhat quicker (Speed +25%.).</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10278,7 +10226,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Menorah that's smothered in blood. Definitely not kosher.</t>
+          <t>Menorah smothered in blood. Definitely not kosher. (Soul Absorb Lv5)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -10294,7 +10242,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10908,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Why let it expire it when you die? This license is forever.</t>
+          <t>Why let it expire when you die? Licensed forever. (40% speed up)</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -10976,7 +10924,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -10998,7 +10946,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Forgeries are more common than the genuine article.</t>
+          <t>Forgeries are more common than the genuine article. (60% speed up)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
@@ -11012,11 +10960,7 @@
           <t>Forgeries are more common than the genuine article (Speed +60%.).</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11036,7 +10980,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Raise your clock rate for a limited time.</t>
+          <t>Raise your clock rate for a while. (80% speed up, 60% evasion up)</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
@@ -11052,7 +10996,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13702,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>The carbonation feels good as it slides down your throat.</t>
+          <t>The carbonation feels good sliding down your throat. (25% speed up)</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -13774,7 +13718,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17563,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>What you get when you toss a chunk of whale in your soup.</t>
+          <t>Toss whale in soup. Get this. (party HP +240, party cures freeze)</t>
         </is>
       </c>
       <c r="E478" t="inlineStr"/>
@@ -17635,7 +17579,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_item_text.xlsx
+++ b/mod_project/data_tables/qol_item_text.xlsx
@@ -506,11 +506,7 @@
           <t xml:space="preserve">0:60 | </t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Restore an ally's HP (small) (+60 HP).</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -540,11 +536,7 @@
           <t xml:space="preserve">0:250 | </t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Restore an ally's HP (medium) (+250 HP).</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -574,11 +566,7 @@
           <t xml:space="preserve">0:500 | </t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Restore an ally's HP (large) (+500 HP).</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -608,11 +596,7 @@
           <t xml:space="preserve">0:9999 | </t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Fully restore an ally's HP (Full HP).</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -642,11 +626,7 @@
           <t xml:space="preserve">3:100 | </t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Restore all allies' HP (small) (Party: +100 HP).</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -676,11 +656,7 @@
           <t xml:space="preserve">3:200 | </t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Restore all allies' HP (medium) (Party: +200 HP).</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -710,11 +686,7 @@
           <t xml:space="preserve">3:500 | </t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Restore all allies' HP (large) (Party: +500 HP).</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -744,11 +716,7 @@
           <t xml:space="preserve">2:10, 6:1 | </t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Sandwich filled with soft, fluffy eggs (+10 HP/TP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -778,12 +746,7 @@
           <t xml:space="preserve">2:20, 6:1 | </t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Bread stuffed with yakisoba noodles. Sells out very quickly.
-(+20 HP/TP, Cure 1 Ailment)</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -817,12 +780,7 @@
           <t xml:space="preserve">2:30, 7:1 | </t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Premium steak sandwich with luxury sauce. Extra deluxe.
-(+30 HP/TP, Cure All Ailments)</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -856,12 +814,7 @@
           <t xml:space="preserve">2:150, 7:1 | </t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Super spicy curry that would make even a Maharaja groan.
-(+150 HP/TP, Cure All Ailments)</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -895,12 +848,7 @@
           <t xml:space="preserve">2:1000, 7:1 | </t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Legendary food that's said to make any who eats it fall in love.
-(+1000 HP/TP, Cure All Ailments)</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -934,11 +882,7 @@
           <t xml:space="preserve">1:25 | </t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Restore an ally's TP (small). The flavor is good as well (+50 TP).</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -968,11 +912,7 @@
           <t xml:space="preserve">1:50 | </t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Restore an ally's TP (medium). Fairies love 'em (+100 TP).</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1002,11 +942,7 @@
           <t xml:space="preserve">1:100 | </t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Restore an ally's TP (large). Intimidating but delicious (Full TP).</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1036,11 +972,7 @@
           <t xml:space="preserve">6:1 | </t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Cure one status ailment for an ally. Somewhat bitter (Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1070,11 +1002,7 @@
           <t xml:space="preserve">7:1 | </t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Cure all status ailments for an ally. Sweet to the taste (Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1104,11 +1032,7 @@
           <t xml:space="preserve">8:10 | </t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Revive a fallen ally. Considerably bitter aftertaste (Revive 30% HP).</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -1142,11 +1066,7 @@
           <t xml:space="preserve">23:1 | </t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>A bell that can restore all debuffed stats to their original levels (Clear Debuffs).</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1176,12 +1096,7 @@
           <t xml:space="preserve">22:1 | </t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>A charm that cancels Shadow Sew and its skill binding effect.
-(Cure Shadow Sew &amp; Bind)</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1211,11 +1126,7 @@
           <t xml:space="preserve">9:10 | </t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Lets you light up the dungeon (Light 30 steps).</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1245,11 +1156,7 @@
           <t xml:space="preserve">10:1 | </t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Lets you escape the dungeon (Escape Dungeon).</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1279,11 +1186,7 @@
           <t xml:space="preserve">24:3 | </t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Eat, Skill, Love (+3 SP).</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1313,11 +1216,7 @@
           <t xml:space="preserve">24:9 | </t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Even more umami than MSG. Taste the skill points (+9 SP).</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1347,11 +1246,7 @@
           <t xml:space="preserve">24:9 | </t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Highly potent skill point extract. A little goes a long way (+9 SP).</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1381,12 +1276,7 @@
           <t>0:50, 1:20 | 0:50</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>High in nutritional value, it heals HP and TP but is extremely bitter.
-(+50 HP, +20 TP)</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -1420,11 +1310,7 @@
           <t>0:30, 1:40 | 0:30</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Tea with condensed bitterness. I hear it's an acquired taste.. (+30 HP, +40 TP).</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -1458,12 +1344,7 @@
           <t>3:75, 4:25 | 3:75</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Beard's special bento. A well-balanced meal, and big enough to share.
-(Party: +75 HP, +25 TP)</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -1497,11 +1378,7 @@
           <t>1:30, 16:20 | 16:10</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Peggy's eggy milk pudding. It's said to be legendary (+30 TP, 20% Sleep).</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -1535,12 +1412,7 @@
           <t>2:20, 16:15 | 16:10</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Kumaya Mangetsudo's anpan. It's low-calorie, but still delicious.
-(+20 HP/TP, 15% Sleep)</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -1574,11 +1446,7 @@
           <t>2:20, 16:15 | 16:10</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Mrs. Mary's snack smothered in maple butter (+20 HP/TP, 15% Sleep).</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1608,11 +1476,7 @@
           <t>1:30, 16:20 | 16:10</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Honey-filled monaka sold at the Kumana Mangetsudo (+30 TP, 20% Sleep).</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1642,12 +1506,7 @@
           <t>7:1, 23:1 | 7:1, 23:1</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Consists of Mary Florina's super rich milk collagen. Sorts ailments right out.
-(Cure Ailments &amp; Debuffs)</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -1681,11 +1540,7 @@
           <t xml:space="preserve"> | 59:5</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Cat food made out of their favorite high class fish.</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1715,12 +1570,7 @@
           <t>61:3 | 61:3</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Beasts love it! The flavor and nutrition balance is just right.
-(Nutritious feed for beasts. Restores loyalty and stamina.)</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -1754,11 +1604,7 @@
           <t xml:space="preserve">8:1 | </t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>An exciting new way to cheat death. Courtesy of the Peggy Company (Revive 100% HP).</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -1792,12 +1638,7 @@
           <t>7:1, 23:1 | 7:1, 23:1</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>There's a cure for pretty much anything, and there's plenty of it.
-(Cure Ailments &amp; Debuffs)</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -1831,12 +1672,7 @@
           <t>54:0.5, 11:75 | 54:0.5, 11:75</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>A Souffle special. Goes off with a bang that makes you jump.
-(75% Blind, Explosive Dmg)</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -1870,11 +1706,7 @@
           <t>46:10 | 46:10</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>A Souffle special. Makes a mysterious ticking noise (10 Fixed Dmg).</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1904,11 +1736,7 @@
           <t>3:150 | 3:150</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Helpful item to have when push comes to shove (Party: +150 HP).</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1938,11 +1766,7 @@
           <t>6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Makes you feel lucky... kinda (Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1972,11 +1796,7 @@
           <t>7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>An aged icon that's heard prayers year after year (Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2010,11 +1830,7 @@
           <t>23:1 | 23:1</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>A gun shell left by one who gave up their life for revolution (Clear Debuffs).</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2048,11 +1864,7 @@
           <t xml:space="preserve">9:30 | </t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>A splendidly well-made futuristic metal. It's a bit lumpy. Weird (Light 30 steps).</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2086,11 +1898,7 @@
           <t>19:25 | 19:10</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>It scrambles your brain, and then you die. No coming back from that (25% Death).</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2124,11 +1932,7 @@
           <t>43:0.8, 44:0.8 | 43:0.8, 44:0.8</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Inscribed with impressive wish-granting runes.</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2162,11 +1966,7 @@
           <t>0:100, 23:1 | 0:100, 23:1</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>A fish cake commonly eaten by ninjas (+100 HP, Clear Debuffs).</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2196,12 +1996,7 @@
           <t>2:75, 22:1 | 0:75, 22:1</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Rock-hard cracker. Not just a snack, but also an emergency ration!
-(+75 HP/TP, Cure Shadow Sew)</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2235,11 +2030,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>The cage of a demon that doesn't want to come out of the cage.</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2269,11 +2060,7 @@
           <t>46:1 | 46:1</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>The cage of a flame beast that's too hot to handle.</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2303,11 +2090,7 @@
           <t>51:3 | 51:2</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>A book chock-full of information about demons.</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2337,11 +2120,7 @@
           <t>35:0.8, 36:0.8 | 35:0.9, 36:0.9</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>A miraculous wind that once brought spring to the underworld.</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2375,11 +2154,7 @@
           <t>32:0.2 | 32:0.3</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Those who join the Order receive this medal.</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -2413,11 +2188,7 @@
           <t>38:0.6 | 38:0.8</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>For those elegant afternoons (+60% EVA).</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2447,11 +2218,7 @@
           <t>30:0.2 | 25:0.4</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Everyone has been looking, and we've finally found it! (+20% ATK).</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2481,11 +2248,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Without a permit, you're naught but a bandit. A dirty, dirty bandit.</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2515,11 +2278,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>You want to look for one with a short rail.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2549,11 +2308,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>A charm carried by migratory birds that wander in the wilderness.</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2583,11 +2338,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>A 27-sheet origami set, complete with gold and silver.</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2617,11 +2368,7 @@
           <t>19:25 | 19:6</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>When I peeked in, something peeked back... There's someone in there! (25% Death).</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2655,11 +2402,7 @@
           <t>29:0.4 | 29:0.8</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>A fortunetelling book with a storied history (+40% DEF).</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -2693,11 +2436,7 @@
           <t>22:1 | 22:1</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Might be usable in traditional medicine... if anything (Cure Shadow Sew &amp; Bind).</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2731,11 +2470,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>A useless hunk of rusted iron.</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2765,11 +2500,7 @@
           <t xml:space="preserve"> | 58:1</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>A miraculous fishing rod that can catch any fish in explosive fashion.</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2799,11 +2530,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>A rare ore sought by people with screwhead eyes.</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -2833,11 +2560,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Its enticing scent will consume you. Used to lube your rifle.</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -2867,11 +2590,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Carol never wore her airsoft goggles. Now she doesn't need them.</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -2901,11 +2620,7 @@
           <t>2:175, 30:0.75 | 0:175, 25:0.75</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Whatever's under all that breading, you can bet it's good and fried (+75% ATK).</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -2939,11 +2654,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Shoots a laser that lets you control folks with your mind.</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -2973,11 +2684,7 @@
           <t>14:40 | 14:20</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Those memories are precious... and painful (40% Silence).</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3007,11 +2714,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Powder compact shaped like a heart. Every gal's gotta have one.</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3041,11 +2744,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>A spoon bent not manually but mentally.</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3075,11 +2774,7 @@
           <t>16:50, 29:0.75 | 16:20, 29:0.75</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>A sedative for pregnant women, but there are side effects.. (+75% DEF).</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -3113,11 +2808,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Hide it. Quickly. Where no one will ever see it.</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -3147,11 +2838,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Poet's. The brand means quality.</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -3181,11 +2868,7 @@
           <t xml:space="preserve">10:1 | </t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Lets a witch fly free, but takes some practice (Escape Dungeon).</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -3215,11 +2898,7 @@
           <t>7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Might's not all that makes right. Money does the trick too (Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3253,11 +2932,7 @@
           <t>14:50 | 14:25</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>I must immediately depart on a long, long journey. Don't look for me (50% Silence).</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3291,11 +2966,7 @@
           <t>30:0.85, 27:0.85 | 30:0.85, 27:0.85</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Compendium of every style made by a master fistfighter (+85% ATK, +85% SPD).</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3329,11 +3000,7 @@
           <t>1:150, 30:0.75 | 25:0.75</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>A red feather you receive after donating to a fundraiser (+75% ATK).</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3367,11 +3034,7 @@
           <t>11:50 | 11:25</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Creepy pitch-black rosary (50% Blind).</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -3401,12 +3064,7 @@
           <t>18:75 | 18:30</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Cursed words from an ex-girlfriend. She's really vile...
-(Inflict Gray Curse (75% chance).)</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3436,11 +3094,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>The last stop is smudged out, but the route is via Pleiades and Orion.</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3470,11 +3124,7 @@
           <t xml:space="preserve">10:1 | </t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Down came the rain, but this web did not get washed out (Escape Dungeon).</t>
-        </is>
-      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3508,11 +3158,7 @@
           <t>12:40 | 12:20</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>One prick with this needle would be disastrous. Handle with care (40% Poison).</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3546,11 +3192,7 @@
           <t>11:30 | 11:15</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>A mirror that reveals the truth... You might not want to look (30% Blind).</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3584,11 +3226,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>A tapestry's not the only thing that can be well-hung.</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -3618,11 +3256,7 @@
           <t xml:space="preserve">1:8 | </t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>It's fantastick! (+8 TP).</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
@@ -3652,11 +3286,7 @@
           <t>51:4 | 51:6</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>A stick for kids. To play with. Get your mind out of the gutter.</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3690,11 +3320,7 @@
           <t>42:0.4 | 42:0.6</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>You can be a magical girl too.</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
@@ -3724,11 +3350,7 @@
           <t>93:4 | 93:2</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>The handle of a toilet plunger.</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
@@ -3758,11 +3380,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>A cephalo-gathering of cephalo-ladies and cephalo-gentlemen.</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
@@ -3792,11 +3410,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>A pot overflowing with mysterious black liquid. Spoiler alert: it's ink.</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
@@ -3826,11 +3440,7 @@
           <t>19:90 | 19:25</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>A disconcerting egg. The face is always screaming (90% Death).</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -3860,11 +3470,7 @@
           <t>42:0.1 | 42:0.25</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Clay used for handicraft in the heavens. Heh. They soil themselves.</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3898,12 +3504,7 @@
           <t>6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Vial of mysterious holy water. Tiny waves are ever-present at the top.
-(Cure 1 Ailment)</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3937,11 +3538,7 @@
           <t>0:50, 25:0.2 | 0:50, 25:0.4</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Fried up in an iron pan. A steal at 3 million lira! (+20% ATK).</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -3975,11 +3572,7 @@
           <t>14:30 | 14:15</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>There's no wind blowing, yet you can hear its sound. It cries Mary (30% Silence).</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4013,11 +3606,7 @@
           <t>48:2 | 48:2</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>A glass bottle containing pure electricity. Shocking!</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4051,11 +3640,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Those with a garter fetish will surely be satisfied (wink, wink).</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
@@ -4085,11 +3670,7 @@
           <t>37:0.8 | 37:0.8</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Just one drop will refresh constantly overworked eyes (Accuracy +80%.).</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4123,11 +3704,7 @@
           <t>7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>It's not just for petrification anymore! (Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
@@ -4157,12 +3734,7 @@
           <t xml:space="preserve">9:15 | </t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Blowing or splashing water won't put out this fire. We didn't start it.
-(Light 15 steps)</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4196,11 +3768,7 @@
           <t>46:4 | 46:2</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Creepy black fire. It was always burning since the world's been turning.</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4234,11 +3802,7 @@
           <t>44:0.3 | 44:0.3</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Make a man out of this and it comes to life. Weird.</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
@@ -4268,11 +3832,7 @@
           <t xml:space="preserve">1:24 | </t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>The fruit, sadly, not the special event. Sweet and packed with energy (+24 TP).</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4306,11 +3866,7 @@
           <t>1:40, 19:30 | 19:10</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>If this is waiting back at the base, you know someone's about to die (+40 TP).</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4344,11 +3900,7 @@
           <t>3:100, 4:40 | 3:100</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>A pastry for the prosperous. Crumbles on your tongue (Party: +100 HP, +40 TP).</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4382,11 +3934,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Regular old sand. Maybe you could, like, throw it at somebody?</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
@@ -4416,11 +3964,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Stone roses like this form naturally in the desert.</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
@@ -4450,11 +3994,7 @@
           <t>41:0.5 | 41:0.5</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Moist with the power of life.</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
@@ -4484,11 +4024,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>A graceful demon's tail. It's still moving.</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
@@ -4518,11 +4054,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>A graceful demon's expensive-looking choker.</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
@@ -4552,11 +4084,7 @@
           <t xml:space="preserve"> | 88:1</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Where's all the darkness? Stick your head inside and see!</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
@@ -4586,11 +4114,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>The Demon Queen's favorite sexy bra. Oooh, kill 'em!</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
@@ -4620,11 +4144,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Supposedly from the moon's surface. There's no way to check.</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
@@ -4654,11 +4174,7 @@
           <t>103:3 | 103:1</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Apparently a product of lunar metallurgy. Who can say?</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
@@ -4688,11 +4204,7 @@
           <t>19:20 | 19:10</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Plan the perfect trip to the world beyond the veil (20% Death).</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
@@ -4722,11 +4234,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Almost suspiciously simple to assemble out of blocky parts.</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
@@ -4756,11 +4264,7 @@
           <t>51:3 | 51:3</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>It's better not to make contracts with your soul. Even with other humans.</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4794,11 +4298,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>A story that panders to a taste for candor.</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
@@ -4828,11 +4328,7 @@
           <t>38:0.3 | 38:0.3</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Smooth, sticky lotion for professional use (+30% EVA).</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
@@ -4862,11 +4358,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Sow as many as you want. The one you're waiting for won't come.</t>
-        </is>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
@@ -4896,11 +4388,7 @@
           <t>35:0.6, 39:0.3 | 35:0.6, 39:0.6</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>A skull ascended through a secret rite. It's said to grant wishes.</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -4934,11 +4422,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Having these makes you feel ecologically friendly.</t>
-        </is>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
@@ -4968,11 +4452,7 @@
           <t xml:space="preserve">8:35 | </t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>It makes a nice crunching sound when you bite into it (Revive 35% HP).</t>
-        </is>
-      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -5006,12 +4486,7 @@
           <t>7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>A branch only certain people are allowed to pray to. It's twig-sclusive.
-(Cure All Ailments)</t>
-        </is>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -5045,11 +4520,7 @@
           <t>34:0.5 | 34:0.5</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>A bud of a tree that grows where God resides.</t>
-        </is>
-      </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
@@ -5079,11 +4550,7 @@
           <t>38:0.15 | 38:0.15</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Sandals that are no longer of any use. Might as well toss 'em (+15% EVA).</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -5117,11 +4584,7 @@
           <t>49:3 | 49:1</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Special fan that was distributed at a big event.</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
@@ -5151,11 +4614,7 @@
           <t>55:0.5 | 54:0.5</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>An experimental pill created by a secret organization. Do not consume.</t>
-        </is>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -5189,11 +4648,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>An old-fashioned raincoat made of straw.</t>
-        </is>
-      </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
@@ -5223,11 +4678,7 @@
           <t>11:35 | 11:20</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Stone core made when an evil heart has hardened completely (35% Blind).</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
@@ -5257,11 +4708,7 @@
           <t>25:0.5 | 25:0.5</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Do YOU ever ruin your good cleaver on bone? Finally, there's help! (+50% ATK).</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -5295,11 +4742,7 @@
           <t>106:3 | 106:1</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>A gem with a power source within. Apparently created by fairies.</t>
-        </is>
-      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -5333,12 +4776,7 @@
           <t>60:100, 17:50 | 60:100, 17:25</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Liquor made of crushed fairies. Not guaranteed not to curse you...
-(May inflict Curse (50%).)</t>
-        </is>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -5372,11 +4810,7 @@
           <t xml:space="preserve">9:5 | </t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Lantern that's overused, and somewhat broken (Light 5 steps).</t>
-        </is>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
@@ -5406,11 +4840,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>A completely worn-out hood that has lost its heat resistance.</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
@@ -5440,11 +4870,7 @@
           <t>52:30 | 52:30</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>It might be able to take... one more hit. Hit it baby one more time.</t>
-        </is>
-      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -5478,11 +4904,7 @@
           <t>41:0.5 | 41:0.5</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Do the goggles switch her personality, or just give her confidence...?</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -5516,11 +4938,7 @@
           <t>51:5 | 51:3</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Spice that flows smoothly, which is good, because it must.</t>
-        </is>
-      </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -5554,11 +4972,7 @@
           <t>6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Sparkly and radiant (Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
@@ -5588,11 +5002,7 @@
           <t>43:0.2 | 43:0.35</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Drop made out of collected mirage.</t>
-        </is>
-      </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
@@ -5622,11 +5032,7 @@
           <t>45:0.4 | 45:0.6</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>A large, mysterious key made in Hyperborea.</t>
-        </is>
-      </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
@@ -5656,11 +5062,7 @@
           <t>19:90, 1:999 | 19:35</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Eat this and you may die on the spot... or not at all (+999 TP).</t>
-        </is>
-      </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -5694,11 +5096,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Seems to be the currency of a far-off land. Basically worthless.</t>
-        </is>
-      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
@@ -5728,11 +5126,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Wrapping cloth with a pattern popular amongst particular professions.</t>
-        </is>
-      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
@@ -5762,11 +5156,7 @@
           <t>37:0.8 | 37:0.8</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Tonight, I will steal away your heart (Accuracy +80%.).</t>
-        </is>
-      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
@@ -5796,11 +5186,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>So small it'd be impossible for humans to wear.</t>
-        </is>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
@@ -5830,11 +5216,7 @@
           <t>20:1 | 20:1</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>A support item used by people who can't swim (Cure Freeze).</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
@@ -5864,11 +5246,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Oxygen tank that's been completely depleted of oxygen.</t>
-        </is>
-      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
@@ -5898,11 +5276,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Toothpick that someone has already used. Someone who wasn't you.</t>
-        </is>
-      </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
@@ -5932,11 +5306,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Cats would bump into walls without these.</t>
-        </is>
-      </c>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
@@ -5966,11 +5336,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>One of the creepier dried goods available.</t>
-        </is>
-      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
@@ -6000,11 +5366,7 @@
           <t>0:95 | 0:95</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Fried-up culinary mix of potato... and korpokkur (+95 HP).</t>
-        </is>
-      </c>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
@@ -6034,11 +5396,7 @@
           <t>1:50, 30:0.5 | 30:0.5</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Rice-based liquor aged for more than three years (+50% ATK).</t>
-        </is>
-      </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -6072,11 +5430,7 @@
           <t>28:0.6 | 28:0.3</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>For nailing uncooperative ogres to the ground (Speed DOWN -60%.).</t>
-        </is>
-      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
@@ -6106,11 +5460,7 @@
           <t xml:space="preserve">89:1 | </t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Careful. Even though it's dead, it's still hungry.</t>
-        </is>
-      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -6144,11 +5494,7 @@
           <t xml:space="preserve">89:1 | </t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Piece of the stone under which there sleeps a king of gamblers.</t>
-        </is>
-      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -6182,11 +5528,7 @@
           <t>93:2 | 93:1</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Block of ice all too available in the distant northern seas.</t>
-        </is>
-      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -6220,11 +5562,7 @@
           <t>47:3 | 47:1</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Unmeltable in fire of any temperature.</t>
-        </is>
-      </c>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
@@ -6254,11 +5592,7 @@
           <t xml:space="preserve">1:14 | </t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>A kind of dried food. Rehydrate before cooking (+14 TP).</t>
-        </is>
-      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
@@ -6288,11 +5622,7 @@
           <t>0:60, 38:0.2 | 0:60, 38:0.4</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Oil you can rub on a wound in place of salve. If you want (+20% EVA).</t>
-        </is>
-      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -6326,11 +5656,7 @@
           <t>47:3 | 47:1</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Lets you stay one step ahead of the bad weather.</t>
-        </is>
-      </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
@@ -6360,11 +5686,7 @@
           <t>21:1 | 21:1</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Somebody shut it up! (Cure Sleep).</t>
-        </is>
-      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
@@ -6394,11 +5716,7 @@
           <t>0:200, 16:75 | 0:200, 16:20</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Looks like that's a YES (+200 HP, 75% Sleep).</t>
-        </is>
-      </c>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
@@ -6428,11 +5746,7 @@
           <t>0:100, 27:0.3 | 0:100, 27:0.3</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Red and white so you know it's auspicious. Only shaped like a turtle! (+100 HP).</t>
-        </is>
-      </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -6466,11 +5780,7 @@
           <t>12:75 | 12:35</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Huge poisonous spike plucked from a tarasque's back (75% Poison).</t>
-        </is>
-      </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
@@ -6500,11 +5810,7 @@
           <t>104:4 | 104:2</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Spin it on its little stand and feel as if you rule the world.</t>
-        </is>
-      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -6538,11 +5844,7 @@
           <t>98:3 | 98:1</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Made of a clear, shining crystal. It's missing one eye.</t>
-        </is>
-      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -6576,11 +5878,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>A large bell that's noisy. Not much else to say.</t>
-        </is>
-      </c>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
@@ -6610,11 +5908,7 @@
           <t>37:0.3 | 37:0.4</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Fake version of Alexandrite Cat's Eye (Accuracy +30%.).</t>
-        </is>
-      </c>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
@@ -6644,11 +5938,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>You could poke it ad infinitum. I shall call him squishy!</t>
-        </is>
-      </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
@@ -6678,11 +5968,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>You should be able to fly with this. No guarantees though...</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
@@ -6712,12 +5998,7 @@
           <t xml:space="preserve">10:1 | </t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Throw it up in the air and maybe you'll warp to a city you've visited before.
-(Instantly teleport back to town/base.)</t>
-        </is>
-      </c>
+      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
@@ -6747,11 +6028,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>A nostalgic treble clef-shaped straw. But isn't it all about that bass...?</t>
-        </is>
-      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
@@ -6781,11 +6058,7 @@
           <t>16:90 | 16:50</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>You were forced to buy it at 5x the market price. I could cry (90% Sleep).</t>
-        </is>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -6819,11 +6092,7 @@
           <t>17:40 | 17:10</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Unfortunately, it's a one-way ticket (Inflict Curse (40% chance).).</t>
-        </is>
-      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
@@ -6853,12 +6122,7 @@
           <t>19:60 | 19:30</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Apparently it'll send you to another world with just one sip (it's poison).
-(60% Death)</t>
-        </is>
-      </c>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -6892,11 +6156,7 @@
           <t>43:0.2 | 43:0.4</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Still a step or two away from being a salad.</t>
-        </is>
-      </c>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -6926,11 +6186,7 @@
           <t xml:space="preserve">10:1 | </t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>In illegible letters, it says: I am here (Escape Dungeon).</t>
-        </is>
-      </c>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -6960,11 +6216,7 @@
           <t>44:0.3, 38:0.3 | 44:0.6, 38:0.6</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Said to bring its holder happiness (+30% EVA).</t>
-        </is>
-      </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -6994,11 +6246,7 @@
           <t>17:30 | 17:15</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Honestly, just cut me some slack (Inflict Curse (30% chance).).</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -7028,12 +6276,7 @@
           <t>14:30 | 14:15</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>It says it's lucky. You can't believe everything you read, now can you?
-(30% Silence)</t>
-        </is>
-      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7067,11 +6310,7 @@
           <t>37:0.5 | 37:0.6</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>A letter that simply says: You are my fire. My one desire (Accuracy +50%.).</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7105,11 +6344,7 @@
           <t>30:0.8 | 30:0.4</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>The prompt asks, who's your personal hero? I wrote, 'Me.' (+80% ATK).</t>
-        </is>
-      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7143,11 +6378,7 @@
           <t>25:0.3 | 25:0.3</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Tiger scroll filled with innermost secrets of martial arts (+30% ATK).</t>
-        </is>
-      </c>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7181,11 +6412,7 @@
           <t>25:0.5 | 25:0.5</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>The symbol of justice. Who needs bats, anyways? (+50% ATK).</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
@@ -7215,11 +6442,7 @@
           <t>106:5 | 106:2</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>The seven-colored liquid that rainbows are made of.</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7253,11 +6476,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Illegal due to some treaty or other. Correspondingly expensive.</t>
-        </is>
-      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
@@ -7287,11 +6506,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>It was formerly a flying carpet. Now it's just a crappy everyday carpet.</t>
-        </is>
-      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
@@ -7321,12 +6536,7 @@
           <t>1:100, 11:75 | 11:40</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Holy river water that contains all sorts of extracts. Extracts...
-(+100 TP, 75% Blind)</t>
-        </is>
-      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7360,11 +6570,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Chipped front tooth left behind by a Mole.</t>
-        </is>
-      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
@@ -7394,11 +6600,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Lovingly arranged anthology of only the most salacious cases.</t>
-        </is>
-      </c>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
@@ -7428,11 +6630,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Do you understand the difference between a shovel and a spade?</t>
-        </is>
-      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -7462,11 +6660,7 @@
           <t>102:2 | 102:1</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Drill, baby, drill! Pierce those heavens!</t>
-        </is>
-      </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -7496,11 +6690,7 @@
           <t>15:40 | 15:20</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>More of a snow acquaintance. A snowperson at any rate (40% Freeze).</t>
-        </is>
-      </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
@@ -7530,11 +6720,7 @@
           <t xml:space="preserve">88:1 | </t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Works on door-to-door salesmen and debt collectors.</t>
-        </is>
-      </c>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
@@ -7564,11 +6750,7 @@
           <t>51:2 | 51:1</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Fossil of some kind of interstellar cetacean.</t>
-        </is>
-      </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
@@ -7598,11 +6780,7 @@
           <t>104:5 | 104:2</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>The soil of a lost continent. Rich in potassium and mystery.</t>
-        </is>
-      </c>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7636,11 +6814,7 @@
           <t xml:space="preserve">1:18 | </t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>A scent to calm even the most candle-hating heart (+18 TP).</t>
-        </is>
-      </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
@@ -7670,11 +6844,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Jiggles back and forth ever so slightly. Makes you wanna punch it.</t>
-        </is>
-      </c>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -7704,11 +6874,7 @@
           <t>22:1, 23:1 | 22:1, 23:1</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Good for massages and hair care and so on (Cure Shadow Sew).</t>
-        </is>
-      </c>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7742,11 +6908,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Brown recycled paper used for lunch bags.</t>
-        </is>
-      </c>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
@@ -7776,11 +6938,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Paper with some great bamboo scent. Scent-illating!</t>
-        </is>
-      </c>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
@@ -7810,11 +6968,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Paper that lasts for a millennium. Or two.</t>
-        </is>
-      </c>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
@@ -7844,11 +6998,7 @@
           <t>34:0.6 | 34:0.6</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>An origami crane made with an exceedingly high number of folds.</t>
-        </is>
-      </c>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7882,11 +7032,7 @@
           <t>103:3 | 103:1</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Ancient doll so weird looking, it's gotta be extraterrestrial.</t>
-        </is>
-      </c>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -7920,11 +7066,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Annoying box that won't open so easily.</t>
-        </is>
-      </c>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
@@ -7954,11 +7096,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>A box that can't be opened. No way, no how.</t>
-        </is>
-      </c>
+      <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
@@ -7988,11 +7126,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Where'd all the stuff inside it go?</t>
-        </is>
-      </c>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
@@ -8022,11 +7156,7 @@
           <t>52:110 | 52:110</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Dangerous box that shoots out needles when opened improperly.</t>
-        </is>
-      </c>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -8060,11 +7190,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>You store wishes in it, but they likely won't be granted. Such is life.</t>
-        </is>
-      </c>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
@@ -8094,11 +7220,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>It's broken, possibly from getting hit so much.</t>
-        </is>
-      </c>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
@@ -8128,11 +7250,7 @@
           <t>53:150 | 53:150</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>A box full of contracts signed under threat of violence.</t>
-        </is>
-      </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -8166,11 +7284,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>It was magnificent in the past... apparently.</t>
-        </is>
-      </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
@@ -8200,11 +7314,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Toy that looks like the sword of a hero.</t>
-        </is>
-      </c>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
@@ -8234,11 +7344,7 @@
           <t>11:50 | 11:35</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>A sword with a bamboo grip. For some reason, the grip... reeks (50% Blind).</t>
-        </is>
-      </c>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -8272,11 +7378,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>You can tell it's fake just from the name.</t>
-        </is>
-      </c>
+      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
@@ -8306,11 +7408,7 @@
           <t>13:50 | 13:35</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>A giant bloodshot eyeball. At least it's not moving (50% Paralysis).</t>
-        </is>
-      </c>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
@@ -8340,11 +7438,7 @@
           <t>52:15 | 52:15</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>A chain that's been worn down by too much grinding. Kinda like my ex.</t>
-        </is>
-      </c>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -8378,11 +7472,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>A large-scale spanner for retightening bolt heads.</t>
-        </is>
-      </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
@@ -8412,11 +7502,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>A form of immortality. Be careful what you wish for!</t>
-        </is>
-      </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
@@ -8446,11 +7532,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Chipped, useless gear wheel.</t>
-        </is>
-      </c>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
@@ -8480,11 +7562,7 @@
           <t>13:35 | 13:22</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Despite its not having a head, you swear you've heard it giggle (35% Paralysis).</t>
-        </is>
-      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -8518,11 +7596,7 @@
           <t>45:0.3 | 45:0.6</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Doll that changes to look just like you when you press its nose.</t>
-        </is>
-      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -8556,11 +7630,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Silver and black portable gaming device. It's a piece of history.</t>
-        </is>
-      </c>
+      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
@@ -8590,11 +7660,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>A pebble. Nothing more and nothing less.</t>
-        </is>
-      </c>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
@@ -8624,11 +7690,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>A beautiful, emerald rock. God dammit Marie, they're minerals!</t>
-        </is>
-      </c>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
@@ -8658,11 +7720,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>A jasper with many red, blood-like speckles.</t>
-        </is>
-      </c>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
@@ -8692,11 +7750,7 @@
           <t>14:30 | 14:15</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Every time you look at it, the people are in different poses (30% Silence).</t>
-        </is>
-      </c>
+      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -8730,11 +7784,7 @@
           <t>11:40 | 11:20</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>A primal scream that resounds through the natural world (40% Blind).</t>
-        </is>
-      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
@@ -8764,11 +7814,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>So expensive, you can't bring yourself to actually try it.</t>
-        </is>
-      </c>
+      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
@@ -8798,11 +7844,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Handy for extorting affection.</t>
-        </is>
-      </c>
+      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
@@ -8832,11 +7874,7 @@
           <t>0:325 | 0:325</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>Fried doughball confection. Just one will fill you up (+325 HP).</t>
-        </is>
-      </c>
+      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
@@ -8866,11 +7904,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>Too old now to be of any use to anyone...</t>
-        </is>
-      </c>
+      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
     </row>
     <row r="238">
@@ -8900,11 +7934,7 @@
           <t>20:1 | 20:1</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>Low-tech but reliable way to warm up (Cure Freeze).</t>
-        </is>
-      </c>
+      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
@@ -8934,11 +7964,7 @@
           <t>19:30 | 19:15</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>Not for use indoors. DEFINITELY not for use in a vehicle! (30% Death).</t>
-        </is>
-      </c>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -8972,11 +7998,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Put this in your wallet and goodbye money problems!</t>
-        </is>
-      </c>
+      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
@@ -9006,11 +8028,7 @@
           <t>11:15 | 11:12</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>Used for voodoo curses. Picture your enemy, and give it your all! (15% Blind).</t>
-        </is>
-      </c>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9044,11 +8062,7 @@
           <t>12:20, 14:20 | 12:10, 14:10</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>Jelly infused with natural demon... stuff (20% Poison, 20% Silence).</t>
-        </is>
-      </c>
+      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
@@ -9078,11 +8092,7 @@
           <t>90:6 | 90:3</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Burning ice that sleeps in the ocean's depths.</t>
-        </is>
-      </c>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -9116,11 +8126,7 @@
           <t>54:0.2 | 54:0.2</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>Water with malicious intent. Good thing it's stuck in the bottle.</t>
-        </is>
-      </c>
+      <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -9154,11 +8160,7 @@
           <t xml:space="preserve">89:1 | </t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>Emits a fell light and leads its owner to ruin.</t>
-        </is>
-      </c>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -9192,11 +8194,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>A sturdy chastity belt for wyverns. It also comes with a lock.</t>
-        </is>
-      </c>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
@@ -9226,11 +8224,7 @@
           <t>1:150, 15:30 | 15:15</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Mist that covers your skin in glossy beads (+150 TP, 30% Freeze).</t>
-        </is>
-      </c>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
@@ -9260,11 +8254,7 @@
           <t>90:7 | 90:3</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Apparently these are very expensive in some places.</t>
-        </is>
-      </c>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -9298,11 +8288,7 @@
           <t>4:75, 23:1 | 23:1</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>A boxful of crackin' chocolate. The ladies love it! (Party: +75 TP, Clear Debuffs).</t>
-        </is>
-      </c>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9336,11 +8322,7 @@
           <t>28:0.6 | 28:0.4</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>I'd like to think this is the cause for my weight gain.. (Speed DOWN -60%.).</t>
-        </is>
-      </c>
+      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
@@ -9370,12 +8352,7 @@
           <t xml:space="preserve">56:0.15, 17:0.8 | </t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>A roiling mass of darkness. And... is that a green lady in there?
-(May inflict Curse (80%).)</t>
-        </is>
-      </c>
+      <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -9409,11 +8386,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>A ball used by kemari masters for practice.</t>
-        </is>
-      </c>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
@@ -9443,11 +8416,7 @@
           <t>40:0.95 | 40:0.75</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>Collecting seven of these summons a dragon that grants your wishes.</t>
-        </is>
-      </c>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9481,11 +8450,7 @@
           <t>47:4 | 47:2</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>Burned when praying for rain. Works great... as prayers go.</t>
-        </is>
-      </c>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9519,11 +8484,7 @@
           <t>12:60 | 12:35</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>It had to be removed due to cavity (60% Poison).</t>
-        </is>
-      </c>
+      <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
@@ -9553,11 +8514,7 @@
           <t>13:60 | 13:35</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>A paralyzing claw that was cut to the quick (60% Paralysis).</t>
-        </is>
-      </c>
+      <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
@@ -9587,11 +8544,7 @@
           <t>101:4 | 101:2</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Throw it and a violent tornado comes out.</t>
-        </is>
-      </c>
+      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
     </row>
     <row r="258">
@@ -9621,11 +8574,7 @@
           <t>4:100, 53:500 | 53:200</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>No-good apple that tempts women into strife (Party: +100 TP).</t>
-        </is>
-      </c>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9659,11 +8608,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>Stone that shines with seven colors. Not a real rainbow, though.</t>
-        </is>
-      </c>
+      <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
     </row>
     <row r="260">
@@ -9693,11 +8638,7 @@
           <t>36:0.2 | 36:0.35</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>Huge bell that wards off evil when run. Awkward to carry around.</t>
-        </is>
-      </c>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9731,11 +8672,7 @@
           <t>34:0.9 | 4:15, 34:0.9</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Water from a shrine that venerates a god of the land.</t>
-        </is>
-      </c>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9769,11 +8706,7 @@
           <t>1:50, 30:0.4 | 30:0.2</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Fruit goes in the dragon. This stuff comes out. Don't ask (+40% ATK).</t>
-        </is>
-      </c>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9807,11 +8740,7 @@
           <t>40:0.95 | 40:0.9</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>Press it if you want peace at any cost. There may be consequences...</t>
-        </is>
-      </c>
+      <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9845,11 +8774,7 @@
           <t>16:20 | 16:10</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Used by busy mommy dragons to keep their babies quiet (20% Sleep).</t>
-        </is>
-      </c>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
@@ -9879,11 +8804,7 @@
           <t>16:40 | 16:20</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Tough enough to survive in a mouth full of dragon baby teeth (40% Sleep).</t>
-        </is>
-      </c>
+      <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9917,11 +8838,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>Used instead of a floorcloth...</t>
-        </is>
-      </c>
+      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
     </row>
     <row r="267">
@@ -9951,11 +8868,7 @@
           <t>38:0.3 | 38:0.6</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>A strange substance that feels like nothingness when you touch it (+30% EVA).</t>
-        </is>
-      </c>
+      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -9989,11 +8902,7 @@
           <t>0:200, 16:90 | 0:200, 16:20</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>Not for napping in. For hiding people taking naps (+200 HP, 90% Sleep).</t>
-        </is>
-      </c>
+      <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10027,11 +8936,7 @@
           <t>13:15 | 13:12</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>A mask that is just gold in color. Not all that glitters is gold (15% Paralysis).</t>
-        </is>
-      </c>
+      <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10065,11 +8970,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>Broken scale that's splattered in blood.</t>
-        </is>
-      </c>
+      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
     </row>
     <row r="271">
@@ -10099,11 +9000,7 @@
           <t>27:0.25 | 27:0.25</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>Makes you feel somewhat quicker (Speed +25%.).</t>
-        </is>
-      </c>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
     </row>
     <row r="272">
@@ -10133,11 +9030,7 @@
           <t>19:60 | 19:20</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>Goodnight forever (60% Death).</t>
-        </is>
-      </c>
+      <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
@@ -10167,11 +9060,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>Fetters that have faded after a long period of time.</t>
-        </is>
-      </c>
+      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
     </row>
     <row r="274">
@@ -10201,11 +9090,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>Fresh stockings that move around freely.</t>
-        </is>
-      </c>
+      <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
@@ -10235,11 +9120,7 @@
           <t>51:5 | 51:5</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>Menorah that's smothered in blood. Definitely not kosher.</t>
-        </is>
-      </c>
+      <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10273,11 +9154,7 @@
           <t>19:40 | 19:15</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! (40% Death).</t>
-        </is>
-      </c>
+      <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10311,11 +9188,7 @@
           <t>19:80 | 19:20</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>Dangerous! Do not touch! Deadly poison! Requires careful handling! #2 (80% Death).</t>
-        </is>
-      </c>
+      <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10349,11 +9222,7 @@
           <t>19:95 | 19:30</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>A nice little rowboat. Cruise the river separating life and death (95% Death).</t>
-        </is>
-      </c>
+      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10387,11 +9256,7 @@
           <t>1:35, 16:25 | 16:16</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>Sweet mint immortali-tea. More relaxing than relaxation itself (+35 TP, 25% Sleep).</t>
-        </is>
-      </c>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10425,11 +9290,7 @@
           <t>13:30, 16:30 | 13:15, 16:15</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>So much jealousy, it's visible to the naked eye (30% Paralysis, 30% Sleep).</t>
-        </is>
-      </c>
+      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10463,11 +9324,7 @@
           <t xml:space="preserve">8:15 | </t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>You'll come back to life. No guarantees about how (Revive 15% HP).</t>
-        </is>
-      </c>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -10497,11 +9354,7 @@
           <t>0:60, 11:25 | 0:60, 11:15</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>Bun that gives off the taste of the afterlife (+60 HP, 25% Blind).</t>
-        </is>
-      </c>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
@@ -10531,11 +9384,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>Don't follow where it goes.</t>
-        </is>
-      </c>
+      <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr"/>
     </row>
     <row r="284">
@@ -10565,11 +9414,7 @@
           <t>17:20 | 17:15</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>I really hope my photo's not on there (Inflict Curse (20% chance).).</t>
-        </is>
-      </c>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
@@ -10599,11 +9444,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>A book by ladies for ladies regarding how to act like the first ladies.</t>
-        </is>
-      </c>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr"/>
     </row>
     <row r="286">
@@ -10633,11 +9474,7 @@
           <t>13:50 | 13:25</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>You'll want to stay away from the water this came from (50% Paralysis).</t>
-        </is>
-      </c>
+      <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10671,11 +9508,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>No kittens here. Comes in like spam every week, though, so ignore it.</t>
-        </is>
-      </c>
+      <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr"/>
     </row>
     <row r="288">
@@ -10705,11 +9538,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>Bloom nobly, and scatter beautifully.</t>
-        </is>
-      </c>
+      <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
@@ -10739,11 +9568,7 @@
           <t>42:0.25 | 42:0.5</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>Living shadow that leaves and acts on its own.</t>
-        </is>
-      </c>
+      <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
@@ -10773,11 +9598,7 @@
           <t>52:50 | 52:50</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>Toss it in to any potluck stew to instantly increase the chaos.</t>
-        </is>
-      </c>
+      <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10811,11 +9632,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>No light can escape it. A serious tripping hazard at night.</t>
-        </is>
-      </c>
+      <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
     </row>
     <row r="292">
@@ -10845,11 +9662,7 @@
           <t>14:40 | 14:20</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>Just ignore them (40% Silence).</t>
-        </is>
-      </c>
+      <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr"/>
     </row>
     <row r="293">
@@ -10879,11 +9692,7 @@
           <t>11:60 | 11:30</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>Disembodied wrist. Scurries all over the floor like a cleaning robot (60% Blind).</t>
-        </is>
-      </c>
+      <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10917,11 +9726,7 @@
           <t>27:0.4 | 27:0.8</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>Why let it expire it when you die? This license is forever (Speed +40%.).</t>
-        </is>
-      </c>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -10955,11 +9760,7 @@
           <t>27:0.6 | 27:0.8</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>Forgeries are more common than the genuine article (Speed +60%.).</t>
-        </is>
-      </c>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr"/>
     </row>
     <row r="296">
@@ -10989,11 +9790,7 @@
           <t>27:0.8, 38:0.6 | 27:0.8, 38:0.6</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>Raise your clock rate for a limited time (+60% EVA).</t>
-        </is>
-      </c>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11027,11 +9824,7 @@
           <t>1:20, 6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>Careful there, mate. That's not chocolate (+20 TP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr"/>
     </row>
     <row r="298">
@@ -11061,11 +9854,7 @@
           <t>1:12, 15:20 | 15:10</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>Ice cream in a peach-shaped container (+12 TP, 20% Freeze).</t>
-        </is>
-      </c>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
     </row>
     <row r="299">
@@ -11095,11 +9884,7 @@
           <t>1:24, 16:20 | 16:10</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>Sweet mixed drink popular with the ladies (+24 TP, 20% Sleep).</t>
-        </is>
-      </c>
+      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
     </row>
     <row r="300">
@@ -11129,11 +9914,7 @@
           <t>1:36, 6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>Peach-shaped bun eaten in times of celebration (+36 TP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11167,11 +9948,7 @@
           <t>0:30 | 0:30</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>Not actually persimmon seeds. More a seed-shaped rice snack (+30 HP).</t>
-        </is>
-      </c>
+      <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
     </row>
     <row r="302">
@@ -11201,12 +9978,7 @@
           <t>1:15, 6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>Sweet persimmons fumigated with sulfur for preservation. Tasty.
-(+15 TP, Cure 1 Ailment)</t>
-        </is>
-      </c>
+      <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11240,11 +10012,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>A snapshot of the famous persimmon-themed bad boys.</t>
-        </is>
-      </c>
+      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
     </row>
     <row r="304">
@@ -11274,12 +10042,7 @@
           <t>3:130, 22:1 | 3:130, 22:1</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>Sushi wrapped in persimmon leaves. Don't eat the leaves, kiddo.
-(Party: +130 HP, Cure Shadow Sew)</t>
-        </is>
-      </c>
+      <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11313,12 +10076,7 @@
           <t>3:600, 20:1 | 3:150, 20:1</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>Stew of bear-meat citatap with pukusakina and plenty of veggies.
-(Party: +600 HP, Cure Freeze)</t>
-        </is>
-      </c>
+      <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11352,11 +10110,7 @@
           <t>0:200, 20:1 | 0:200, 20:1</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>Bear soup that warms up your body (+200 HP, Cure Freeze).</t>
-        </is>
-      </c>
+      <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
     </row>
     <row r="307">
@@ -11386,11 +10140,7 @@
           <t>3:300 | 3:300</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>Add some rice at the end to make porridge! (Party: +300 HP).</t>
-        </is>
-      </c>
+      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
@@ -11420,11 +10170,7 @@
           <t>1:20, 6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>Healthy and delicious chicken meatballs (+20 TP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr"/>
     </row>
     <row r="309">
@@ -11454,11 +10200,7 @@
           <t>0:320 | 0:200</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>Enjoy the flavor of the meat! Salt, not sauce! (+320 HP).</t>
-        </is>
-      </c>
+      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
     </row>
     <row r="310">
@@ -11488,12 +10230,7 @@
           <t>0:240, 23:1 | 0:200, 23:1</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>Piping hot fried chicken. Ask before you add lemon juice, just to be safe.
-(+240 HP, Clear Debuffs)</t>
-        </is>
-      </c>
+      <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11527,11 +10264,7 @@
           <t>0:180 | 0:200</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>Perfect for diets. Though... isn't raw chicken dangerous? (+180 HP).</t>
-        </is>
-      </c>
+      <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr"/>
     </row>
     <row r="312">
@@ -11561,11 +10294,7 @@
           <t>3:150 | 3:150</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>A delicious hotpot dish with an addicting smell (Party: +150 HP).</t>
-        </is>
-      </c>
+      <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
     </row>
     <row r="313">
@@ -11595,11 +10324,7 @@
           <t>0:200 | 0:200</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>Lamb dish with heavy garlic flavor (+200 HP).</t>
-        </is>
-      </c>
+      <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr"/>
     </row>
     <row r="314">
@@ -11629,11 +10354,7 @@
           <t>1:300, 7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>A slightly disgusting dish made with simmered bear paw (+300 TP, Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11667,11 +10388,7 @@
           <t>0:200 | 0:200</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>Luxury lamb dish with absolutely no bad odor (+200 HP).</t>
-        </is>
-      </c>
+      <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
     </row>
     <row r="316">
@@ -11701,11 +10418,7 @@
           <t>1:50, 38:1 | 38:1</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>Fried lamb meatballs with strong coriander scent (+100% EVA).</t>
-        </is>
-      </c>
+      <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11739,11 +10452,7 @@
           <t>0:300, 6:1 | 0:300, 6:1</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>Lunch set with bird meat and bear meat mixed together (+300 HP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11777,11 +10486,7 @@
           <t>38:0.8 | 38:0.9</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>Brave penguins gave their lives to bring you fuel and soap (+80% EVA).</t>
-        </is>
-      </c>
+      <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11815,11 +10520,7 @@
           <t>0:100 | 0:100</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>Drink made by mixing cola and strawberries together (+100 HP).</t>
-        </is>
-      </c>
+      <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr"/>
     </row>
     <row r="320">
@@ -11849,11 +10550,7 @@
           <t>0:200, 21:1 | 0:200, 21:1</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>Feel refreshed by the mint's cold and transcendent stimulation (+200 HP, Cure Sleep).</t>
-        </is>
-      </c>
+      <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -11887,11 +10584,7 @@
           <t>0:275 | 0:275</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>Frozen danish with a penguin mark on it (+275 HP).</t>
-        </is>
-      </c>
+      <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr"/>
     </row>
     <row r="322">
@@ -11921,11 +10614,7 @@
           <t>0:400 | 0:400</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>Ice cream from the past with a nostalgic texture (+400 HP).</t>
-        </is>
-      </c>
+      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr"/>
     </row>
     <row r="323">
@@ -11955,11 +10644,7 @@
           <t xml:space="preserve">1:30 | </t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>Salmon buried in snow to be preserved by the cold (+30 TP).</t>
-        </is>
-      </c>
+      <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr"/>
     </row>
     <row r="324">
@@ -11989,11 +10674,7 @@
           <t xml:space="preserve">1:75 | </t>
         </is>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>All-natural, of course. Gluten-free, too! (+75 TP).</t>
-        </is>
-      </c>
+      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr"/>
     </row>
     <row r="325">
@@ -12023,11 +10704,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>A splendid woodcarved bear ornament. It's black and shiny.</t>
-        </is>
-      </c>
+      <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr"/>
     </row>
     <row r="326">
@@ -12057,11 +10734,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>A blue bear. I think I'll call it Teddie.</t>
-        </is>
-      </c>
+      <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr"/>
     </row>
     <row r="327">
@@ -12091,11 +10764,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>Awakens from its hibernation if you put a coin in the slot on its back.</t>
-        </is>
-      </c>
+      <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
@@ -12125,11 +10794,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>Suit representing a popular bear. Wear it and get in trademark trouble!</t>
-        </is>
-      </c>
+      <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr"/>
     </row>
     <row r="329">
@@ -12159,11 +10824,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>Pile of wool that is essentially worthless.</t>
-        </is>
-      </c>
+      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr"/>
     </row>
     <row r="330">
@@ -12193,11 +10854,7 @@
           <t>22:1 | 22:1</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>Oil that reeks of sheep (Cure Shadow Sew &amp; Bind).</t>
-        </is>
-      </c>
+      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr"/>
     </row>
     <row r="331">
@@ -12227,11 +10884,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>Classy wool that doesn't prickle and keeps the heat in just right.</t>
-        </is>
-      </c>
+      <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr"/>
     </row>
     <row r="332">
@@ -12261,11 +10914,7 @@
           <t>12:5 | 12:5</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>Supplement with a pungently strange odor (5% Poison).</t>
-        </is>
-      </c>
+      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
@@ -12295,11 +10944,7 @@
           <t>11:10 | 11:10</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>Sketchy in over seven ways. Get it? Like seven colors of the rainbow! (10% Blind).</t>
-        </is>
-      </c>
+      <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -12333,11 +10978,7 @@
           <t>44:0.2 | 44:0.3</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>All your exhaustion magically melts away.</t>
-        </is>
-      </c>
+      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr"/>
     </row>
     <row r="335">
@@ -12367,11 +11008,7 @@
           <t>0:100 | 0:100</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>Fun, colorful rice dumplings on a skewer (+100 HP).</t>
-        </is>
-      </c>
+      <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
     </row>
     <row r="336">
@@ -12401,11 +11038,7 @@
           <t>0:200, 6:1 | 0:200, 6:1</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>Rice dumplings glazed in sweet soy (+200 HP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr"/>
     </row>
     <row r="337">
@@ -12435,11 +11068,7 @@
           <t>3:180, 35:0.6 | 3:180, 35:0.6</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>Three delicious aspects of the dumpling, together on one skewer (Party: +180 HP).</t>
-        </is>
-      </c>
+      <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -12473,11 +11102,7 @@
           <t>2:180 | 0:80</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>Freshly cut horse-meat sashimi (+180 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr"/>
     </row>
     <row r="339">
@@ -12507,11 +11132,7 @@
           <t>2:360, 29:0.75 | 0:360, 29:0.75</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>Aged, well-smoked horse meat. An exquisite dish (+75% DEF).</t>
-        </is>
-      </c>
+      <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -12545,11 +11166,7 @@
           <t>2:2000, 45:0.95 | 0:2000, 45:0.95</t>
         </is>
       </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>Raw meat cut fine and called a steak. Consume with caution (+2000 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -12583,11 +11200,7 @@
           <t>0:120 | 0:120</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>A homemade rice ball made this morning (+120 HP).</t>
-        </is>
-      </c>
+      <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr"/>
     </row>
     <row r="342">
@@ -12617,11 +11230,7 @@
           <t>0:280 | 0:280</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>A salmon-filled rice ball that required a lot of effort (+280 HP).</t>
-        </is>
-      </c>
+      <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr"/>
     </row>
     <row r="343">
@@ -12651,11 +11260,7 @@
           <t>0:380 | 0:380</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>A rice ball stuffed with sour pickled plums (+380 HP).</t>
-        </is>
-      </c>
+      <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr"/>
     </row>
     <row r="344">
@@ -12685,11 +11290,7 @@
           <t>0:420 | 0:420</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>A warm rice ball, pan-grilled with soy sauce (+420 HP).</t>
-        </is>
-      </c>
+      <c r="G344" t="inlineStr"/>
       <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
@@ -12719,11 +11320,7 @@
           <t>0:515, 45:0.3 | 0:650, 45:0.6</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>Glutinous steamed rice dish with big pieces of chestnut (+515 HP).</t>
-        </is>
-      </c>
+      <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -12757,11 +11354,7 @@
           <t>0:105 | 0:105</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>Chewy on the outside, moist on the inside (+105 HP).</t>
-        </is>
-      </c>
+      <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr"/>
     </row>
     <row r="347">
@@ -12791,11 +11384,7 @@
           <t>0:135, 37:0.3 | 0:135, 37:0.3</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>Seashell-shaped snack. Sally sells them by the seashore (+135 HP).</t>
-        </is>
-      </c>
+      <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -12829,12 +11418,7 @@
           <t>3:165, 23:1 | 3:165, 23:1</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>Solidified syrup and dry fruit. A hard candy for hard men.
-(Party: +165 HP, Clear Debuffs)</t>
-        </is>
-      </c>
+      <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -12868,12 +11452,7 @@
           <t>3:250, 4:25 | 3:225</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>A cake with a figurine in it. Whoever finds the little feller gets to be king.
-(Party: +250 HP, +25 TP)</t>
-        </is>
-      </c>
+      <c r="G349" t="inlineStr"/>
       <c r="H349" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -12907,11 +11486,7 @@
           <t>2:30 | 0:30</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>Not everyone who eats muffins is in the mafia. The muffia? Hyuk hyuk (+30 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G350" t="inlineStr"/>
       <c r="H350" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -12945,11 +11520,7 @@
           <t>0:50, 37:0.5 | 0:50, 37:0.7</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>Off the shelf or the classy kind? They're really not that different (+50 HP).</t>
-        </is>
-      </c>
+      <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -12983,11 +11554,7 @@
           <t>4:115, 39:0.7 | 39:0.9</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>Party pastry constructed of fruits, custard, and jelly (Party: +115 TP).</t>
-        </is>
-      </c>
+      <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13021,11 +11588,7 @@
           <t>3:55 | 3:55</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>A cookie cut into a simple shape. Ooh, looks like a star! (Party: +55 HP).</t>
-        </is>
-      </c>
+      <c r="G353" t="inlineStr"/>
       <c r="H353" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13059,11 +11622,7 @@
           <t>3:160 | 3:160</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>A cookie cut into a somewhat complex shape. Ooh, looks like a cow! (Party: +160 HP).</t>
-        </is>
-      </c>
+      <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13097,11 +11656,7 @@
           <t>3:200, 34:0.6 | 3:200, 34:0.6</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>A cookie cut into a highly complex shape. Ooh, looks like Japan! (Party: +200 HP).</t>
-        </is>
-      </c>
+      <c r="G355" t="inlineStr"/>
       <c r="H355" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13135,11 +11690,7 @@
           <t>0:75 | 0:75</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>Old-fashioned rice cracker covered in soy sauce (+75 HP).</t>
-        </is>
-      </c>
+      <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr"/>
     </row>
     <row r="357">
@@ -13169,11 +11720,7 @@
           <t>0:120, 31:0.25 | 0:120, 26:0.25</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>Rice cracker covered in plenty of cayenne powder (+120 HP).</t>
-        </is>
-      </c>
+      <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13207,11 +11754,7 @@
           <t>0:240, 31:0.5 | 0:240, 26:0.5</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>Just a cracker with tasty sauce, but dang, that's tasty (+240 HP).</t>
-        </is>
-      </c>
+      <c r="G358" t="inlineStr"/>
       <c r="H358" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13245,11 +11788,7 @@
           <t>0:300, 31:0.7 | 0:300, 26:0.7</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>Pre-chewed for convenience. Yum! (+300 HP).</t>
-        </is>
-      </c>
+      <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr"/>
     </row>
     <row r="360">
@@ -13279,11 +11818,7 @@
           <t>0:100 | 0:100</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>Dried food with a very particular mouthfeel (+100 HP).</t>
-        </is>
-      </c>
+      <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr"/>
     </row>
     <row r="361">
@@ -13313,11 +11848,7 @@
           <t>0:120, 14:90 | 0:120, 14:75</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>Extremely smelly and rotten tofu (+120 HP, 90% Silence).</t>
-        </is>
-      </c>
+      <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
     </row>
     <row r="362">
@@ -13347,11 +11878,7 @@
           <t xml:space="preserve">54:0.2 | </t>
         </is>
       </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>Food that smells like a public toilet that has gone uncleaned for years.</t>
-        </is>
-      </c>
+      <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -13385,11 +11912,7 @@
           <t xml:space="preserve">54:0.5 | </t>
         </is>
       </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>So malodorous it's been mistaken for a chemical weapon.</t>
-        </is>
-      </c>
+      <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -13423,11 +11946,7 @@
           <t xml:space="preserve">1:10 | </t>
         </is>
       </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>Candy that makes your mouth all sticky (+10 TP).</t>
-        </is>
-      </c>
+      <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
     </row>
     <row r="365">
@@ -13457,11 +11976,7 @@
           <t>1:31, 6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>Colorful candy that is kneaded with two sticks (+31 TP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13495,11 +12010,7 @@
           <t>1:46, 6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>An amber candy (+46 TP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr"/>
     </row>
     <row r="367">
@@ -13529,11 +12040,7 @@
           <t>1:75, 6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>Intensely sweet sugar candy (+75 TP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr"/>
     </row>
     <row r="368">
@@ -13563,11 +12070,7 @@
           <t>1:150, 37:0.75 | 37:0.95</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>Eat a long candy, live a long life. It's just math (+150 TP).</t>
-        </is>
-      </c>
+      <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13601,11 +12104,7 @@
           <t>5:666, 34:0.95 | 3:666, 34:0.95</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>An extremely rare, top-notch candy from the demon world (Party: +666 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13639,11 +12138,7 @@
           <t>0:80, 25:0.35 | 0:80, 25:0.35</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>Meatball patty with conspicuous chunks of onion (+35% ATK).</t>
-        </is>
-      </c>
+      <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr"/>
     </row>
     <row r="371">
@@ -13673,11 +12168,7 @@
           <t>0:300, 25:0.75 | 0:300, 25:0.75</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>Sunny-side up egg on a patty. When to break the yolk...? (+75% ATK).</t>
-        </is>
-      </c>
+      <c r="G371" t="inlineStr"/>
       <c r="H371" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13711,11 +12202,7 @@
           <t>27:0.25 | 27:0.25</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>The carbonation feels good as it slides down your throat (Speed +25%.).</t>
-        </is>
-      </c>
+      <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13749,11 +12236,7 @@
           <t>29:0.25 | 29:0.25</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>It's sweet and spicy... What evil genius came up with this?? (+25% DEF).</t>
-        </is>
-      </c>
+      <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -13787,11 +12270,7 @@
           <t>27:0.5, 29:0.5 | 27:0.5, 29:0.5</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>Hard to understand the point. Unbearably hot (+50% DEF).</t>
-        </is>
-      </c>
+      <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -13825,11 +12304,7 @@
           <t>0:200 | 0:200</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>Wafer sandwich, fully-packed with red beans (+200 HP).</t>
-        </is>
-      </c>
+      <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr"/>
     </row>
     <row r="376">
@@ -13859,11 +12334,7 @@
           <t>19:95 | 19:35</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>An ominous monaka in the shape of a coffin (95% Death).</t>
-        </is>
-      </c>
+      <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
     </row>
     <row r="377">
@@ -13893,11 +12364,7 @@
           <t>0:400, 37:0.75 | 0:400, 37:0.75</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>Sesame, white bean paste, and... red bean paste! (+400 HP).</t>
-        </is>
-      </c>
+      <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -13931,11 +12398,7 @@
           <t>0:75 | 0:75</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>A tiny, yet expensive, pastry (+75 HP).</t>
-        </is>
-      </c>
+      <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr"/>
     </row>
     <row r="379">
@@ -13965,11 +12428,7 @@
           <t>0:150, 37:0.75 | 0:150, 37:0.75</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>Bright macarons with an assortment of colors (+150 HP).</t>
-        </is>
-      </c>
+      <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14003,11 +12462,7 @@
           <t>0:50, 26:0.75 | 26:0.75</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>Cookies for your iron abs (+75% DEF).</t>
-        </is>
-      </c>
+      <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
     </row>
     <row r="381">
@@ -14037,11 +12492,7 @@
           <t>0:100, 25:0.5 | 0:100, 25:0.5</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>Cake for your swole six-pack (+50% ATK).</t>
-        </is>
-      </c>
+      <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr"/>
     </row>
     <row r="382">
@@ -14071,11 +12522,7 @@
           <t>0:300, 41:0.75 | 0:300, 41:0.75</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>Staple food on Planet Muscle. Go from ripped to jacked (+300 HP).</t>
-        </is>
-      </c>
+      <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14109,11 +12556,7 @@
           <t>1:55, 16:10 | 16:5</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>Apple drink. Sweet, spiked, or sparkling (+55 TP, 10% Sleep).</t>
-        </is>
-      </c>
+      <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr"/>
     </row>
     <row r="384">
@@ -14143,11 +12586,7 @@
           <t>1:74, 16:25 | 16:12</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>Mellow, rich, and just the right amount of bitter (+74 TP, 25% Sleep).</t>
-        </is>
-      </c>
+      <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr"/>
     </row>
     <row r="385">
@@ -14177,11 +12616,7 @@
           <t>1:140, 16:35 | 16:17</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>Sultry spirit. The perfect apertif (+140 TP, 35% Sleep).</t>
-        </is>
-      </c>
+      <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
     </row>
     <row r="386">
@@ -14211,11 +12646,7 @@
           <t>1:999, 16:45 | 16:22</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>The oil of conversation. The philosophic wine (+999 TP, 45% Sleep).</t>
-        </is>
-      </c>
+      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
     </row>
     <row r="387">
@@ -14245,11 +12676,7 @@
           <t>1:20, 14:40 | 14:20</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>You know you should stop but you just can't kelp yourself (+20 TP, 40% Silence).</t>
-        </is>
-      </c>
+      <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14283,11 +12710,7 @@
           <t>1:30, 14:60 | 14:30</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>Sandfish simmered in sugar and soy sauce (+30 TP, 60% Silence).</t>
-        </is>
-      </c>
+      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
     </row>
     <row r="389">
@@ -14317,12 +12740,7 @@
           <t>1:40, 14:60 | 14:30</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>If you get served this without a warning, you're the butt of a joke.
-(+40 TP, 60% Silence)</t>
-        </is>
-      </c>
+      <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14356,11 +12774,7 @@
           <t>1:50, 14:60 | 14:30</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>Bad looks and worse texture but weirdly addictive (+50 TP, 60% Silence).</t>
-        </is>
-      </c>
+      <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14394,12 +12808,7 @@
           <t>3:160, 39:0.2 | 3:160, 39:0.4</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>Flatten an octopus and this is what you get. There's plenty to go around.
-(Party: +160 HP)</t>
-        </is>
-      </c>
+      <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14433,11 +12842,7 @@
           <t>0:400, 25:0.5 | 0:400, 25:0.8</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>Rice with big ol' chunks of tentacle (+50% ATK).</t>
-        </is>
-      </c>
+      <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr"/>
     </row>
     <row r="393">
@@ -14467,11 +12872,7 @@
           <t xml:space="preserve">1:125 | </t>
         </is>
       </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>Completely, utterly, absolutely flavorless (+125 TP).</t>
-        </is>
-      </c>
+      <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr"/>
     </row>
     <row r="394">
@@ -14501,11 +12902,7 @@
           <t>2:200 | 0:200</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>Apparently the primary source of sustenance for one particular race (+200 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14539,11 +12936,7 @@
           <t xml:space="preserve">1:20 | </t>
         </is>
       </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>A foreign snack smothered in syrupy goodness (+20 TP).</t>
-        </is>
-      </c>
+      <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
     </row>
     <row r="396">
@@ -14573,11 +12966,7 @@
           <t xml:space="preserve">1:44 | </t>
         </is>
       </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>Tastes... sweet. Nothing but sweet. Not to be confused with balaclava (+44 TP).</t>
-        </is>
-      </c>
+      <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14611,11 +13000,7 @@
           <t xml:space="preserve">1:72 | </t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>A runny, sugary snack. The calorie content must be through the roof (+72 TP).</t>
-        </is>
-      </c>
+      <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14649,11 +13034,7 @@
           <t>1:98, 37:0.5 | 37:0.5</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>Spiral sweet soaked in sugary syrup (+98 TP).</t>
-        </is>
-      </c>
+      <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
     </row>
     <row r="399">
@@ -14683,11 +13064,7 @@
           <t xml:space="preserve">1:25 | </t>
         </is>
       </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>Rather bland-tasting. A wholly disappointing dish (+25 TP).</t>
-        </is>
-      </c>
+      <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
     </row>
     <row r="400">
@@ -14717,11 +13094,7 @@
           <t>1:60, 6:1 | 6:1</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>Fluffy food with a mesh pattern (+60 TP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr"/>
     </row>
     <row r="401">
@@ -14751,11 +13124,7 @@
           <t>1:50, 23:1 | 23:1</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>Waffle made with rice flour. Comes out mochi-ish (+50 TP, Clear Debuffs).</t>
-        </is>
-      </c>
+      <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14789,11 +13158,7 @@
           <t>1:85, 7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>A sweet waffle with syrup mixed into the batter (+85 TP, Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14827,11 +13192,7 @@
           <t>1:160, 7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>Luxury pancakes like you only get at overpriced hotels (+160 TP, Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14865,11 +13226,7 @@
           <t xml:space="preserve">1:30 | </t>
         </is>
       </c>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>Which end do you eat it from? It's a matter of scholarly debate (+30 TP).</t>
-        </is>
-      </c>
+      <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14903,11 +13260,7 @@
           <t>0:58 | 0:58</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>Tough rye bread that poses a challenge for seniors with weak teeth (+58 HP).</t>
-        </is>
-      </c>
+      <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14941,11 +13294,7 @@
           <t>0:400, 31:0.8 | 0:400, 26:0.8</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>Red bean bun baked with fine gold wheat. Diabetics should avoid it (+400 HP).</t>
-        </is>
-      </c>
+      <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -14979,11 +13328,7 @@
           <t>0:75 | 0:75</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>Snack made by frying sliced potatoes. Also known as crisps (+75 HP).</t>
-        </is>
-      </c>
+      <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr"/>
     </row>
     <row r="408">
@@ -15013,11 +13358,7 @@
           <t>0:120, 29:0.75 | 0:120, 29:0.75</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>Potato chips covered with habanero powder (+75% DEF).</t>
-        </is>
-      </c>
+      <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -15051,11 +13392,7 @@
           <t>25:0.4, 11:70 | 25:0.4, 11:30</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>Potato chips that'll blow your top (+40% ATK).</t>
-        </is>
-      </c>
+      <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr"/>
     </row>
     <row r="410">
@@ -15085,11 +13422,7 @@
           <t>0:20 | 0:20</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>Nana always has one or two in her bag. It's the law (+20 HP).</t>
-        </is>
-      </c>
+      <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr"/>
     </row>
     <row r="411">
@@ -15119,11 +13452,7 @@
           <t>0:70 | 0:70</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>Invokes the undeniable urge to rap. You'll be a real Kandy-e West (+70 HP).</t>
-        </is>
-      </c>
+      <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15157,11 +13486,7 @@
           <t>0:150 | 0:150</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>A high-class rusk coated in white chocolate. Mindblowingly delicious (+150 HP).</t>
-        </is>
-      </c>
+      <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15195,11 +13520,7 @@
           <t>0:300, 14:30 | 0:300, 14:15</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>A candy so sweet it will cause your brain to melt (+300 HP, 30% Silence).</t>
-        </is>
-      </c>
+      <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15233,11 +13554,7 @@
           <t>13:25 | 13:25</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>So spicy it makes your eyes hurt (25% Paralysis).</t>
-        </is>
-      </c>
+      <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr"/>
     </row>
     <row r="415">
@@ -15267,11 +13584,7 @@
           <t>0:50, 20:1 | 0:50, 20:1</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>Eat it and you'll sweat from every orifice you've got (+50 HP, Cure Freeze).</t>
-        </is>
-      </c>
+      <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15305,11 +13618,7 @@
           <t>2:75, 13:15 | 0:75, 13:15</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>First-timers will lose consciousness due to the spice (+75 HP/TP, 15% Paralysis).</t>
-        </is>
-      </c>
+      <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15343,12 +13652,7 @@
           <t>0:400, 14:80 | 0:400, 14:40</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>So spicy, it's out of this world. Just one phone call and they'll deliver.
-(+400 HP, 80% Silence)</t>
-        </is>
-      </c>
+      <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15382,11 +13686,7 @@
           <t>0:90 | 0:90</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>Fresh, warm donut (+90 HP).</t>
-        </is>
-      </c>
+      <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr"/>
     </row>
     <row r="419">
@@ -15416,11 +13716,7 @@
           <t>0:200 | 0:200</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>Donut with red bean paste on the inside, sugar coating on the outside (+200 HP).</t>
-        </is>
-      </c>
+      <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15454,11 +13750,7 @@
           <t xml:space="preserve">1:25 | </t>
         </is>
       </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>Sweet and tasty almond-flavored tofu (+25 TP).</t>
-        </is>
-      </c>
+      <c r="G420" t="inlineStr"/>
       <c r="H420" t="inlineStr"/>
     </row>
     <row r="421">
@@ -15488,11 +13780,7 @@
           <t>1:100, 29:0.5 | 29:0.5</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>Exquisite and jiggly almond-flavored tofu (+50% DEF).</t>
-        </is>
-      </c>
+      <c r="G421" t="inlineStr"/>
       <c r="H421" t="inlineStr">
         <is>
           <t>has an effect that is not decoded</t>
@@ -15526,11 +13814,7 @@
           <t>0:130 | 0:130</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>A fish-shaped cake filled with red beans from head to tail (+130 HP).</t>
-        </is>
-      </c>
+      <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr"/>
     </row>
     <row r="423">
@@ -15560,11 +13844,7 @@
           <t>0:200, 1:40 | 0:200</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>Taiyaki with matcha mixed into the batter. Looks a little gross (+200 HP, +40 TP).</t>
-        </is>
-      </c>
+      <c r="G423" t="inlineStr"/>
       <c r="H423" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15598,11 +13878,7 @@
           <t xml:space="preserve">1:40 | </t>
         </is>
       </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>The shrooms of the hills despise the coddled city bamboo shoots (+40 TP).</t>
-        </is>
-      </c>
+      <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15636,11 +13912,7 @@
           <t>1:40, 23:1 | 23:1</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>Safe, cheap, and tropical (+40 TP, Clear Debuffs).</t>
-        </is>
-      </c>
+      <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr"/>
     </row>
     <row r="426">
@@ -15670,11 +13942,7 @@
           <t>43:0.25 | 43:0.5</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>The mushroom formerly known as matsutake. They're... fine.</t>
-        </is>
-      </c>
+      <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15708,11 +13976,7 @@
           <t>41:0.5 | 41:0.95</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>Yellow with red spots. Eat it, and you might get bigger.</t>
-        </is>
-      </c>
+      <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15746,11 +14010,7 @@
           <t xml:space="preserve">1:40 | </t>
         </is>
       </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>The perfect dessert for a hot day (+40 TP).</t>
-        </is>
-      </c>
+      <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr"/>
     </row>
     <row r="429">
@@ -15780,11 +14040,7 @@
           <t xml:space="preserve">1:75 | </t>
         </is>
       </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>Shaved ice with some joyous rice-flour dumplings (+75 TP).</t>
-        </is>
-      </c>
+      <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr"/>
     </row>
     <row r="430">
@@ -15814,11 +14070,7 @@
           <t>1:160, 20:1 | 20:1</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>Refrigerated agar with added beans and fruits (+160 TP, Cure Freeze).</t>
-        </is>
-      </c>
+      <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr"/>
     </row>
     <row r="431">
@@ -15848,11 +14100,7 @@
           <t>0:105 | 0:105</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>A grab bag of vegetables! Rabbit food. Hooray (+105 HP).</t>
-        </is>
-      </c>
+      <c r="G431" t="inlineStr"/>
       <c r="H431" t="inlineStr"/>
     </row>
     <row r="432">
@@ -15882,11 +14130,7 @@
           <t xml:space="preserve">1:45 | </t>
         </is>
       </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>Salad showered with colorful flower petals (+45 TP).</t>
-        </is>
-      </c>
+      <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr"/>
     </row>
     <row r="433">
@@ -15916,11 +14160,7 @@
           <t xml:space="preserve">1:135 | </t>
         </is>
       </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>An assortment of sweet fruits (+135 TP).</t>
-        </is>
-      </c>
+      <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr"/>
     </row>
     <row r="434">
@@ -15950,11 +14190,7 @@
           <t xml:space="preserve">1:150 | </t>
         </is>
       </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>Opulent Chinese vegetable dish. Contains no meat. For some reason (+150 TP).</t>
-        </is>
-      </c>
+      <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -15988,12 +14224,7 @@
           <t>0:100, 6:1 | 0:100, 6:1</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>This sticky pudding is speckled with raisins. It's just pudding. Honestly.
-(+100 HP, Cure 1 Ailment)</t>
-        </is>
-      </c>
+      <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16027,11 +14258,7 @@
           <t>0:280, 6:1 | 0:280, 6:1</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>A cakey treat filled with delicious red bean paste (+280 HP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16065,11 +14292,7 @@
           <t>1:125, 44:0.65 | 44:0.8</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>Ol' reliable. You can't go wrong with bean paste (+125 TP).</t>
-        </is>
-      </c>
+      <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16103,11 +14326,7 @@
           <t>4:10, 34:0.2 | 34:0.3</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>Soup made wholly out of leftovers. Liver and let die! (Party: +10 TP).</t>
-        </is>
-      </c>
+      <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16141,11 +14360,7 @@
           <t>4:25, 34:0.4 | 34:0.5</t>
         </is>
       </c>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>The unagi's not necessarily good, but the sauce is (Party: +25 TP).</t>
-        </is>
-      </c>
+      <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16179,11 +14394,7 @@
           <t>4:50, 34:0.6 | 34:0.7</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>Dead eels on rice. It's terrible, you wouldn't want any (Party: +50 TP).</t>
-        </is>
-      </c>
+      <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16217,12 +14428,7 @@
           <t>2:30, 14:50 | 0:30, 14:25</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>Sushi roll containing sticky, smelly, fermented soybeans. Yum...?
-(+30 HP/TP, 50% Silence)</t>
-        </is>
-      </c>
+      <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16256,11 +14462,7 @@
           <t>2:60, 14:60 | 0:60, 14:30</t>
         </is>
       </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>You must be mindful of your surroundings when eating this (+60 HP/TP, 60% Silence).</t>
-        </is>
-      </c>
+      <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16294,11 +14496,7 @@
           <t>2:100, 14:70 | 0:100, 14:35</t>
         </is>
       </c>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>Extremely smelly... but somehow delicious (+100 HP/TP, 70% Silence).</t>
-        </is>
-      </c>
+      <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr"/>
     </row>
     <row r="444">
@@ -16328,11 +14526,7 @@
           <t>0:40, 26:0.3 | 0:40, 26:0.3</t>
         </is>
       </c>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>Silky-smooth little fish, rich in calcium (+30% DEF).</t>
-        </is>
-      </c>
+      <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr"/>
     </row>
     <row r="445">
@@ -16362,11 +14556,7 @@
           <t>0:100, 11:40 | 0:80, 11:20</t>
         </is>
       </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>Somewhat grotesque when the fish has the face of a man (+100 HP, 40% Blind).</t>
-        </is>
-      </c>
+      <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16400,11 +14590,7 @@
           <t>0:120, 26:0.6 | 0:120, 26:0.6</t>
         </is>
       </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>Well dried bonito flakes (+60% DEF).</t>
-        </is>
-      </c>
+      <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr"/>
     </row>
     <row r="447">
@@ -16434,11 +14620,7 @@
           <t>0:200, 26:0.8 | 0:200, 26:0.8</t>
         </is>
       </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>Bonito so dry it's a blunt weapon. The world's hardest food (+80% DEF).</t>
-        </is>
-      </c>
+      <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16472,11 +14654,7 @@
           <t xml:space="preserve">1:18 | </t>
         </is>
       </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>Cucumber sushi. The kappa's favorite (+18 TP).</t>
-        </is>
-      </c>
+      <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
     </row>
     <row r="449">
@@ -16506,11 +14684,7 @@
           <t>0:50, 1:10 | 0:50</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>A simple but deep sushi. Make this your last order to look cultured (+50 HP, +10 TP).</t>
-        </is>
-      </c>
+      <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16544,12 +14718,7 @@
           <t>7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G450" t="inlineStr">
-        <is>
-          <t>Bitter jelly allegedly good for the skin. Not so great for the tortoise.
-(Cure All Ailments)</t>
-        </is>
-      </c>
+      <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16583,11 +14752,7 @@
           <t>7:1, 41:0.4 | 7:1, 41:0.8</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>Genuine, honest, real turtle soup! Would I lie to you? (Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16621,12 +14786,7 @@
           <t>7:1, 1:125 | 7:1</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>Made in an earthenware pot at high temperature. Delicious but steep.
-(+125 TP, Cure All Ailments)</t>
-        </is>
-      </c>
+      <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16660,11 +14820,7 @@
           <t>0:100 | 0:100</t>
         </is>
       </c>
-      <c r="G453" t="inlineStr">
-        <is>
-          <t>Regular size, smothered with sauce please! (+100 HP).</t>
-        </is>
-      </c>
+      <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr"/>
     </row>
     <row r="454">
@@ -16694,11 +14850,7 @@
           <t>0:150, 25:0.5 | 0:150, 25:0.5</t>
         </is>
       </c>
-      <c r="G454" t="inlineStr">
-        <is>
-          <t>Bento with only meat and rice. Get those veggies out of here! (+50% ATK).</t>
-        </is>
-      </c>
+      <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16732,11 +14884,7 @@
           <t>0:200, 25:0.7 | 0:200, 25:0.7</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr">
-        <is>
-          <t>Sukiyaki bento with super luxurious wagyu included (+70% ATK).</t>
-        </is>
-      </c>
+      <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16770,11 +14918,7 @@
           <t>0:400, 25:0.9 | 0:400, 25:0.9</t>
         </is>
       </c>
-      <c r="G456" t="inlineStr">
-        <is>
-          <t>Steak bento so delicious it'll make you dizzy (+90% ATK).</t>
-        </is>
-      </c>
+      <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
     </row>
     <row r="457">
@@ -16804,11 +14948,7 @@
           <t>12:60 | 12:20</t>
         </is>
       </c>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>A liquid formed from the drool of the elusive nuko (60% Poison).</t>
-        </is>
-      </c>
+      <c r="G457" t="inlineStr"/>
       <c r="H457" t="inlineStr"/>
     </row>
     <row r="458">
@@ -16838,11 +14978,7 @@
           <t>1:30 | 57:1</t>
         </is>
       </c>
-      <c r="G458" t="inlineStr">
-        <is>
-          <t>Sake with silver vine for added energy. Do it for the vine! (+30 TP).</t>
-        </is>
-      </c>
+      <c r="G458" t="inlineStr"/>
       <c r="H458" t="inlineStr"/>
     </row>
     <row r="459">
@@ -16872,11 +15008,7 @@
           <t xml:space="preserve">1:60 | </t>
         </is>
       </c>
-      <c r="G459" t="inlineStr">
-        <is>
-          <t>Try to point out that it's yellow, and a rep will appear to call it gold (+60 TP).</t>
-        </is>
-      </c>
+      <c r="G459" t="inlineStr"/>
       <c r="H459" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16910,11 +15042,7 @@
           <t>1:75, 19:20 | 19:10</t>
         </is>
       </c>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>Don't drink too much if you like your brain cells (+75 TP).</t>
-        </is>
-      </c>
+      <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -16948,11 +15076,7 @@
           <t>0:80 | 0:80</t>
         </is>
       </c>
-      <c r="G461" t="inlineStr">
-        <is>
-          <t>It takes a lot of effort to make (+80 HP).</t>
-        </is>
-      </c>
+      <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr"/>
     </row>
     <row r="462">
@@ -16982,12 +15106,7 @@
           <t>0:135, 22:1 | 0:135, 22:1</t>
         </is>
       </c>
-      <c r="G462" t="inlineStr">
-        <is>
-          <t>Cheap and delicious. Sometimes filled with strawberry or pudding.
-(+135 HP, Cure Shadow Sew)</t>
-        </is>
-      </c>
+      <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17021,11 +15140,7 @@
           <t>0:225, 6:1 | 0:225, 6:1</t>
         </is>
       </c>
-      <c r="G463" t="inlineStr">
-        <is>
-          <t>Mochi with mugwort. You can never have too much mugwort! (+225 HP, Cure 1 Ailment).</t>
-        </is>
-      </c>
+      <c r="G463" t="inlineStr"/>
       <c r="H463" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17059,11 +15174,7 @@
           <t>0:342, 23:1 | 0:342, 23:1</t>
         </is>
       </c>
-      <c r="G464" t="inlineStr">
-        <is>
-          <t>An offering to a certain god (+342 HP, Clear Debuffs).</t>
-        </is>
-      </c>
+      <c r="G464" t="inlineStr"/>
       <c r="H464" t="inlineStr"/>
     </row>
     <row r="465">
@@ -17093,11 +15204,7 @@
           <t>0:38 | 0:38</t>
         </is>
       </c>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>An inexpensive little cupful of cake (+38 HP).</t>
-        </is>
-      </c>
+      <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr"/>
     </row>
     <row r="466">
@@ -17127,11 +15234,7 @@
           <t>0:100 | 0:100</t>
         </is>
       </c>
-      <c r="G466" t="inlineStr">
-        <is>
-          <t>The perfect mid-afternoon snack. Loved by all (+100 HP).</t>
-        </is>
-      </c>
+      <c r="G466" t="inlineStr"/>
       <c r="H466" t="inlineStr"/>
     </row>
     <row r="467">
@@ -17161,11 +15264,7 @@
           <t>0:200, 26:0.25 | 0:200, 26:0.25</t>
         </is>
       </c>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>If you don't handle it with care, the cream will spurt all over you (+25% DEF).</t>
-        </is>
-      </c>
+      <c r="G467" t="inlineStr"/>
       <c r="H467" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17199,11 +15298,7 @@
           <t>3:125 | 3:125</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>Roll-shaped cake that people line up for ages to get (Party: +125 HP).</t>
-        </is>
-      </c>
+      <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr"/>
     </row>
     <row r="469">
@@ -17233,11 +15328,7 @@
           <t>3:180, 35:0.25 | 3:180, 35:0.25</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>Triple-stack of pancakes smothered in sticky maple syrup (Party: +180 HP).</t>
-        </is>
-      </c>
+      <c r="G469" t="inlineStr"/>
       <c r="H469" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17271,11 +15362,7 @@
           <t>0:300, 37:0.25 | 0:300, 37:0.25</t>
         </is>
       </c>
-      <c r="G470" t="inlineStr">
-        <is>
-          <t>It means white mountain. And yet, yellow cake. Y u do dis? (+300 HP).</t>
-        </is>
-      </c>
+      <c r="G470" t="inlineStr"/>
       <c r="H470" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17309,11 +15396,7 @@
           <t>0:400, 38:0.25 | 0:400, 38:0.25</t>
         </is>
       </c>
-      <c r="G471" t="inlineStr">
-        <is>
-          <t>Sweetness and justice are synonymous (+25% EVA).</t>
-        </is>
-      </c>
+      <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr"/>
     </row>
     <row r="472">
@@ -17343,11 +15426,7 @@
           <t>3:300, 39:0.25 | 3:300, 39:0.25</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr">
-        <is>
-          <t>A multi-layered, doughy pie cake (Party: +300 HP).</t>
-        </is>
-      </c>
+      <c r="G472" t="inlineStr"/>
       <c r="H472" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17381,11 +15460,7 @@
           <t>4:200, 36:0.4 | 36:0.4</t>
         </is>
       </c>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>A luxury item perfect for souvenirs or gift exchanges (Party: +200 TP).</t>
-        </is>
-      </c>
+      <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17419,11 +15494,7 @@
           <t>0:60, 1:15 | 0:60</t>
         </is>
       </c>
-      <c r="G474" t="inlineStr">
-        <is>
-          <t>Maple leaf-shaped souvenir confection. Even better as ice cream (+60 HP, +15 TP).</t>
-        </is>
-      </c>
+      <c r="G474" t="inlineStr"/>
       <c r="H474" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17457,11 +15528,7 @@
           <t>0:125, 16:40 | 0:125, 16:20</t>
         </is>
       </c>
-      <c r="G475" t="inlineStr">
-        <is>
-          <t>Liquor brewed from millet. Its mature flavor can become a habit (+125 HP, 40% Sleep).</t>
-        </is>
-      </c>
+      <c r="G475" t="inlineStr"/>
       <c r="H475" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17495,12 +15562,7 @@
           <t>0:165, 11:20 | 0:165, 11:10</t>
         </is>
       </c>
-      <c r="G476" t="inlineStr">
-        <is>
-          <t>The mascot creature of this chocolate has yet to be identified by science.
-(+165 HP, 20% Blind)</t>
-        </is>
-      </c>
+      <c r="G476" t="inlineStr"/>
       <c r="H476" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17534,11 +15596,7 @@
           <t>0:200, 43:0.25 | 0:200, 43:0.25</t>
         </is>
       </c>
-      <c r="G477" t="inlineStr">
-        <is>
-          <t>Canned whale. Slowly vanishing from shelves (+200 HP).</t>
-        </is>
-      </c>
+      <c r="G477" t="inlineStr"/>
       <c r="H477" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17572,11 +15630,7 @@
           <t>3:240, 69:1 | 3:240, 69:1</t>
         </is>
       </c>
-      <c r="G478" t="inlineStr">
-        <is>
-          <t>What you get when you toss a chunk of whale in your soup (Party: +240 HP).</t>
-        </is>
-      </c>
+      <c r="G478" t="inlineStr"/>
       <c r="H478" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17610,11 +15664,7 @@
           <t>3:400, 36:0.6 | 3:400, 36:0.6</t>
         </is>
       </c>
-      <c r="G479" t="inlineStr">
-        <is>
-          <t>Simple hotpot of whale and mizuna (Party: +400 HP).</t>
-        </is>
-      </c>
+      <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr"/>
     </row>
     <row r="480">
@@ -17644,11 +15694,7 @@
           <t>0:50 | 0:50</t>
         </is>
       </c>
-      <c r="G480" t="inlineStr">
-        <is>
-          <t>Way too simple of a food. Really. It's just wheat (+50 HP).</t>
-        </is>
-      </c>
+      <c r="G480" t="inlineStr"/>
       <c r="H480" t="inlineStr"/>
     </row>
     <row r="481">
@@ -17678,11 +15724,7 @@
           <t>0:120, 20:1 | 0:150, 20:1</t>
         </is>
       </c>
-      <c r="G481" t="inlineStr">
-        <is>
-          <t>Filled with meat and veggies! Very delicious (+120 HP, Cure Freeze).</t>
-        </is>
-      </c>
+      <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr"/>
     </row>
     <row r="482">
@@ -17712,11 +15754,7 @@
           <t>0:180, 20:1 | 0:300, 20:1</t>
         </is>
       </c>
-      <c r="G482" t="inlineStr">
-        <is>
-          <t>Warms your body to the core on a cold day (+180 HP, Cure Freeze).</t>
-        </is>
-      </c>
+      <c r="G482" t="inlineStr"/>
       <c r="H482" t="inlineStr"/>
     </row>
     <row r="483">
@@ -17746,11 +15784,7 @@
           <t>52:10, 28:0.2 | 52:10, 28:0.1</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr">
-        <is>
-          <t>Jelly made with copious amounts of slime (Speed DOWN -20%.).</t>
-        </is>
-      </c>
+      <c r="G483" t="inlineStr"/>
       <c r="H483" t="inlineStr"/>
     </row>
     <row r="484">
@@ -17780,11 +15814,7 @@
           <t>52:30, 28:0.1 | 52:30, 28:0.05</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr">
-        <is>
-          <t>Made from only the gloopiest cuts of the slime (Speed DOWN -10%.).</t>
-        </is>
-      </c>
+      <c r="G484" t="inlineStr"/>
       <c r="H484" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17818,11 +15848,7 @@
           <t>52:50, 28:0.4 | 52:50, 28:0.2</t>
         </is>
       </c>
-      <c r="G485" t="inlineStr">
-        <is>
-          <t>So chewy it'll tire out your jaw (Speed DOWN -40%.).</t>
-        </is>
-      </c>
+      <c r="G485" t="inlineStr"/>
       <c r="H485" t="inlineStr"/>
     </row>
     <row r="486">
@@ -17852,11 +15878,7 @@
           <t>53:50, 40:0.75 | 53:50, 40:0.75</t>
         </is>
       </c>
-      <c r="G486" t="inlineStr">
-        <is>
-          <t>Bavarian cream filled with tons of slime. Appetizing, isn't it?</t>
-        </is>
-      </c>
+      <c r="G486" t="inlineStr"/>
       <c r="H486" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17890,11 +15912,7 @@
           <t>30:0.5 | 25:0.5</t>
         </is>
       </c>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t>Spray that turns you into a super sadist for a few minutes (+50% ATK).</t>
-        </is>
-      </c>
+      <c r="G487" t="inlineStr"/>
       <c r="H487" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17928,11 +15946,7 @@
           <t>30:0.75, 11:75 | 25:0.75, 11:25</t>
         </is>
       </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>The feeling of being foreign. You're a stranger in a strange land (+75% ATK).</t>
-        </is>
-      </c>
+      <c r="G488" t="inlineStr"/>
       <c r="H488" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -17966,12 +15980,7 @@
           <t>1:150, 7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G489" t="inlineStr">
-        <is>
-          <t>Can stuffed with dragon meat. Rare and expensive but a little smelly.
-(+150 TP, Cure All Ailments)</t>
-        </is>
-      </c>
+      <c r="G489" t="inlineStr"/>
       <c r="H489" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18005,11 +16014,7 @@
           <t>0:75, 16:30 | 0:75, 16:15</t>
         </is>
       </c>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>No alcohol until you're 21! (+75 HP, 30% Sleep).</t>
-        </is>
-      </c>
+      <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr"/>
     </row>
     <row r="491">
@@ -18039,12 +16044,7 @@
           <t>0:150, 16:15 | 0:150, 16:10</t>
         </is>
       </c>
-      <c r="G491" t="inlineStr">
-        <is>
-          <t>Some have never tried this sake, but none have tried it only once.
-(+150 HP, 15% Sleep)</t>
-        </is>
-      </c>
+      <c r="G491" t="inlineStr"/>
       <c r="H491" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18078,12 +16078,7 @@
           <t>0:300, 11:20 | 0:300, 11:15</t>
         </is>
       </c>
-      <c r="G492" t="inlineStr">
-        <is>
-          <t>Powerful sake that intoxicates even heavy drinkers. Super harsh flavor.
-(+300 HP, 20% Blind)</t>
-        </is>
-      </c>
+      <c r="G492" t="inlineStr"/>
       <c r="H492" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18117,11 +16112,7 @@
           <t>0:400, 16:20 | 0:400, 16:15</t>
         </is>
       </c>
-      <c r="G493" t="inlineStr">
-        <is>
-          <t>Port wine carefully aged for over a hundred years (+400 HP, 20% Sleep).</t>
-        </is>
-      </c>
+      <c r="G493" t="inlineStr"/>
       <c r="H493" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18155,11 +16146,7 @@
           <t>2:100 | 0:100</t>
         </is>
       </c>
-      <c r="G494" t="inlineStr">
-        <is>
-          <t>Would you like some fries with that? (+100 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr"/>
     </row>
     <row r="495">
@@ -18189,11 +16176,7 @@
           <t>2:150 | 0:150</t>
         </is>
       </c>
-      <c r="G495" t="inlineStr">
-        <is>
-          <t>Taste aside, it's stiff and difficult to eat (+150 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G495" t="inlineStr"/>
       <c r="H495" t="inlineStr"/>
     </row>
     <row r="496">
@@ -18223,11 +16206,7 @@
           <t>2:200, 13:50 | 0:200, 13:25</t>
         </is>
       </c>
-      <c r="G496" t="inlineStr">
-        <is>
-          <t>Dish made by shoving waterfowls into a dragon corpse (+200 HP/TP, 50% Paralysis).</t>
-        </is>
-      </c>
+      <c r="G496" t="inlineStr"/>
       <c r="H496" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18261,11 +16240,7 @@
           <t>2:260, 38:0.25 | 0:260, 38:0.25</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>A huge, hard egg. It's unbreakable (+25% EVA).</t>
-        </is>
-      </c>
+      <c r="G497" t="inlineStr"/>
       <c r="H497" t="inlineStr"/>
     </row>
     <row r="498">
@@ -18295,11 +16270,7 @@
           <t>0:200, 1:50 | 0:200</t>
         </is>
       </c>
-      <c r="G498" t="inlineStr">
-        <is>
-          <t>A snack so hard, you might chip a tooth when you bite into it (+200 HP, +50 TP).</t>
-        </is>
-      </c>
+      <c r="G498" t="inlineStr"/>
       <c r="H498" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18333,11 +16304,7 @@
           <t>5:200, 23:1 | 3:200, 23:1</t>
         </is>
       </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>Cloying, syrupy drink (Party: +250 HP/TP, Clear Debuffs).</t>
-        </is>
-      </c>
+      <c r="G499" t="inlineStr"/>
       <c r="H499" t="inlineStr"/>
     </row>
     <row r="500">
@@ -18367,11 +16334,7 @@
           <t>12:50 | 12:25</t>
         </is>
       </c>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>Meat so tender that it melts at the touch (50% Poison).</t>
-        </is>
-      </c>
+      <c r="G500" t="inlineStr"/>
       <c r="H500" t="inlineStr"/>
     </row>
     <row r="501">
@@ -18401,11 +16364,7 @@
           <t>12:70 | 12:35</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr">
-        <is>
-          <t>Meat is most delicious when it's almost rotten... or so they say (70% Poison).</t>
-        </is>
-      </c>
+      <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18439,12 +16398,7 @@
           <t>12:95, 13:80 | 12:50, 13:40</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t>Primitive meat that shines suspiciously. Basically steroids in meat form.
-(95% Poison, 80% Paralysis)</t>
-        </is>
-      </c>
+      <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18478,11 +16432,7 @@
           <t>2:20 | 0:20</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr">
-        <is>
-          <t>Rich milk. I drink your 2% milk, Eli! I drink it up! (+20 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G503" t="inlineStr"/>
       <c r="H503" t="inlineStr"/>
     </row>
     <row r="504">
@@ -18512,11 +16462,7 @@
           <t>0:100, 1:20 | 0:100</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr">
-        <is>
-          <t>Rich yogurt (+100 HP, +20 TP).</t>
-        </is>
-      </c>
+      <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr"/>
     </row>
     <row r="505">
@@ -18546,11 +16492,7 @@
           <t>0:200, 1:30 | 0:200</t>
         </is>
       </c>
-      <c r="G505" t="inlineStr">
-        <is>
-          <t>Rich cheese (+200 HP, +30 TP).</t>
-        </is>
-      </c>
+      <c r="G505" t="inlineStr"/>
       <c r="H505" t="inlineStr"/>
     </row>
     <row r="506">
@@ -18580,11 +16522,7 @@
           <t xml:space="preserve">4:60 | </t>
         </is>
       </c>
-      <c r="G506" t="inlineStr">
-        <is>
-          <t>Small candy with a rugged shape (Party: +60 TP).</t>
-        </is>
-      </c>
+      <c r="G506" t="inlineStr"/>
       <c r="H506" t="inlineStr"/>
     </row>
     <row r="507">
@@ -18614,11 +16552,7 @@
           <t>4:120, 22:1 | 22:1</t>
         </is>
       </c>
-      <c r="G507" t="inlineStr">
-        <is>
-          <t>A larger-scale konpeito (Party: +120 TP, Cure Shadow Sew).</t>
-        </is>
-      </c>
+      <c r="G507" t="inlineStr"/>
       <c r="H507" t="inlineStr"/>
     </row>
     <row r="508">
@@ -18648,11 +16582,7 @@
           <t>4:400, 42:0.5 | 42:0.8</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr">
-        <is>
-          <t>Konpeito as big as your fist (Party: +400 TP).</t>
-        </is>
-      </c>
+      <c r="G508" t="inlineStr"/>
       <c r="H508" t="inlineStr"/>
     </row>
     <row r="509">
@@ -18682,11 +16612,7 @@
           <t>2:100, 12:40 | 0:100, 12:10</t>
         </is>
       </c>
-      <c r="G509" t="inlineStr">
-        <is>
-          <t>Beverage squeezed out of an apple creature's insides (+100 HP/TP, 40% Poison).</t>
-        </is>
-      </c>
+      <c r="G509" t="inlineStr"/>
       <c r="H509" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18720,11 +16646,7 @@
           <t>2:200, 12:80 | 0:200, 12:20</t>
         </is>
       </c>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>A candy with a whole appler trapped inside (+200 HP/TP, 80% Poison).</t>
-        </is>
-      </c>
+      <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr"/>
     </row>
     <row r="511">
@@ -18754,11 +16676,7 @@
           <t>2:100, 13:90 | 0:100, 13:45</t>
         </is>
       </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>Beverage squeezed out of a melon creature's insides (+100 HP/TP, 90% Paralysis).</t>
-        </is>
-      </c>
+      <c r="G511" t="inlineStr"/>
       <c r="H511" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18792,12 +16710,7 @@
           <t>2:200, 13:80 | 0:200, 13:20</t>
         </is>
       </c>
-      <c r="G512" t="inlineStr">
-        <is>
-          <t>Unrelated to that anime character who lets people eat her face.
-(+200 HP/TP, 80% Paralysis)</t>
-        </is>
-      </c>
+      <c r="G512" t="inlineStr"/>
       <c r="H512" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18831,11 +16744,7 @@
           <t>2:100, 14:40 | 0:100, 14:10</t>
         </is>
       </c>
-      <c r="G513" t="inlineStr">
-        <is>
-          <t>Beverage squeezed out of a banana creature's insides (+100 HP/TP, 40% Silence).</t>
-        </is>
-      </c>
+      <c r="G513" t="inlineStr"/>
       <c r="H513" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -18869,11 +16778,7 @@
           <t>2:200, 14:80 | 0:200, 14:20</t>
         </is>
       </c>
-      <c r="G514" t="inlineStr">
-        <is>
-          <t>It's a big banana. Looks pretty sexy (+200 HP/TP, 80% Silence).</t>
-        </is>
-      </c>
+      <c r="G514" t="inlineStr"/>
       <c r="H514" t="inlineStr"/>
     </row>
     <row r="515">
@@ -18903,11 +16808,7 @@
           <t>11:10 | 11:10</t>
         </is>
       </c>
-      <c r="G515" t="inlineStr">
-        <is>
-          <t>A Fairy Mandra that's badly wounded (10% Blind).</t>
-        </is>
-      </c>
+      <c r="G515" t="inlineStr"/>
       <c r="H515" t="inlineStr"/>
     </row>
     <row r="516">
@@ -18937,11 +16838,7 @@
           <t>0:160 | 0:160</t>
         </is>
       </c>
-      <c r="G516" t="inlineStr">
-        <is>
-          <t>Best when stuck on a skewer and grilled (+160 HP).</t>
-        </is>
-      </c>
+      <c r="G516" t="inlineStr"/>
       <c r="H516" t="inlineStr"/>
     </row>
     <row r="517">
@@ -18971,11 +16868,7 @@
           <t>7:1 | 7:1</t>
         </is>
       </c>
-      <c r="G517" t="inlineStr">
-        <is>
-          <t>Can be used as herbal medicine. It has a strong scent (Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G517" t="inlineStr"/>
       <c r="H517" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19009,11 +16902,7 @@
           <t>4:150, 39:0.6 | 39:0.6</t>
         </is>
       </c>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>The trefoil of a mandra, used as a graduation charm (Party: +150 TP).</t>
-        </is>
-      </c>
+      <c r="G518" t="inlineStr"/>
       <c r="H518" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19047,11 +16936,7 @@
           <t>14:95, 15:95 | 14:99, 15:99</t>
         </is>
       </c>
-      <c r="G519" t="inlineStr">
-        <is>
-          <t>Made by grinding up mandras (95% Silence, 95% Freeze).</t>
-        </is>
-      </c>
+      <c r="G519" t="inlineStr"/>
       <c r="H519" t="inlineStr"/>
     </row>
     <row r="520">
@@ -19081,11 +16966,7 @@
           <t>12:15 | 12:15</t>
         </is>
       </c>
-      <c r="G520" t="inlineStr">
-        <is>
-          <t>An Otherworld Mandra that's badly wounded (15% Poison).</t>
-        </is>
-      </c>
+      <c r="G520" t="inlineStr"/>
       <c r="H520" t="inlineStr"/>
     </row>
     <row r="521">
@@ -19115,11 +16996,7 @@
           <t xml:space="preserve">1:80 | </t>
         </is>
       </c>
-      <c r="G521" t="inlineStr">
-        <is>
-          <t>Slice it thin and eat it like sashimi (+80 TP).</t>
-        </is>
-      </c>
+      <c r="G521" t="inlineStr"/>
       <c r="H521" t="inlineStr"/>
     </row>
     <row r="522">
@@ -19149,11 +17026,7 @@
           <t>0:350, 22:1 | 0:350, 22:1</t>
         </is>
       </c>
-      <c r="G522" t="inlineStr">
-        <is>
-          <t>Goes really well with meat rolls (+350 HP, Cure Shadow Sew).</t>
-        </is>
-      </c>
+      <c r="G522" t="inlineStr"/>
       <c r="H522" t="inlineStr"/>
     </row>
     <row r="523">
@@ -19183,11 +17056,7 @@
           <t>31:0.8 | 26:0.8</t>
         </is>
       </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>Too much of it will cause severe hallucinations. Not the good kind.</t>
-        </is>
-      </c>
+      <c r="G523" t="inlineStr"/>
       <c r="H523" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19221,11 +17090,7 @@
           <t>5:2000, 34:0.9 | 3:2000, 34:0.9</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>Freshly squeezed mandra juice. Nice and pulpy (Party: +2000 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G524" t="inlineStr"/>
       <c r="H524" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19259,11 +17124,7 @@
           <t>5:1000 | 3:1000</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr">
-        <is>
-          <t>Said to bring good fortune. Does anyone actually believe that? (Party: +1000 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G525" t="inlineStr"/>
       <c r="H525" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19297,11 +17158,7 @@
           <t>2:7 | 0:7</t>
         </is>
       </c>
-      <c r="G526" t="inlineStr">
-        <is>
-          <t>Freshly squeezed, straight from OC (+7 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G526" t="inlineStr"/>
       <c r="H526" t="inlineStr"/>
     </row>
     <row r="527">
@@ -19331,11 +17188,7 @@
           <t>2:14 | 0:14</t>
         </is>
       </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>Strange rice cooked with tangerine juice (+14 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G527" t="inlineStr"/>
       <c r="H527" t="inlineStr"/>
     </row>
     <row r="528">
@@ -19365,11 +17218,7 @@
           <t>2:45 | 0:45</t>
         </is>
       </c>
-      <c r="G528" t="inlineStr">
-        <is>
-          <t>A cafe au lait mixed with oranges. It's scalding hot (+45 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G528" t="inlineStr"/>
       <c r="H528" t="inlineStr"/>
     </row>
     <row r="529">
@@ -19399,11 +17248,7 @@
           <t>2:13 | 0:13</t>
         </is>
       </c>
-      <c r="G529" t="inlineStr">
-        <is>
-          <t>Full of vitamins. Have some after you exercise (+13 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G529" t="inlineStr"/>
       <c r="H529" t="inlineStr"/>
     </row>
     <row r="530">
@@ -19433,11 +17278,7 @@
           <t>2:22 | 0:22</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr">
-        <is>
-          <t>Sweet pie that's made with tons of cherries (+22 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G530" t="inlineStr"/>
       <c r="H530" t="inlineStr"/>
     </row>
     <row r="531">
@@ -19467,12 +17308,7 @@
           <t>2:50, 7:1 | 0:50, 7:1</t>
         </is>
       </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>Made in an attempt to achieve sake supremacy. To sake-cceed.
-(+50 HP/TP, Cure All Ailments)</t>
-        </is>
-      </c>
+      <c r="G531" t="inlineStr"/>
       <c r="H531" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19506,11 +17342,7 @@
           <t>1:1000, 44:0.9 | 44:0.9</t>
         </is>
       </c>
-      <c r="G532" t="inlineStr">
-        <is>
-          <t>The denizens of the world above say these pair well with tea (+1000 TP).</t>
-        </is>
-      </c>
+      <c r="G532" t="inlineStr"/>
       <c r="H532" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19544,11 +17376,7 @@
           <t xml:space="preserve">1:65 | </t>
         </is>
       </c>
-      <c r="G533" t="inlineStr">
-        <is>
-          <t>Moon cake with just the right level of sweetness (+65 TP).</t>
-        </is>
-      </c>
+      <c r="G533" t="inlineStr"/>
       <c r="H533" t="inlineStr"/>
     </row>
     <row r="534">
@@ -19578,11 +17406,7 @@
           <t>1:130, 43:0.75 | 43:0.75</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr">
-        <is>
-          <t>Rice cake that crumbles from the outside as you eat it (+130 TP).</t>
-        </is>
-      </c>
+      <c r="G534" t="inlineStr"/>
       <c r="H534" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19616,12 +17440,7 @@
           <t xml:space="preserve">1:999, 7:1 | </t>
         </is>
       </c>
-      <c r="G535" t="inlineStr">
-        <is>
-          <t>Precious, sweet-smelling beverage made of liquified mana crystals.
-(+999 TP, Cure All Ailments)</t>
-        </is>
-      </c>
+      <c r="G535" t="inlineStr"/>
       <c r="H535" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19655,11 +17474,7 @@
           <t xml:space="preserve">0:5000, 41:0.99 | </t>
         </is>
       </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>Dangerous drink that lights a fire in your loins. Yowch! That's hot! (+5000 HP).</t>
-        </is>
-      </c>
+      <c r="G536" t="inlineStr"/>
       <c r="H536" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19693,11 +17508,7 @@
           <t xml:space="preserve">24:9 | </t>
         </is>
       </c>
-      <c r="G537" t="inlineStr">
-        <is>
-          <t>Stained with the blood of sacrifice. It's golden underneath (+9 SP).</t>
-        </is>
-      </c>
+      <c r="G537" t="inlineStr"/>
       <c r="H537" t="inlineStr"/>
     </row>
     <row r="538">
@@ -19727,11 +17538,7 @@
           <t xml:space="preserve">20:1 | </t>
         </is>
       </c>
-      <c r="G538" t="inlineStr">
-        <is>
-          <t>The most treasured treasure of the Dragon Palace... cures Freeze (Cure Freeze).</t>
-        </is>
-      </c>
+      <c r="G538" t="inlineStr"/>
       <c r="H538" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19765,11 +17572,7 @@
           <t>40:0.95 | 40:0.95</t>
         </is>
       </c>
-      <c r="G539" t="inlineStr">
-        <is>
-          <t>Tender green bud held by the former ruler of the world.</t>
-        </is>
-      </c>
+      <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19803,11 +17606,7 @@
           <t xml:space="preserve">0:1000, 23:1 | </t>
         </is>
       </c>
-      <c r="G540" t="inlineStr">
-        <is>
-          <t>A magical egg. There's a whole new world inside it (+1000 HP, Clear Debuffs).</t>
-        </is>
-      </c>
+      <c r="G540" t="inlineStr"/>
       <c r="H540" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19841,11 +17640,7 @@
           <t xml:space="preserve">10:1 | </t>
         </is>
       </c>
-      <c r="G541" t="inlineStr">
-        <is>
-          <t>Proof that you've attended all of Miss Euthys's lectures (Escape Dungeon).</t>
-        </is>
-      </c>
+      <c r="G541" t="inlineStr"/>
       <c r="H541" t="inlineStr">
         <is>
           <t>original sentence shortened to fit</t>
@@ -19879,11 +17674,7 @@
           <t xml:space="preserve">1:50 | </t>
         </is>
       </c>
-      <c r="G542" t="inlineStr">
-        <is>
-          <t>A fruit from the garden of Paradise (+50 TP).</t>
-        </is>
-      </c>
+      <c r="G542" t="inlineStr"/>
       <c r="H542" t="inlineStr"/>
     </row>
     <row r="543">
@@ -19913,11 +17704,7 @@
           <t xml:space="preserve">7:1 | </t>
         </is>
       </c>
-      <c r="G543" t="inlineStr">
-        <is>
-          <t>Huskin' makes me feel good (Cure All Ailments).</t>
-        </is>
-      </c>
+      <c r="G543" t="inlineStr"/>
       <c r="H543" t="inlineStr"/>
     </row>
     <row r="544">
@@ -19947,11 +17734,7 @@
           <t xml:space="preserve">0:100 | </t>
         </is>
       </c>
-      <c r="G544" t="inlineStr">
-        <is>
-          <t>The original underlying form of all matter in the universe (+100 HP).</t>
-        </is>
-      </c>
+      <c r="G544" t="inlineStr"/>
       <c r="H544" t="inlineStr"/>
     </row>
     <row r="545">
@@ -19981,11 +17764,7 @@
           <t xml:space="preserve">2:10 | </t>
         </is>
       </c>
-      <c r="G545" t="inlineStr">
-        <is>
-          <t>Dry and dead. It won't grow into anything more (+10 HP/TP).</t>
-        </is>
-      </c>
+      <c r="G545" t="inlineStr"/>
       <c r="H545" t="inlineStr"/>
     </row>
     <row r="546">
@@ -20015,11 +17794,7 @@
           <t>14:95 | 14:50</t>
         </is>
       </c>
-      <c r="G546" t="inlineStr">
-        <is>
-          <t>A precious book depicting powerful bonds between men (95% Silence).</t>
-        </is>
-      </c>
+      <c r="G546" t="inlineStr"/>
       <c r="H546" t="inlineStr"/>
     </row>
     <row r="547">
@@ -20049,11 +17824,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t>A salty Luco special. The odor is an affront to the nose.</t>
-        </is>
-      </c>
+      <c r="G547" t="inlineStr"/>
       <c r="H547" t="inlineStr"/>
     </row>
     <row r="548">
@@ -20083,11 +17854,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G548" t="inlineStr">
-        <is>
-          <t>A bell designed to catch the Mad Catter of Mount Kongol. It glows faintly...</t>
-        </is>
-      </c>
+      <c r="G548" t="inlineStr"/>
       <c r="H548" t="inlineStr"/>
     </row>
     <row r="549">
@@ -20117,11 +17884,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G549" t="inlineStr">
-        <is>
-          <t>Can pry open doors on Mount Kongol. Also highly brandishable.</t>
-        </is>
-      </c>
+      <c r="G549" t="inlineStr"/>
       <c r="H549" t="inlineStr"/>
     </row>
     <row r="550">
@@ -20151,11 +17914,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>Orb that controls the tides. Tame the wild waters of the Dragon Palace.</t>
-        </is>
-      </c>
+      <c r="G550" t="inlineStr"/>
       <c r="H550" t="inlineStr"/>
     </row>
     <row r="551">
@@ -20185,11 +17944,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G551" t="inlineStr">
-        <is>
-          <t>Key to a door on the second floor of the Rousset Royal Villa.</t>
-        </is>
-      </c>
+      <c r="G551" t="inlineStr"/>
       <c r="H551" t="inlineStr"/>
     </row>
     <row r="552">
@@ -20219,11 +17974,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G552" t="inlineStr">
-        <is>
-          <t>Bell that summons a shady peddler. Only usable in Khorramshahr.</t>
-        </is>
-      </c>
+      <c r="G552" t="inlineStr"/>
       <c r="H552" t="inlineStr"/>
     </row>
     <row r="553">
@@ -20253,11 +18004,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G553" t="inlineStr">
-        <is>
-          <t>Seeds of an Otherworldly rose. They guzzle magic when they sprout.</t>
-        </is>
-      </c>
+      <c r="G553" t="inlineStr"/>
       <c r="H553" t="inlineStr"/>
     </row>
     <row r="554">
@@ -20287,11 +18034,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G554" t="inlineStr">
-        <is>
-          <t>Drawn from the miraculous Fountain of Life at the Temple of Wrappl.</t>
-        </is>
-      </c>
+      <c r="G554" t="inlineStr"/>
       <c r="H554" t="inlineStr"/>
     </row>
     <row r="555">
@@ -20321,11 +18064,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G555" t="inlineStr">
-        <is>
-          <t>Widely beloved fruit. Somebody in the Wildwoods might want it...</t>
-        </is>
-      </c>
+      <c r="G555" t="inlineStr"/>
       <c r="H555" t="inlineStr"/>
     </row>
     <row r="556">
@@ -20355,11 +18094,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G556" t="inlineStr">
-        <is>
-          <t>Access pass from the Spirit of Mag Mell. Show it to a Forest Guardian.</t>
-        </is>
-      </c>
+      <c r="G556" t="inlineStr"/>
       <c r="H556" t="inlineStr"/>
     </row>
     <row r="557">
@@ -20389,11 +18124,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G557" t="inlineStr">
-        <is>
-          <t>Magic-rich soil received from the Spirit of Mag Mell.</t>
-        </is>
-      </c>
+      <c r="G557" t="inlineStr"/>
       <c r="H557" t="inlineStr"/>
     </row>
     <row r="558">
@@ -20423,11 +18154,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>Perhaps you ought to bring this to Gruneworth B5F...</t>
-        </is>
-      </c>
+      <c r="G558" t="inlineStr"/>
       <c r="H558" t="inlineStr"/>
     </row>
     <row r="559">
@@ -20457,11 +18184,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t>Opens a path that's otherwise exclusive to the fairies of the Wildwood.</t>
-        </is>
-      </c>
+      <c r="G559" t="inlineStr"/>
       <c r="H559" t="inlineStr"/>
     </row>
     <row r="560">
@@ -20491,11 +18214,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>Marked with symbols like those on the circle in the Ruined Shrine Cave.</t>
-        </is>
-      </c>
+      <c r="G560" t="inlineStr"/>
       <c r="H560" t="inlineStr"/>
     </row>
     <row r="561">
@@ -20525,11 +18244,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G561" t="inlineStr">
-        <is>
-          <t>Opens a locked door in the town of Vrachia.</t>
-        </is>
-      </c>
+      <c r="G561" t="inlineStr"/>
       <c r="H561" t="inlineStr"/>
     </row>
     <row r="562">
@@ -20559,11 +18274,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G562" t="inlineStr">
-        <is>
-          <t>AKA the Four Guardians' Beads. Bring it somewhere with eerie swirls...</t>
-        </is>
-      </c>
+      <c r="G562" t="inlineStr"/>
       <c r="H562" t="inlineStr"/>
     </row>
     <row r="563">
@@ -20593,11 +18304,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>Cowbell that smells like a beast. Shaking it creates a soothing sound.</t>
-        </is>
-      </c>
+      <c r="G563" t="inlineStr"/>
       <c r="H563" t="inlineStr"/>
     </row>
     <row r="564">
@@ -20627,11 +18334,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>Spool that was owned by the three sisters of fate. Controls life itself.</t>
-        </is>
-      </c>
+      <c r="G564" t="inlineStr"/>
       <c r="H564" t="inlineStr"/>
     </row>
     <row r="565">
@@ -20661,11 +18364,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t>Opens the unopenable door in Area C of the Temple of Wrappl.</t>
-        </is>
-      </c>
+      <c r="G565" t="inlineStr"/>
       <c r="H565" t="inlineStr"/>
     </row>
     <row r="566">
@@ -20695,11 +18394,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G566" t="inlineStr">
-        <is>
-          <t>Rechargeable grass-cutter. Can clear your way in the Prizren Wildwood.</t>
-        </is>
-      </c>
+      <c r="G566" t="inlineStr"/>
       <c r="H566" t="inlineStr"/>
     </row>
     <row r="567">
@@ -20729,11 +18424,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>Lets you penetrate the dreams beyond dreams. We have to go deeper!</t>
-        </is>
-      </c>
+      <c r="G567" t="inlineStr"/>
       <c r="H567" t="inlineStr"/>
     </row>
     <row r="568">
@@ -20763,11 +18454,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G568" t="inlineStr">
-        <is>
-          <t>If you have strength and seek the four, bring this to where they wait.</t>
-        </is>
-      </c>
+      <c r="G568" t="inlineStr"/>
       <c r="H568" t="inlineStr"/>
     </row>
     <row r="569">
@@ -20797,11 +18484,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G569" t="inlineStr">
-        <is>
-          <t>A special card for a special customer. Yours, from Casino Esperanza.</t>
-        </is>
-      </c>
+      <c r="G569" t="inlineStr"/>
       <c r="H569" t="inlineStr"/>
     </row>
     <row r="570">
@@ -20831,11 +18514,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G570" t="inlineStr">
-        <is>
-          <t>The amount is 156,804,000. Sadly it's in some strange units called Yen.</t>
-        </is>
-      </c>
+      <c r="G570" t="inlineStr"/>
       <c r="H570" t="inlineStr"/>
     </row>
     <row r="571">
@@ -20865,11 +18544,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G571" t="inlineStr">
-        <is>
-          <t>Accursed fire. Throw some into the volcano in Hell's Hole for a party...</t>
-        </is>
-      </c>
+      <c r="G571" t="inlineStr"/>
       <c r="H571" t="inlineStr"/>
     </row>
     <row r="572">
@@ -20899,11 +18574,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G572" t="inlineStr">
-        <is>
-          <t>An employee pass with the Casino Esperanza logo.</t>
-        </is>
-      </c>
+      <c r="G572" t="inlineStr"/>
       <c r="H572" t="inlineStr"/>
     </row>
     <row r="573">
@@ -20933,11 +18604,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G573" t="inlineStr">
-        <is>
-          <t>Vintage camera with the Romulean royal crest. Vitoria might recognize it?</t>
-        </is>
-      </c>
+      <c r="G573" t="inlineStr"/>
       <c r="H573" t="inlineStr"/>
     </row>
     <row r="574">
@@ -20967,11 +18634,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G574" t="inlineStr">
-        <is>
-          <t>Shows the pre-death forms of the dead. Some monsters REALLY hate it.</t>
-        </is>
-      </c>
+      <c r="G574" t="inlineStr"/>
       <c r="H574" t="inlineStr"/>
     </row>
     <row r="575">
@@ -21001,11 +18664,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G575" t="inlineStr">
-        <is>
-          <t>A certain alchemist's favorite pen. Somewhere in the First Sealbook...?</t>
-        </is>
-      </c>
+      <c r="G575" t="inlineStr"/>
       <c r="H575" t="inlineStr"/>
     </row>
     <row r="576">
@@ -21035,11 +18694,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G576" t="inlineStr">
-        <is>
-          <t>Open the door and go: NEEEEENNNNWWSWWNENE... It continues.</t>
-        </is>
-      </c>
+      <c r="G576" t="inlineStr"/>
       <c r="H576" t="inlineStr"/>
     </row>
     <row r="577">
@@ -21069,11 +18724,7 @@
           <t xml:space="preserve"> | </t>
         </is>
       </c>
-      <c r="G577" t="inlineStr">
-        <is>
-          <t>On the obverse is Tenerezza's golden smile. On the reverse too.</t>
-        </is>
-      </c>
+      <c r="G577" t="inlineStr"/>
       <c r="H577" t="inlineStr"/>
     </row>
   </sheetData>

--- a/mod_project/data_tables/qol_item_text.xlsx
+++ b/mod_project/data_tables/qol_item_text.xlsx
@@ -2145,7 +2145,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Those who join the Order receive this medal.</t>
+          <t>Those who join the Order receive this medal. (20% War Cry)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2155,11 +2155,7 @@
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2393,7 +2389,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A fortunetelling book with a storied history.</t>
+          <t>A fortunetelling book with a storied history. (40% Accelerator)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2403,11 +2399,7 @@
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2777,7 +2769,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>no room for (50% sleep, 75% Accelerator): 89 characters</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5443,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Careful. Even though it's dead, it's still hungry.</t>
+          <t>Careful. Even though it's dead, it's still hungry. (lose 5% of gold)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5461,11 +5453,7 @@
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5497,7 +5485,7 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>no room for (lose 5% of gold): 81 characters</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8071,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Burning ice that sleeps in the ocean's depths.</t>
+          <t>Burning ice that sleeps in the ocean's depths. (Fireball Lv3)</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -8093,11 +8081,7 @@
         </is>
       </c>
       <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8151,7 +8135,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Emits a fell light and leads its owner to ruin.</t>
+          <t>Emits a fell light and leads its owner to ruin. (lose 5% of gold)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -8161,11 +8145,7 @@
         </is>
       </c>
       <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8245,7 +8225,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Apparently these are very expensive in some places.</t>
+          <t>Apparently these are very expensive in some places. (Fireball Lv3)</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -8255,11 +8235,7 @@
         </is>
       </c>
       <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11135,7 +11111,7 @@
       <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>no room for (HP/TP +360, 75% Accelerator): 78 characters</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12215,7 @@
       <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>no room for (25% Accelerator): 78 characters</t>
         </is>
       </c>
     </row>
@@ -12273,7 +12249,7 @@
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>no room for (50% speed up, 50% Accelerator): 77 characters</t>
         </is>
       </c>
     </row>
@@ -13349,7 +13325,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Potato chips covered with habanero powder.</t>
+          <t>Potato chips covered with habanero powder. (HP +120, 75% Accelerator)</t>
         </is>
       </c>
       <c r="E408" t="inlineStr"/>
@@ -13359,11 +13335,7 @@
         </is>
       </c>
       <c r="G408" t="inlineStr"/>
-      <c r="H408" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -13771,7 +13743,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Exquisite and jiggly almond-flavored tofu.</t>
+          <t>Exquisite and jiggly almond-flavored tofu. (TP +100, 50% Accelerator)</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -13781,11 +13753,7 @@
         </is>
       </c>
       <c r="G421" t="inlineStr"/>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>has an effect that is not decoded</t>
-        </is>
-      </c>
+      <c r="H421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">

--- a/mod_project/data_tables/qol_item_text.xlsx
+++ b/mod_project/data_tables/qol_item_text.xlsx
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Beasts love it! The flavor and nutrition balance is just right.</t>
+          <t>Beasts love it! Flavor and nutrition just right. (30% HP to Beasts)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1573,7 +1573,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A Souffle special. Goes off with a bang that makes you jump.</t>
+          <t>A Souffle special. Bang! (50% max HP damage up to 100, 75% stun)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>A sedative for pregnant women, but there are side effects...</t>
+          <t>Pregnancy sedative. Side effects... (50% sleep, 75% Accelerator)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2769,7 +2769,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>no room for (50% sleep, 75% Accelerator): 89 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>An experimental pill created by a secret organization. Do not consume.</t>
+          <t>Secret organization pill. Do not eat. (50% max HP damage up to 100)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Liquor made of crushed fairies. Not guaranteed not to curse you...</t>
+          <t>Liquor of crushed fairies. (silences Apparitions, 25% petrifying)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -4771,7 +4771,7 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Piece of the stone under which there sleeps a king of gamblers.</t>
+          <t>Stone under which sleeps a king of gamblers. (lose 5% of gold)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5485,7 +5485,7 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>no room for (lose 5% of gold): 81 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Water with malicious intent. Good thing it's stuck in the bottle.</t>
+          <t>Malicious water, stuck in its bottle. (20% max HP damage up to 100)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -8113,7 +8113,7 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>no room for (15% max HP damage, 0.8% petrifying): 102 characters</t>
         </is>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Aged, well-smoked horse meat. An exquisite dish.</t>
+          <t>Aged, smoked horse meat. Exquisite. (HP/TP +360, 75% Accelerator)</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
@@ -11111,7 +11111,7 @@
       <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
-          <t>no room for (HP/TP +360, 75% Accelerator): 78 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Food that smells like a public toilet that has gone uncleaned for years.</t>
+          <t>Smells like a filthy public toilet. (20% max HP damage up to 100)</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
@@ -11857,7 +11857,7 @@
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>So malodorous it's been mistaken for a chemical weapon.</t>
+          <t>Mistaken for a chemical weapon. (50% max HP damage up to 100)</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
-          <t>has an effect that is not decoded</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>It's sweet and spicy... What evil genius came up with this??</t>
+          <t>Sweet and spicy... What evil genius made this?? (25% Accelerator)</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
@@ -12215,7 +12215,7 @@
       <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr">
         <is>
-          <t>no room for (25% Accelerator): 78 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Hard to understand the point. Unbearably hot.</t>
+          <t>Pointless. Unbearably hot. (50% speed up, 50% Accelerator)</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -12249,7 +12249,7 @@
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr">
         <is>
-          <t>no room for (50% speed up, 50% Accelerator): 77 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_item_text.xlsx
+++ b/mod_project/data_tables/qol_item_text.xlsx
@@ -4759,7 +4759,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Liquor of crushed fairies. (silences Apparitions, 25% petrifying)</t>
+          <t>Liquor of crushed fairies. (silences Apparitions, 25% petry)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Unfortunately, it's a one-way ticket. (10% petrifying)</t>
+          <t>Unfortunately, it's a one-way ticket. (10% petry)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Honestly, just cut me some slack. (15% petrifying)</t>
+          <t>Honestly, just cut me some slack. (15% petry)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>A roiling mass of darkness. And... is that a green lady in there?</t>
+          <t>Roiling mass. Is that a green lady in there? (15% HP dmg, 0.8% petry)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -8331,7 +8331,7 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
-          <t>no room for (15% max HP damage, 0.8% petrifying): 102 characters</t>
+          <t>original sentence shortened to fit</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>I really hope my photo's not on there. (15% petrifying)</t>
+          <t>I really hope my photo's not on there. (15% petry)</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
